--- a/projects/2026-05-fujie-gcard-v1/versions/fujie_gcard_v7_20260630/reports_tuned_main_lgbm_tuned_balanced/model_report.xlsx
+++ b/projects/2026-05-fujie-gcard-v1/versions/fujie_gcard_v7_20260630/reports_tuned_main_lgbm_tuned_balanced/model_report.xlsx
@@ -24,10 +24,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
-    <numFmt numFmtId="166" formatCode="#,##0.000"/>
   </numFmts>
   <fonts count="8">
     <font>
@@ -179,7 +178,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -231,12 +230,6 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1109,7 +1102,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M231"/>
+  <dimension ref="A1:M238"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1380,7 +1373,7 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>本轮 model_score vs 旧版全客群 G卡V6</t>
+          <t>G卡V7 model_score vs 旧版全客群 G卡V6</t>
         </is>
       </c>
     </row>
@@ -2429,7 +2422,7 @@
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>本轮AUC</t>
+          <t>G卡V7 AUC</t>
         </is>
       </c>
       <c r="D67" s="6" t="inlineStr">
@@ -2454,7 +2447,7 @@
       </c>
       <c r="J67" s="6" t="inlineStr">
         <is>
-          <t>本轮KS</t>
+          <t>G卡V7 KS</t>
         </is>
       </c>
       <c r="K67" s="6" t="inlineStr">
@@ -2669,7 +2662,7 @@
       </c>
       <c r="D77" s="6" t="inlineStr">
         <is>
-          <t>本轮AUC</t>
+          <t>G卡V7 AUC</t>
         </is>
       </c>
       <c r="E77" s="6" t="inlineStr">
@@ -2699,7 +2692,7 @@
       </c>
       <c r="K77" s="6" t="inlineStr">
         <is>
-          <t>本轮KS</t>
+          <t>G卡V7 KS</t>
         </is>
       </c>
       <c r="L77" s="6" t="inlineStr">
@@ -2965,7 +2958,7 @@
       </c>
       <c r="D86" s="6" t="inlineStr">
         <is>
-          <t>本轮AUC</t>
+          <t>G卡V7 AUC</t>
         </is>
       </c>
       <c r="E86" s="6" t="inlineStr">
@@ -2995,7 +2988,7 @@
       </c>
       <c r="K86" s="6" t="inlineStr">
         <is>
-          <t>本轮KS</t>
+          <t>G卡V7 KS</t>
         </is>
       </c>
       <c r="L86" s="6" t="inlineStr">
@@ -3012,7 +3005,7 @@
     <row r="87">
       <c r="A87" s="7" t="inlineStr">
         <is>
-          <t>DEV-OOS 2025-06</t>
+          <t>2025-06 DEV-OOS</t>
         </is>
       </c>
       <c r="B87" s="8" t="n">
@@ -3032,7 +3025,7 @@
       </c>
       <c r="H87" s="7" t="inlineStr">
         <is>
-          <t>DEV-OOS 2025-06</t>
+          <t>2025-06 DEV-OOS</t>
         </is>
       </c>
       <c r="I87" s="8" t="n">
@@ -3054,7 +3047,7 @@
     <row r="88">
       <c r="A88" s="7" t="inlineStr">
         <is>
-          <t>DEV-OOS 2025-07</t>
+          <t>2025-07 DEV-OOS</t>
         </is>
       </c>
       <c r="B88" s="8" t="n">
@@ -3074,7 +3067,7 @@
       </c>
       <c r="H88" s="7" t="inlineStr">
         <is>
-          <t>DEV-OOS 2025-07</t>
+          <t>2025-07 DEV-OOS</t>
         </is>
       </c>
       <c r="I88" s="8" t="n">
@@ -3096,7 +3089,7 @@
     <row r="89">
       <c r="A89" s="7" t="inlineStr">
         <is>
-          <t>DEV-OOS 2025-08</t>
+          <t>2025-08 DEV-OOS</t>
         </is>
       </c>
       <c r="B89" s="8" t="n">
@@ -3116,7 +3109,7 @@
       </c>
       <c r="H89" s="7" t="inlineStr">
         <is>
-          <t>DEV-OOS 2025-08</t>
+          <t>2025-08 DEV-OOS</t>
         </is>
       </c>
       <c r="I89" s="8" t="n">
@@ -3138,7 +3131,7 @@
     <row r="90">
       <c r="A90" s="7" t="inlineStr">
         <is>
-          <t>DEV-OOS 2025-09</t>
+          <t>2025-09 DEV-OOS</t>
         </is>
       </c>
       <c r="B90" s="8" t="n">
@@ -3158,7 +3151,7 @@
       </c>
       <c r="H90" s="7" t="inlineStr">
         <is>
-          <t>DEV-OOS 2025-09</t>
+          <t>2025-09 DEV-OOS</t>
         </is>
       </c>
       <c r="I90" s="8" t="n">
@@ -3180,7 +3173,7 @@
     <row r="91">
       <c r="A91" s="7" t="inlineStr">
         <is>
-          <t>DEV-OOS 2025-10</t>
+          <t>2025-10 DEV-OOS</t>
         </is>
       </c>
       <c r="B91" s="8" t="n">
@@ -3200,7 +3193,7 @@
       </c>
       <c r="H91" s="7" t="inlineStr">
         <is>
-          <t>DEV-OOS 2025-10</t>
+          <t>2025-10 DEV-OOS</t>
         </is>
       </c>
       <c r="I91" s="8" t="n">
@@ -3222,7 +3215,7 @@
     <row r="92">
       <c r="A92" s="7" t="inlineStr">
         <is>
-          <t>DEV-OOS 2025-11</t>
+          <t>2025-11 DEV-OOS</t>
         </is>
       </c>
       <c r="B92" s="8" t="n">
@@ -3242,7 +3235,7 @@
       </c>
       <c r="H92" s="7" t="inlineStr">
         <is>
-          <t>DEV-OOS 2025-11</t>
+          <t>2025-11 DEV-OOS</t>
         </is>
       </c>
       <c r="I92" s="8" t="n">
@@ -3264,7 +3257,7 @@
     <row r="93">
       <c r="A93" s="7" t="inlineStr">
         <is>
-          <t>OOT-OOS 2025-12</t>
+          <t>2025-12 OOT-OOS</t>
         </is>
       </c>
       <c r="B93" s="8" t="n">
@@ -3284,7 +3277,7 @@
       </c>
       <c r="H93" s="7" t="inlineStr">
         <is>
-          <t>OOT-OOS 2025-12</t>
+          <t>2025-12 OOT-OOS</t>
         </is>
       </c>
       <c r="I93" s="8" t="n">
@@ -3306,7 +3299,7 @@
     <row r="94">
       <c r="A94" s="7" t="inlineStr">
         <is>
-          <t>OOT-OOS 2026-01</t>
+          <t>2026-01 OOT-OOS</t>
         </is>
       </c>
       <c r="B94" s="8" t="n">
@@ -3326,7 +3319,7 @@
       </c>
       <c r="H94" s="7" t="inlineStr">
         <is>
-          <t>OOT-OOS 2026-01</t>
+          <t>2026-01 OOT-OOS</t>
         </is>
       </c>
       <c r="I94" s="8" t="n">
@@ -3388,7 +3381,7 @@
     <row r="103">
       <c r="A103" s="4" t="inlineStr">
         <is>
-          <t>本轮模型</t>
+          <t>G卡V7</t>
         </is>
       </c>
       <c r="B103" s="5" t="n"/>
@@ -3475,8 +3468,10 @@
           <t>001</t>
         </is>
       </c>
-      <c r="B105" s="9" t="n">
-        <v>0.1000014293210929</v>
+      <c r="B105" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C105" s="9" t="n">
         <v>0.001143440530883104</v>
@@ -3495,8 +3490,10 @@
           <t>001</t>
         </is>
       </c>
-      <c r="I105" s="9" t="n">
-        <v>0.1000014293210929</v>
+      <c r="I105" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J105" s="9" t="n">
         <v>0.0007146503318019398</v>
@@ -3517,8 +3514,10 @@
           <t>002</t>
         </is>
       </c>
-      <c r="B106" s="9" t="n">
-        <v>0.09999938743381732</v>
+      <c r="B106" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C106" s="9" t="n">
         <v>0.001500781018693402</v>
@@ -3537,8 +3536,10 @@
           <t>002</t>
         </is>
       </c>
-      <c r="I106" s="9" t="n">
-        <v>0.09999938743381732</v>
+      <c r="I106" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J106" s="9" t="n">
         <v>0.001143452204718782</v>
@@ -3559,8 +3560,10 @@
           <t>003</t>
         </is>
       </c>
-      <c r="B107" s="9" t="n">
-        <v>0.09999938743381732</v>
+      <c r="B107" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C107" s="9" t="n">
         <v>0.002178011611524404</v>
@@ -3579,8 +3582,10 @@
           <t>003</t>
         </is>
       </c>
-      <c r="I107" s="9" t="n">
-        <v>0.09999938743381732</v>
+      <c r="I107" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J107" s="9" t="n">
         <v>0.001912566446369867</v>
@@ -3601,8 +3606,10 @@
           <t>004</t>
         </is>
       </c>
-      <c r="B108" s="9" t="n">
-        <v>0.09999938743381732</v>
+      <c r="B108" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C108" s="9" t="n">
         <v>0.003011786806331899</v>
@@ -3621,8 +3628,10 @@
           <t>004</t>
         </is>
       </c>
-      <c r="I108" s="9" t="n">
-        <v>0.09999938743381732</v>
+      <c r="I108" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J108" s="9" t="n">
         <v>0.002863749827715585</v>
@@ -3643,8 +3652,10 @@
           <t>005</t>
         </is>
       </c>
-      <c r="B109" s="9" t="n">
-        <v>0.1000014293210929</v>
+      <c r="B109" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C109" s="9" t="n">
         <v>0.004398216210918357</v>
@@ -3663,8 +3674,10 @@
           <t>005</t>
         </is>
       </c>
-      <c r="I109" s="9" t="n">
-        <v>0.1000014293210929</v>
+      <c r="I109" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J109" s="9" t="n">
         <v>0.004630990885033813</v>
@@ -3685,8 +3698,10 @@
           <t>006</t>
         </is>
       </c>
-      <c r="B110" s="9" t="n">
-        <v>0.09999938743381732</v>
+      <c r="B110" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C110" s="9" t="n">
         <v>0.007844244944630862</v>
@@ -3705,8 +3720,10 @@
           <t>006</t>
         </is>
       </c>
-      <c r="I110" s="9" t="n">
-        <v>0.09999938743381732</v>
+      <c r="I110" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J110" s="9" t="n">
         <v>0.008698433873525589</v>
@@ -3727,8 +3744,10 @@
           <t>007</t>
         </is>
       </c>
-      <c r="B111" s="9" t="n">
-        <v>0.09999938743381732</v>
+      <c r="B111" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C111" s="9" t="n">
         <v>0.01835657196196255</v>
@@ -3747,8 +3766,10 @@
           <t>007</t>
         </is>
       </c>
-      <c r="I111" s="9" t="n">
-        <v>0.09999938743381732</v>
+      <c r="I111" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J111" s="9" t="n">
         <v>0.01999883320693075</v>
@@ -3769,8 +3790,10 @@
           <t>008</t>
         </is>
       </c>
-      <c r="B112" s="9" t="n">
-        <v>0.09999938743381732</v>
+      <c r="B112" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C112" s="9" t="n">
         <v>0.04150650596997402</v>
@@ -3789,8 +3812,10 @@
           <t>008</t>
         </is>
       </c>
-      <c r="I112" s="9" t="n">
-        <v>0.09999938743381732</v>
+      <c r="I112" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J112" s="9" t="n">
         <v>0.04469185337192504</v>
@@ -3811,8 +3836,10 @@
           <t>009</t>
         </is>
       </c>
-      <c r="B113" s="9" t="n">
-        <v>0.09999938743381732</v>
+      <c r="B113" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C113" s="9" t="n">
         <v>0.08552344997821984</v>
@@ -3831,8 +3858,10 @@
           <t>009</t>
         </is>
       </c>
-      <c r="I113" s="9" t="n">
-        <v>0.09999938743381732</v>
+      <c r="I113" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J113" s="9" t="n">
         <v>0.0883344525918397</v>
@@ -3853,8 +3882,10 @@
           <t>010</t>
         </is>
       </c>
-      <c r="B114" s="9" t="n">
-        <v>0.1000014293210929</v>
+      <c r="B114" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C114" s="9" t="n">
         <v>0.1567332253855594</v>
@@ -3873,8 +3904,10 @@
           <t>010</t>
         </is>
       </c>
-      <c r="I114" s="9" t="n">
-        <v>0.1000014293210929</v>
+      <c r="I114" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J114" s="9" t="n">
         <v>0.1567332253855594</v>
@@ -3909,7 +3942,7 @@
     <row r="119">
       <c r="A119" s="4" t="inlineStr">
         <is>
-          <t>本轮模型</t>
+          <t>G卡V7</t>
         </is>
       </c>
       <c r="B119" s="5" t="n"/>
@@ -3996,8 +4029,10 @@
           <t>001</t>
         </is>
       </c>
-      <c r="B121" s="9" t="n">
-        <v>0.1000012304814874</v>
+      <c r="B121" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C121" s="9" t="n">
         <v>0.06053894425987449</v>
@@ -4016,8 +4051,10 @@
           <t>001</t>
         </is>
       </c>
-      <c r="I121" s="9" t="n">
-        <v>0.1000012304814874</v>
+      <c r="I121" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J121" s="9" t="n">
         <v>0.06921373200442968</v>
@@ -4038,8 +4075,10 @@
           <t>002</t>
         </is>
       </c>
-      <c r="B122" s="9" t="n">
-        <v>0.1000012304814874</v>
+      <c r="B122" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C122" s="9" t="n">
         <v>0.08767072720561092</v>
@@ -4058,8 +4097,10 @@
           <t>002</t>
         </is>
       </c>
-      <c r="I122" s="9" t="n">
-        <v>0.1000012304814874</v>
+      <c r="I122" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J122" s="9" t="n">
         <v>0.09972929740371601</v>
@@ -4080,8 +4121,10 @@
           <t>003</t>
         </is>
       </c>
-      <c r="B123" s="9" t="n">
-        <v>0.1000012304814874</v>
+      <c r="B123" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C123" s="9" t="n">
         <v>0.1149050490135761</v>
@@ -4100,8 +4143,10 @@
           <t>003</t>
         </is>
       </c>
-      <c r="I123" s="9" t="n">
-        <v>0.1000012304814874</v>
+      <c r="I123" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J123" s="9" t="n">
         <v>0.128583733234896</v>
@@ -4122,8 +4167,10 @@
           <t>004</t>
         </is>
       </c>
-      <c r="B124" s="9" t="n">
-        <v>0.09999507807405038</v>
+      <c r="B124" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C124" s="9" t="n">
         <v>0.145704837345228</v>
@@ -4142,8 +4189,10 @@
           <t>004</t>
         </is>
       </c>
-      <c r="I124" s="9" t="n">
-        <v>0.09999507807405038</v>
+      <c r="I124" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J124" s="9" t="n">
         <v>0.160562947012228</v>
@@ -4164,8 +4213,10 @@
           <t>005</t>
         </is>
       </c>
-      <c r="B125" s="9" t="n">
-        <v>0.1000012304814874</v>
+      <c r="B125" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C125" s="9" t="n">
         <v>0.1795149441976645</v>
@@ -4184,8 +4235,10 @@
           <t>005</t>
         </is>
       </c>
-      <c r="I125" s="9" t="n">
-        <v>0.1000012304814874</v>
+      <c r="I125" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J125" s="9" t="n">
         <v>0.1948713531604917</v>
@@ -4206,8 +4259,10 @@
           <t>006</t>
         </is>
       </c>
-      <c r="B126" s="9" t="n">
-        <v>0.1000012304814874</v>
+      <c r="B126" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C126" s="9" t="n">
         <v>0.2197225269936323</v>
@@ -4226,8 +4281,10 @@
           <t>006</t>
         </is>
       </c>
-      <c r="I126" s="9" t="n">
-        <v>0.1000012304814874</v>
+      <c r="I126" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J126" s="9" t="n">
         <v>0.2336474472688494</v>
@@ -4248,8 +4305,10 @@
           <t>007</t>
         </is>
       </c>
-      <c r="B127" s="9" t="n">
-        <v>0.09999507807405038</v>
+      <c r="B127" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C127" s="9" t="n">
         <v>0.2647658557164956</v>
@@ -4268,8 +4327,10 @@
           <t>007</t>
         </is>
       </c>
-      <c r="I127" s="9" t="n">
-        <v>0.09999507807405038</v>
+      <c r="I127" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J127" s="9" t="n">
         <v>0.2751459007171987</v>
@@ -4290,8 +4351,10 @@
           <t>008</t>
         </is>
       </c>
-      <c r="B128" s="9" t="n">
-        <v>0.1000012304814874</v>
+      <c r="B128" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C128" s="9" t="n">
         <v>0.3143274628931785</v>
@@ -4310,8 +4373,10 @@
           <t>008</t>
         </is>
       </c>
-      <c r="I128" s="9" t="n">
-        <v>0.1000012304814874</v>
+      <c r="I128" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J128" s="9" t="n">
         <v>0.320995154964239</v>
@@ -4332,8 +4397,10 @@
           <t>009</t>
         </is>
       </c>
-      <c r="B129" s="9" t="n">
-        <v>0.1000012304814874</v>
+      <c r="B129" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C129" s="9" t="n">
         <v>0.3675111427087036</v>
@@ -4352,8 +4419,10 @@
           <t>009</t>
         </is>
       </c>
-      <c r="I129" s="9" t="n">
-        <v>0.1000012304814874</v>
+      <c r="I129" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J129" s="9" t="n">
         <v>0.3703549260342895</v>
@@ -4374,8 +4443,10 @@
           <t>010</t>
         </is>
       </c>
-      <c r="B130" s="9" t="n">
-        <v>0.1000012304814874</v>
+      <c r="B130" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C130" s="9" t="n">
         <v>0.4240362253749893</v>
@@ -4394,8 +4465,10 @@
           <t>010</t>
         </is>
       </c>
-      <c r="I130" s="9" t="n">
-        <v>0.1000012304814874</v>
+      <c r="I130" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J130" s="9" t="n">
         <v>0.4240362253749893</v>
@@ -4430,7 +4503,7 @@
     <row r="135">
       <c r="A135" s="4" t="inlineStr">
         <is>
-          <t>本轮模型</t>
+          <t>G卡V7</t>
         </is>
       </c>
       <c r="B135" s="5" t="n"/>
@@ -4517,8 +4590,10 @@
           <t>001</t>
         </is>
       </c>
-      <c r="B137" s="9" t="n">
-        <v>0.1000015280940083</v>
+      <c r="B137" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C137" s="9" t="n">
         <v>0.0006112282631948902</v>
@@ -4537,8 +4612,10 @@
           <t>001</t>
         </is>
       </c>
-      <c r="I137" s="9" t="n">
-        <v>0.1000015280940083</v>
+      <c r="I137" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J137" s="9" t="n">
         <v>0.0006417896763546347</v>
@@ -4559,8 +4636,10 @@
           <t>002</t>
         </is>
       </c>
-      <c r="B138" s="9" t="n">
-        <v>0.09999847190599166</v>
+      <c r="B138" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C138" s="9" t="n">
         <v>0.001253037086841583</v>
@@ -4579,8 +4658,10 @@
           <t>002</t>
         </is>
       </c>
-      <c r="I138" s="9" t="n">
-        <v>0.09999847190599166</v>
+      <c r="I138" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J138" s="9" t="n">
         <v>0.0008557326446723002</v>
@@ -4601,8 +4682,10 @@
           <t>003</t>
         </is>
       </c>
-      <c r="B139" s="9" t="n">
-        <v>0.1000015280940083</v>
+      <c r="B139" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C139" s="9" t="n">
         <v>0.001497524500315804</v>
@@ -4621,8 +4704,10 @@
           <t>003</t>
         </is>
       </c>
-      <c r="I139" s="9" t="n">
-        <v>0.1000015280940083</v>
+      <c r="I139" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J139" s="9" t="n">
         <v>0.001151158289358407</v>
@@ -4643,8 +4728,10 @@
           <t>004</t>
         </is>
       </c>
-      <c r="B140" s="9" t="n">
-        <v>0.09999847190599166</v>
+      <c r="B140" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C140" s="9" t="n">
         <v>0.001933038920554392</v>
@@ -4663,8 +4750,10 @@
           <t>004</t>
         </is>
       </c>
-      <c r="I140" s="9" t="n">
-        <v>0.09999847190599166</v>
+      <c r="I140" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J140" s="9" t="n">
         <v>0.001596858238718846</v>
@@ -4685,8 +4774,10 @@
           <t>005</t>
         </is>
       </c>
-      <c r="B141" s="9" t="n">
-        <v>0.1000015280940083</v>
+      <c r="B141" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C141" s="9" t="n">
         <v>0.002451055298496971</v>
@@ -4705,8 +4796,10 @@
           <t>005</t>
         </is>
       </c>
-      <c r="I141" s="9" t="n">
-        <v>0.1000015280940083</v>
+      <c r="I141" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J141" s="9" t="n">
         <v>0.002182111574971119</v>
@@ -4727,8 +4820,10 @@
           <t>006</t>
         </is>
       </c>
-      <c r="B142" s="9" t="n">
-        <v>0.09999847190599166</v>
+      <c r="B142" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C142" s="9" t="n">
         <v>0.003020532489825441</v>
@@ -4747,8 +4842,10 @@
           <t>006</t>
         </is>
       </c>
-      <c r="I142" s="9" t="n">
-        <v>0.09999847190599166</v>
+      <c r="I142" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J142" s="9" t="n">
         <v>0.002888097675769013</v>
@@ -4769,8 +4866,10 @@
           <t>007</t>
         </is>
       </c>
-      <c r="B143" s="9" t="n">
-        <v>0.09999847190599166</v>
+      <c r="B143" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C143" s="9" t="n">
         <v>0.003903197216243238</v>
@@ -4789,8 +4888,10 @@
           <t>007</t>
         </is>
       </c>
-      <c r="I143" s="9" t="n">
-        <v>0.09999847190599166</v>
+      <c r="I143" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J143" s="9" t="n">
         <v>0.003942491147950385</v>
@@ -4811,8 +4912,10 @@
           <t>008</t>
         </is>
       </c>
-      <c r="B144" s="9" t="n">
-        <v>0.1000015280940083</v>
+      <c r="B144" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C144" s="9" t="n">
         <v>0.005252823153680414</v>
@@ -4831,8 +4934,10 @@
           <t>008</t>
         </is>
       </c>
-      <c r="I144" s="9" t="n">
-        <v>0.1000015280940083</v>
+      <c r="I144" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J144" s="9" t="n">
         <v>0.005573722895432527</v>
@@ -4853,8 +4958,10 @@
           <t>009</t>
         </is>
       </c>
-      <c r="B145" s="9" t="n">
-        <v>0.09999847190599166</v>
+      <c r="B145" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C145" s="9" t="n">
         <v>0.008064954292932722</v>
@@ -4873,8 +4980,10 @@
           <t>009</t>
         </is>
       </c>
-      <c r="I145" s="9" t="n">
-        <v>0.09999847190599166</v>
+      <c r="I145" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J145" s="9" t="n">
         <v>0.008845981445511471</v>
@@ -4895,8 +5004,10 @@
           <t>010</t>
         </is>
       </c>
-      <c r="B146" s="9" t="n">
-        <v>0.1000015280940083</v>
+      <c r="B146" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C146" s="9" t="n">
         <v>0.02395134548677435</v>
@@ -4915,8 +5026,10 @@
           <t>010</t>
         </is>
       </c>
-      <c r="I146" s="9" t="n">
-        <v>0.1000015280940083</v>
+      <c r="I146" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J146" s="9" t="n">
         <v>0.02395134548677435</v>
@@ -4944,7 +5057,7 @@
     <row r="151">
       <c r="A151" s="4" t="inlineStr">
         <is>
-          <t>老户次新(e2e3) 占比（意愿 x 资产评级）</t>
+          <t>全客群 intent=意愿档，zc=合计</t>
         </is>
       </c>
       <c r="B151" s="5" t="n"/>
@@ -4959,33 +5072,47 @@
     <row r="152">
       <c r="A152" s="6" t="inlineStr">
         <is>
-          <t>意愿</t>
-        </is>
-      </c>
-      <c r="B152" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C152" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="D152" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="E152" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="F152" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="G152" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="H152" s="6" t="n">
-        <v>7</v>
+          <t>意愿档</t>
+        </is>
+      </c>
+      <c r="B152" s="6" t="inlineStr">
+        <is>
+          <t>G卡V7 样本数</t>
+        </is>
+      </c>
+      <c r="C152" s="6" t="inlineStr">
+        <is>
+          <t>G卡V7 金额逾期率</t>
+        </is>
+      </c>
+      <c r="D152" s="6" t="inlineStr">
+        <is>
+          <t>G卡V7 人头风险率</t>
+        </is>
+      </c>
+      <c r="E152" s="6" t="inlineStr">
+        <is>
+          <t>G卡V7 FTR</t>
+        </is>
+      </c>
+      <c r="F152" s="6" t="inlineStr">
+        <is>
+          <t>G卡V6 样本数</t>
+        </is>
+      </c>
+      <c r="G152" s="6" t="inlineStr">
+        <is>
+          <t>G卡V6 金额逾期率</t>
+        </is>
+      </c>
+      <c r="H152" s="6" t="inlineStr">
+        <is>
+          <t>G卡V6 人头风险率</t>
+        </is>
       </c>
       <c r="I152" s="6" t="inlineStr">
         <is>
-          <t>sum</t>
+          <t>G卡V6 FTR</t>
         </is>
       </c>
     </row>
@@ -4995,30 +5122,14 @@
           <t>低意愿</t>
         </is>
       </c>
-      <c r="B153" s="15" t="n">
-        <v>0.010244</v>
-      </c>
-      <c r="C153" s="15" t="n">
-        <v>0.047749</v>
-      </c>
-      <c r="D153" s="15" t="n">
-        <v>0.088281</v>
-      </c>
-      <c r="E153" s="15" t="n">
-        <v>0.097676</v>
-      </c>
-      <c r="F153" s="15" t="n">
-        <v>0.016033</v>
-      </c>
-      <c r="G153" s="15" t="n">
-        <v>0.064871</v>
-      </c>
-      <c r="H153" s="15" t="n">
-        <v>0.008477999999999999</v>
-      </c>
-      <c r="I153" s="15" t="n">
-        <v>0.333332</v>
-      </c>
+      <c r="B153" s="16" t="n"/>
+      <c r="C153" s="16" t="n"/>
+      <c r="D153" s="16" t="n"/>
+      <c r="E153" s="7" t="n"/>
+      <c r="F153" s="16" t="n"/>
+      <c r="G153" s="16" t="n"/>
+      <c r="H153" s="16" t="n"/>
+      <c r="I153" s="7" t="n"/>
     </row>
     <row r="154">
       <c r="A154" s="7" t="inlineStr">
@@ -5026,30 +5137,14 @@
           <t>中意愿</t>
         </is>
       </c>
-      <c r="B154" s="15" t="n">
-        <v>0.014852</v>
-      </c>
-      <c r="C154" s="15" t="n">
-        <v>0.050388</v>
-      </c>
-      <c r="D154" s="15" t="n">
-        <v>0.071202</v>
-      </c>
-      <c r="E154" s="15" t="n">
-        <v>0.086048</v>
-      </c>
-      <c r="F154" s="15" t="n">
-        <v>0.016021</v>
-      </c>
-      <c r="G154" s="15" t="n">
-        <v>0.075582</v>
-      </c>
-      <c r="H154" s="15" t="n">
-        <v>0.019239</v>
-      </c>
-      <c r="I154" s="15" t="n">
-        <v>0.333332</v>
-      </c>
+      <c r="B154" s="16" t="n"/>
+      <c r="C154" s="16" t="n"/>
+      <c r="D154" s="16" t="n"/>
+      <c r="E154" s="7" t="n"/>
+      <c r="F154" s="16" t="n"/>
+      <c r="G154" s="16" t="n"/>
+      <c r="H154" s="16" t="n"/>
+      <c r="I154" s="7" t="n"/>
     </row>
     <row r="155">
       <c r="A155" s="7" t="inlineStr">
@@ -5057,1160 +5152,1154 @@
           <t>高意愿</t>
         </is>
       </c>
-      <c r="B155" s="15" t="n">
-        <v>0.013418</v>
-      </c>
-      <c r="C155" s="15" t="n">
-        <v>0.049631</v>
-      </c>
-      <c r="D155" s="15" t="n">
-        <v>0.06855</v>
-      </c>
-      <c r="E155" s="15" t="n">
-        <v>0.08766</v>
-      </c>
-      <c r="F155" s="15" t="n">
-        <v>0.015295</v>
-      </c>
-      <c r="G155" s="15" t="n">
-        <v>0.07398299999999999</v>
-      </c>
-      <c r="H155" s="15" t="n">
-        <v>0.0248</v>
-      </c>
-      <c r="I155" s="15" t="n">
-        <v>0.3333369999999999</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" s="7" t="inlineStr">
+      <c r="B155" s="16" t="n"/>
+      <c r="C155" s="16" t="n"/>
+      <c r="D155" s="16" t="n"/>
+      <c r="E155" s="7" t="n"/>
+      <c r="F155" s="16" t="n"/>
+      <c r="G155" s="16" t="n"/>
+      <c r="H155" s="16" t="n"/>
+      <c r="I155" s="7" t="n"/>
+    </row>
+    <row r="156"/>
+    <row r="157"/>
+    <row r="158">
+      <c r="A158" s="4" t="inlineStr">
+        <is>
+          <t>老户次新(e2e3) 占比（意愿 x 资产评级）</t>
+        </is>
+      </c>
+      <c r="B158" s="5" t="n"/>
+      <c r="C158" s="5" t="n"/>
+      <c r="D158" s="5" t="n"/>
+      <c r="E158" s="5" t="n"/>
+      <c r="F158" s="5" t="n"/>
+      <c r="G158" s="5" t="n"/>
+      <c r="H158" s="5" t="n"/>
+      <c r="I158" s="5" t="n"/>
+    </row>
+    <row r="159">
+      <c r="A159" s="6" t="inlineStr">
+        <is>
+          <t>意愿</t>
+        </is>
+      </c>
+      <c r="B159" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C159" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D159" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="E159" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="F159" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="G159" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="H159" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="I159" s="6" t="inlineStr">
         <is>
           <t>sum</t>
         </is>
       </c>
-      <c r="B156" s="15" t="n">
-        <v>0.038514</v>
-      </c>
-      <c r="C156" s="15" t="n">
-        <v>0.147768</v>
-      </c>
-      <c r="D156" s="15" t="n">
-        <v>0.228033</v>
-      </c>
-      <c r="E156" s="15" t="n">
-        <v>0.271384</v>
-      </c>
-      <c r="F156" s="15" t="n">
-        <v>0.047349</v>
-      </c>
-      <c r="G156" s="15" t="n">
-        <v>0.214436</v>
-      </c>
-      <c r="H156" s="15" t="n">
-        <v>0.05251699999999999</v>
-      </c>
-      <c r="I156" s="15" t="n">
-        <v>1.000001</v>
-      </c>
-    </row>
-    <row r="157"/>
-    <row r="158"/>
-    <row r="159">
-      <c r="A159" s="4" t="inlineStr">
-        <is>
-          <t>老户次新(e2e3) 30天发起率（意愿 x 资产评级）</t>
-        </is>
-      </c>
-      <c r="B159" s="5" t="n"/>
-      <c r="C159" s="5" t="n"/>
-      <c r="D159" s="5" t="n"/>
-      <c r="E159" s="5" t="n"/>
-      <c r="F159" s="5" t="n"/>
-      <c r="G159" s="5" t="n"/>
-      <c r="H159" s="5" t="n"/>
-      <c r="I159" s="5" t="n"/>
     </row>
     <row r="160">
-      <c r="A160" s="6" t="inlineStr">
-        <is>
-          <t>意愿</t>
-        </is>
-      </c>
-      <c r="B160" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C160" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="D160" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="E160" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="F160" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="G160" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="H160" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="I160" s="6" t="inlineStr">
-        <is>
-          <t>sum</t>
-        </is>
+      <c r="A160" s="7" t="inlineStr">
+        <is>
+          <t>低意愿</t>
+        </is>
+      </c>
+      <c r="B160" s="15" t="n">
+        <v>0.010244</v>
+      </c>
+      <c r="C160" s="15" t="n">
+        <v>0.047749</v>
+      </c>
+      <c r="D160" s="15" t="n">
+        <v>0.088281</v>
+      </c>
+      <c r="E160" s="15" t="n">
+        <v>0.097676</v>
+      </c>
+      <c r="F160" s="15" t="n">
+        <v>0.016033</v>
+      </c>
+      <c r="G160" s="15" t="n">
+        <v>0.064871</v>
+      </c>
+      <c r="H160" s="15" t="n">
+        <v>0.008477999999999999</v>
+      </c>
+      <c r="I160" s="15" t="n">
+        <v>0.333332</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="7" t="inlineStr">
         <is>
-          <t>低意愿</t>
+          <t>中意愿</t>
         </is>
       </c>
       <c r="B161" s="15" t="n">
-        <v>0.1231231231231231</v>
+        <v>0.014852</v>
       </c>
       <c r="C161" s="15" t="n">
-        <v>0.1132586006957866</v>
+        <v>0.050388</v>
       </c>
       <c r="D161" s="15" t="n">
-        <v>0.1216112621088578</v>
+        <v>0.071202</v>
       </c>
       <c r="E161" s="15" t="n">
-        <v>0.1266061980347695</v>
+        <v>0.086048</v>
       </c>
       <c r="F161" s="15" t="n">
-        <v>0.1343054489639294</v>
+        <v>0.016021</v>
       </c>
       <c r="G161" s="15" t="n">
-        <v>0.1332511380880121</v>
+        <v>0.075582</v>
       </c>
       <c r="H161" s="15" t="n">
-        <v>0.1161103047895501</v>
+        <v>0.019239</v>
       </c>
       <c r="I161" s="15" t="n">
-        <v>0.1246608464534229</v>
+        <v>0.333332</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="7" t="inlineStr">
         <is>
-          <t>中意愿</t>
+          <t>高意愿</t>
         </is>
       </c>
       <c r="B162" s="15" t="n">
-        <v>0.343827671913836</v>
+        <v>0.013418</v>
       </c>
       <c r="C162" s="15" t="n">
-        <v>0.3628815628815629</v>
+        <v>0.049631</v>
       </c>
       <c r="D162" s="15" t="n">
-        <v>0.3611855180160719</v>
+        <v>0.06855</v>
       </c>
       <c r="E162" s="15" t="n">
-        <v>0.3797368797368798</v>
+        <v>0.08766</v>
       </c>
       <c r="F162" s="15" t="n">
-        <v>0.380184331797235</v>
+        <v>0.015295</v>
       </c>
       <c r="G162" s="15" t="n">
-        <v>0.3874643874643874</v>
+        <v>0.07398299999999999</v>
       </c>
       <c r="H162" s="15" t="n">
-        <v>0.3776782858970259</v>
+        <v>0.0248</v>
       </c>
       <c r="I162" s="15" t="n">
-        <v>0.3732811605972794</v>
+        <v>0.3333369999999999</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="7" t="inlineStr">
         <is>
-          <t>高意愿</t>
+          <t>sum</t>
         </is>
       </c>
       <c r="B163" s="15" t="n">
-        <v>0.7574507106831728</v>
+        <v>0.038514</v>
       </c>
       <c r="C163" s="15" t="n">
-        <v>0.7799677699268626</v>
+        <v>0.147768</v>
       </c>
       <c r="D163" s="15" t="n">
-        <v>0.7736492550709029</v>
+        <v>0.228033</v>
       </c>
       <c r="E163" s="15" t="n">
-        <v>0.7799691184727681</v>
+        <v>0.271384</v>
       </c>
       <c r="F163" s="15" t="n">
-        <v>0.7707160096540627</v>
+        <v>0.047349</v>
       </c>
       <c r="G163" s="15" t="n">
-        <v>0.7682328482328482</v>
+        <v>0.214436</v>
       </c>
       <c r="H163" s="15" t="n">
-        <v>0.772264946663359</v>
+        <v>0.05251699999999999</v>
       </c>
       <c r="I163" s="15" t="n">
-        <v>0.7741602067183463</v>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" s="7" t="inlineStr">
+        <v>1.000001</v>
+      </c>
+    </row>
+    <row r="164"/>
+    <row r="165"/>
+    <row r="166">
+      <c r="A166" s="4" t="inlineStr">
+        <is>
+          <t>老户次新(e2e3) 30天发起率（意愿 x 资产评级）</t>
+        </is>
+      </c>
+      <c r="B166" s="5" t="n"/>
+      <c r="C166" s="5" t="n"/>
+      <c r="D166" s="5" t="n"/>
+      <c r="E166" s="5" t="n"/>
+      <c r="F166" s="5" t="n"/>
+      <c r="G166" s="5" t="n"/>
+      <c r="H166" s="5" t="n"/>
+      <c r="I166" s="5" t="n"/>
+    </row>
+    <row r="167">
+      <c r="A167" s="6" t="inlineStr">
+        <is>
+          <t>意愿</t>
+        </is>
+      </c>
+      <c r="B167" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C167" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D167" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="E167" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="F167" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="G167" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="H167" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="I167" s="6" t="inlineStr">
         <is>
           <t>sum</t>
         </is>
       </c>
-      <c r="B164" s="15" t="n">
-        <v>0.4292332268370607</v>
-      </c>
-      <c r="C164" s="15" t="n">
-        <v>0.4223082687984012</v>
-      </c>
-      <c r="D164" s="15" t="n">
-        <v>0.3924293114612562</v>
-      </c>
-      <c r="E164" s="15" t="n">
-        <v>0.417909771026978</v>
-      </c>
-      <c r="F164" s="15" t="n">
-        <v>0.4230769230769231</v>
-      </c>
-      <c r="G164" s="15" t="n">
-        <v>0.4419291903368336</v>
-      </c>
-      <c r="H164" s="15" t="n">
-        <v>0.5217900656044986</v>
-      </c>
-      <c r="I164" s="15" t="n">
-        <v>0.4240362253749893</v>
-      </c>
-    </row>
-    <row r="165"/>
-    <row r="166"/>
-    <row r="167">
-      <c r="A167" s="4" t="inlineStr">
-        <is>
-          <t>流失户(b2) 占比（意愿 x 资产评级）</t>
-        </is>
-      </c>
-      <c r="B167" s="5" t="n"/>
-      <c r="C167" s="5" t="n"/>
-      <c r="D167" s="5" t="n"/>
-      <c r="E167" s="5" t="n"/>
-      <c r="F167" s="5" t="n"/>
-      <c r="G167" s="5" t="n"/>
-      <c r="H167" s="5" t="n"/>
-      <c r="I167" s="5" t="n"/>
     </row>
     <row r="168">
-      <c r="A168" s="6" t="inlineStr">
-        <is>
-          <t>意愿</t>
-        </is>
-      </c>
-      <c r="B168" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C168" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="D168" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="E168" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="F168" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="G168" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="H168" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="I168" s="6" t="inlineStr">
-        <is>
-          <t>sum</t>
-        </is>
+      <c r="A168" s="7" t="inlineStr">
+        <is>
+          <t>低意愿</t>
+        </is>
+      </c>
+      <c r="B168" s="15" t="n">
+        <v>0.1231231231231231</v>
+      </c>
+      <c r="C168" s="15" t="n">
+        <v>0.1132586006957866</v>
+      </c>
+      <c r="D168" s="15" t="n">
+        <v>0.1216112621088578</v>
+      </c>
+      <c r="E168" s="15" t="n">
+        <v>0.1266061980347695</v>
+      </c>
+      <c r="F168" s="15" t="n">
+        <v>0.1343054489639294</v>
+      </c>
+      <c r="G168" s="15" t="n">
+        <v>0.1332511380880121</v>
+      </c>
+      <c r="H168" s="15" t="n">
+        <v>0.1161103047895501</v>
+      </c>
+      <c r="I168" s="15" t="n">
+        <v>0.1246608464534229</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="7" t="inlineStr">
         <is>
-          <t>低意愿</t>
+          <t>中意愿</t>
         </is>
       </c>
       <c r="B169" s="15" t="n">
-        <v>3.4e-05</v>
+        <v>0.343827671913836</v>
       </c>
       <c r="C169" s="15" t="n">
-        <v>0.000248</v>
+        <v>0.3628815628815629</v>
       </c>
       <c r="D169" s="15" t="n">
-        <v>0.001898</v>
+        <v>0.3611855180160719</v>
       </c>
       <c r="E169" s="15" t="n">
-        <v>0.005278</v>
+        <v>0.3797368797368798</v>
       </c>
       <c r="F169" s="15" t="n">
-        <v>0.01261</v>
+        <v>0.380184331797235</v>
       </c>
       <c r="G169" s="15" t="n">
-        <v>0.148781</v>
+        <v>0.3874643874643874</v>
       </c>
       <c r="H169" s="15" t="n">
-        <v>0.164487</v>
+        <v>0.3776782858970259</v>
       </c>
       <c r="I169" s="15" t="n">
-        <v>0.333336</v>
+        <v>0.3732811605972794</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="7" t="inlineStr">
         <is>
-          <t>中意愿</t>
+          <t>高意愿</t>
         </is>
       </c>
       <c r="B170" s="15" t="n">
-        <v>0.000807</v>
+        <v>0.7574507106831728</v>
       </c>
       <c r="C170" s="15" t="n">
-        <v>0.004318</v>
+        <v>0.7799677699268626</v>
       </c>
       <c r="D170" s="15" t="n">
-        <v>0.014942</v>
+        <v>0.7736492550709029</v>
       </c>
       <c r="E170" s="15" t="n">
-        <v>0.018389</v>
+        <v>0.7799691184727681</v>
       </c>
       <c r="F170" s="15" t="n">
-        <v>0.053526</v>
+        <v>0.7707160096540627</v>
       </c>
       <c r="G170" s="15" t="n">
-        <v>0.185006</v>
+        <v>0.7682328482328482</v>
       </c>
       <c r="H170" s="15" t="n">
-        <v>0.056341</v>
+        <v>0.772264946663359</v>
       </c>
       <c r="I170" s="15" t="n">
-        <v>0.333329</v>
+        <v>0.7741602067183463</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="7" t="inlineStr">
         <is>
-          <t>高意愿</t>
+          <t>sum</t>
         </is>
       </c>
       <c r="B171" s="15" t="n">
-        <v>0.015085</v>
+        <v>0.4292332268370607</v>
       </c>
       <c r="C171" s="15" t="n">
-        <v>0.036323</v>
+        <v>0.4223082687984012</v>
       </c>
       <c r="D171" s="15" t="n">
-        <v>0.053526</v>
+        <v>0.3924293114612562</v>
       </c>
       <c r="E171" s="15" t="n">
-        <v>0.034553</v>
+        <v>0.417909771026978</v>
       </c>
       <c r="F171" s="15" t="n">
-        <v>0.075928</v>
+        <v>0.4230769230769231</v>
       </c>
       <c r="G171" s="15" t="n">
-        <v>0.103253</v>
+        <v>0.4419291903368336</v>
       </c>
       <c r="H171" s="15" t="n">
-        <v>0.014667</v>
+        <v>0.5217900656044986</v>
       </c>
       <c r="I171" s="15" t="n">
-        <v>0.333335</v>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" s="7" t="inlineStr">
+        <v>0.4240362253749893</v>
+      </c>
+    </row>
+    <row r="172"/>
+    <row r="173"/>
+    <row r="174">
+      <c r="A174" s="4" t="inlineStr">
+        <is>
+          <t>流失户(b2) 占比（意愿 x 资产评级）</t>
+        </is>
+      </c>
+      <c r="B174" s="5" t="n"/>
+      <c r="C174" s="5" t="n"/>
+      <c r="D174" s="5" t="n"/>
+      <c r="E174" s="5" t="n"/>
+      <c r="F174" s="5" t="n"/>
+      <c r="G174" s="5" t="n"/>
+      <c r="H174" s="5" t="n"/>
+      <c r="I174" s="5" t="n"/>
+    </row>
+    <row r="175">
+      <c r="A175" s="6" t="inlineStr">
+        <is>
+          <t>意愿</t>
+        </is>
+      </c>
+      <c r="B175" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C175" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D175" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="E175" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="F175" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="G175" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="H175" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="I175" s="6" t="inlineStr">
         <is>
           <t>sum</t>
         </is>
       </c>
-      <c r="B172" s="15" t="n">
-        <v>0.015926</v>
-      </c>
-      <c r="C172" s="15" t="n">
-        <v>0.040889</v>
-      </c>
-      <c r="D172" s="15" t="n">
-        <v>0.070366</v>
-      </c>
-      <c r="E172" s="15" t="n">
-        <v>0.05822</v>
-      </c>
-      <c r="F172" s="15" t="n">
-        <v>0.142064</v>
-      </c>
-      <c r="G172" s="15" t="n">
-        <v>0.43704</v>
-      </c>
-      <c r="H172" s="15" t="n">
-        <v>0.235495</v>
-      </c>
-      <c r="I172" s="15" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="173"/>
-    <row r="174"/>
-    <row r="175">
-      <c r="A175" s="4" t="inlineStr">
-        <is>
-          <t>流失户(b2) 30天发起率（意愿 x 资产评级）</t>
-        </is>
-      </c>
-      <c r="B175" s="5" t="n"/>
-      <c r="C175" s="5" t="n"/>
-      <c r="D175" s="5" t="n"/>
-      <c r="E175" s="5" t="n"/>
-      <c r="F175" s="5" t="n"/>
-      <c r="G175" s="5" t="n"/>
-      <c r="H175" s="5" t="n"/>
-      <c r="I175" s="5" t="n"/>
     </row>
     <row r="176">
-      <c r="A176" s="6" t="inlineStr">
-        <is>
-          <t>意愿</t>
-        </is>
-      </c>
-      <c r="B176" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C176" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="D176" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="E176" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="F176" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="G176" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="H176" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="I176" s="6" t="inlineStr">
-        <is>
-          <t>sum</t>
-        </is>
+      <c r="A176" s="7" t="inlineStr">
+        <is>
+          <t>低意愿</t>
+        </is>
+      </c>
+      <c r="B176" s="15" t="n">
+        <v>3.4e-05</v>
+      </c>
+      <c r="C176" s="15" t="n">
+        <v>0.000248</v>
+      </c>
+      <c r="D176" s="15" t="n">
+        <v>0.001898</v>
+      </c>
+      <c r="E176" s="15" t="n">
+        <v>0.005278</v>
+      </c>
+      <c r="F176" s="15" t="n">
+        <v>0.01261</v>
+      </c>
+      <c r="G176" s="15" t="n">
+        <v>0.148781</v>
+      </c>
+      <c r="H176" s="15" t="n">
+        <v>0.164487</v>
+      </c>
+      <c r="I176" s="15" t="n">
+        <v>0.333336</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="7" t="inlineStr">
         <is>
-          <t>低意愿</t>
+          <t>中意愿</t>
         </is>
       </c>
       <c r="B177" s="15" t="n">
-        <v>0</v>
+        <v>0.000807</v>
       </c>
       <c r="C177" s="15" t="n">
-        <v>0</v>
+        <v>0.004318</v>
       </c>
       <c r="D177" s="15" t="n">
-        <v>0.00322061191626409</v>
+        <v>0.014942</v>
       </c>
       <c r="E177" s="15" t="n">
-        <v>0</v>
+        <v>0.018389</v>
       </c>
       <c r="F177" s="15" t="n">
-        <v>0.001211827435773146</v>
+        <v>0.053526</v>
       </c>
       <c r="G177" s="15" t="n">
-        <v>0.001684400805225751</v>
+        <v>0.185006</v>
       </c>
       <c r="H177" s="15" t="n">
-        <v>0.001802270489214247</v>
+        <v>0.056341</v>
       </c>
       <c r="I177" s="15" t="n">
-        <v>0.001705342489616665</v>
+        <v>0.333329</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="7" t="inlineStr">
         <is>
-          <t>中意愿</t>
+          <t>高意愿</t>
         </is>
       </c>
       <c r="B178" s="15" t="n">
-        <v>0</v>
+        <v>0.015085</v>
       </c>
       <c r="C178" s="15" t="n">
-        <v>0.005661712668082095</v>
+        <v>0.036323</v>
       </c>
       <c r="D178" s="15" t="n">
-        <v>0.004499897729597055</v>
+        <v>0.053526</v>
       </c>
       <c r="E178" s="15" t="n">
-        <v>0.003988698687053349</v>
+        <v>0.034553</v>
       </c>
       <c r="F178" s="15" t="n">
-        <v>0.004339385634349663</v>
+        <v>0.075928</v>
       </c>
       <c r="G178" s="15" t="n">
-        <v>0.00536879491203436</v>
+        <v>0.103253</v>
       </c>
       <c r="H178" s="15" t="n">
-        <v>0.007973962571196095</v>
+        <v>0.014667</v>
       </c>
       <c r="I178" s="15" t="n">
-        <v>0.005519543033181439</v>
+        <v>0.333335</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="7" t="inlineStr">
         <is>
+          <t>sum</t>
+        </is>
+      </c>
+      <c r="B179" s="15" t="n">
+        <v>0.015926</v>
+      </c>
+      <c r="C179" s="15" t="n">
+        <v>0.040889</v>
+      </c>
+      <c r="D179" s="15" t="n">
+        <v>0.070366</v>
+      </c>
+      <c r="E179" s="15" t="n">
+        <v>0.05822</v>
+      </c>
+      <c r="F179" s="15" t="n">
+        <v>0.142064</v>
+      </c>
+      <c r="G179" s="15" t="n">
+        <v>0.43704</v>
+      </c>
+      <c r="H179" s="15" t="n">
+        <v>0.235495</v>
+      </c>
+      <c r="I179" s="15" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="180"/>
+    <row r="181"/>
+    <row r="182">
+      <c r="A182" s="4" t="inlineStr">
+        <is>
+          <t>流失户(b2) 30天发起率（意愿 x 资产评级）</t>
+        </is>
+      </c>
+      <c r="B182" s="5" t="n"/>
+      <c r="C182" s="5" t="n"/>
+      <c r="D182" s="5" t="n"/>
+      <c r="E182" s="5" t="n"/>
+      <c r="F182" s="5" t="n"/>
+      <c r="G182" s="5" t="n"/>
+      <c r="H182" s="5" t="n"/>
+      <c r="I182" s="5" t="n"/>
+    </row>
+    <row r="183">
+      <c r="A183" s="6" t="inlineStr">
+        <is>
+          <t>意愿</t>
+        </is>
+      </c>
+      <c r="B183" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C183" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D183" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="E183" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="F183" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="G183" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="H183" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="I183" s="6" t="inlineStr">
+        <is>
+          <t>sum</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="7" t="inlineStr">
+        <is>
+          <t>低意愿</t>
+        </is>
+      </c>
+      <c r="B184" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C184" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D184" s="15" t="n">
+        <v>0.00322061191626409</v>
+      </c>
+      <c r="E184" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F184" s="15" t="n">
+        <v>0.001211827435773146</v>
+      </c>
+      <c r="G184" s="15" t="n">
+        <v>0.001684400805225751</v>
+      </c>
+      <c r="H184" s="15" t="n">
+        <v>0.001802270489214247</v>
+      </c>
+      <c r="I184" s="15" t="n">
+        <v>0.001705342489616665</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="7" t="inlineStr">
+        <is>
+          <t>中意愿</t>
+        </is>
+      </c>
+      <c r="B185" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C185" s="15" t="n">
+        <v>0.005661712668082095</v>
+      </c>
+      <c r="D185" s="15" t="n">
+        <v>0.004499897729597055</v>
+      </c>
+      <c r="E185" s="15" t="n">
+        <v>0.003988698687053349</v>
+      </c>
+      <c r="F185" s="15" t="n">
+        <v>0.004339385634349663</v>
+      </c>
+      <c r="G185" s="15" t="n">
+        <v>0.00536879491203436</v>
+      </c>
+      <c r="H185" s="15" t="n">
+        <v>0.007973962571196095</v>
+      </c>
+      <c r="I185" s="15" t="n">
+        <v>0.005519543033181439</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="7" t="inlineStr">
+        <is>
           <t>高意愿</t>
         </is>
       </c>
-      <c r="B179" s="15" t="n">
+      <c r="B186" s="15" t="n">
         <v>0.08792544570502431</v>
       </c>
-      <c r="C179" s="15" t="n">
+      <c r="C186" s="15" t="n">
         <v>0.07034076567101388</v>
       </c>
-      <c r="D179" s="15" t="n">
+      <c r="D186" s="15" t="n">
         <v>0.05966655247230787</v>
       </c>
-      <c r="E179" s="15" t="n">
+      <c r="E186" s="15" t="n">
         <v>0.05121174597558818</v>
       </c>
-      <c r="F179" s="15" t="n">
+      <c r="F186" s="15" t="n">
         <v>0.05333279665110288</v>
       </c>
-      <c r="G179" s="15" t="n">
+      <c r="G186" s="15" t="n">
         <v>0.0671895811750777</v>
       </c>
-      <c r="H179" s="15" t="n">
+      <c r="H186" s="15" t="n">
         <v>0.1166909772869348</v>
       </c>
-      <c r="I179" s="15" t="n">
+      <c r="I186" s="15" t="n">
         <v>0.06462881295326811</v>
       </c>
     </row>
-    <row r="180">
-      <c r="A180" s="7" t="inlineStr">
+    <row r="187">
+      <c r="A187" s="7" t="inlineStr">
         <is>
           <t>sum</t>
         </is>
       </c>
-      <c r="B180" s="15" t="n">
+      <c r="B187" s="15" t="n">
         <v>0.08328535789675685</v>
       </c>
-      <c r="C180" s="15" t="n">
+      <c r="C187" s="15" t="n">
         <v>0.0630839375140145</v>
       </c>
-      <c r="D180" s="15" t="n">
+      <c r="D187" s="15" t="n">
         <v>0.04642981236970118</v>
       </c>
-      <c r="E180" s="15" t="n">
+      <c r="E187" s="15" t="n">
         <v>0.03165354330708661</v>
       </c>
-      <c r="F180" s="15" t="n">
+      <c r="F187" s="15" t="n">
         <v>0.03024696669821874</v>
       </c>
-      <c r="G180" s="15" t="n">
+      <c r="G187" s="15" t="n">
         <v>0.01872001790184753</v>
       </c>
-      <c r="H180" s="15" t="n">
+      <c r="H187" s="15" t="n">
         <v>0.01043410550905197</v>
       </c>
-      <c r="I180" s="15" t="n">
+      <c r="I187" s="15" t="n">
         <v>0.02395134548677435</v>
       </c>
     </row>
-    <row r="181"/>
-    <row r="182"/>
-    <row r="183">
-      <c r="A183" s="3" t="inlineStr">
+    <row r="188"/>
+    <row r="189"/>
+    <row r="190">
+      <c r="A190" s="3" t="inlineStr">
         <is>
           <t>五、模型稳定性</t>
         </is>
       </c>
     </row>
-    <row r="184"/>
-    <row r="185">
-      <c r="A185" s="13" t="inlineStr">
+    <row r="191"/>
+    <row r="192">
+      <c r="A192" s="13" t="inlineStr">
         <is>
           <t>PSI 同步展示月度汇总和按月/版本/decile 分箱明细覆盖情况；PSI 保留三位小数。</t>
         </is>
       </c>
-      <c r="B185" s="5" t="n"/>
-      <c r="C185" s="5" t="n"/>
-      <c r="D185" s="5" t="n"/>
-      <c r="E185" s="5" t="n"/>
-      <c r="F185" s="5" t="n"/>
-      <c r="G185" s="5" t="n"/>
-      <c r="H185" s="5" t="n"/>
-    </row>
-    <row r="186"/>
-    <row r="187">
-      <c r="A187" s="4" t="inlineStr">
+      <c r="B192" s="5" t="n"/>
+      <c r="C192" s="5" t="n"/>
+      <c r="D192" s="5" t="n"/>
+      <c r="E192" s="5" t="n"/>
+      <c r="F192" s="5" t="n"/>
+      <c r="G192" s="5" t="n"/>
+      <c r="H192" s="5" t="n"/>
+    </row>
+    <row r="193"/>
+    <row r="194">
+      <c r="A194" s="4" t="inlineStr">
         <is>
           <t>月度 PSI</t>
         </is>
       </c>
-      <c r="B187" s="5" t="n"/>
-      <c r="C187" s="5" t="n"/>
-      <c r="D187" s="5" t="n"/>
-      <c r="E187" s="5" t="n"/>
-    </row>
-    <row r="188">
-      <c r="A188" s="6" t="inlineStr">
+      <c r="B194" s="5" t="n"/>
+      <c r="C194" s="5" t="n"/>
+      <c r="D194" s="5" t="n"/>
+      <c r="E194" s="5" t="n"/>
+    </row>
+    <row r="195">
+      <c r="A195" s="6" t="inlineStr">
         <is>
           <t>月份</t>
         </is>
       </c>
-      <c r="B188" s="6" t="inlineStr">
-        <is>
-          <t>本轮 PSI</t>
-        </is>
-      </c>
-      <c r="C188" s="6" t="inlineStr">
-        <is>
-          <t>本轮样本数</t>
-        </is>
-      </c>
-      <c r="D188" s="6" t="inlineStr">
+      <c r="B195" s="6" t="inlineStr">
+        <is>
+          <t>G卡V7 PSI</t>
+        </is>
+      </c>
+      <c r="C195" s="6" t="inlineStr">
+        <is>
+          <t>G卡V7 样本数</t>
+        </is>
+      </c>
+      <c r="D195" s="6" t="inlineStr">
         <is>
           <t>G卡V6 PSI</t>
         </is>
       </c>
-      <c r="E188" s="6" t="inlineStr">
-        <is>
-          <t>G卡V6样本数</t>
-        </is>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" s="7" t="inlineStr">
-        <is>
-          <t>2025-06</t>
-        </is>
-      </c>
-      <c r="B189" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C189" s="8" t="n">
-        <v>60987</v>
-      </c>
-      <c r="D189" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E189" s="8" t="n">
-        <v>60987</v>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" s="7" t="inlineStr">
-        <is>
-          <t>2025-07</t>
-        </is>
-      </c>
-      <c r="B190" s="14" t="n">
-        <v>0.0042066470274786</v>
-      </c>
-      <c r="C190" s="8" t="n">
-        <v>60999</v>
-      </c>
-      <c r="D190" s="14" t="n">
-        <v>0.0039617289107395</v>
-      </c>
-      <c r="E190" s="8" t="n">
-        <v>60999</v>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" s="7" t="inlineStr">
-        <is>
-          <t>2025-08</t>
-        </is>
-      </c>
-      <c r="B191" s="14" t="n">
-        <v>0.0082819345625923</v>
-      </c>
-      <c r="C191" s="8" t="n">
-        <v>61035</v>
-      </c>
-      <c r="D191" s="14" t="n">
-        <v>0.008781353907189701</v>
-      </c>
-      <c r="E191" s="8" t="n">
-        <v>61035</v>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" s="7" t="inlineStr">
-        <is>
-          <t>2025-09</t>
-        </is>
-      </c>
-      <c r="B192" s="14" t="n">
-        <v>0.0201542045656684</v>
-      </c>
-      <c r="C192" s="8" t="n">
-        <v>61200</v>
-      </c>
-      <c r="D192" s="14" t="n">
-        <v>0.0205341765523362</v>
-      </c>
-      <c r="E192" s="8" t="n">
-        <v>61200</v>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" s="7" t="inlineStr">
-        <is>
-          <t>2025-10</t>
-        </is>
-      </c>
-      <c r="B193" s="14" t="n">
-        <v>0.0292165455740987</v>
-      </c>
-      <c r="C193" s="8" t="n">
-        <v>61423</v>
-      </c>
-      <c r="D193" s="14" t="n">
-        <v>0.0309303876901276</v>
-      </c>
-      <c r="E193" s="8" t="n">
-        <v>61423</v>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" s="7" t="inlineStr">
-        <is>
-          <t>2025-11</t>
-        </is>
-      </c>
-      <c r="B194" s="14" t="n">
-        <v>0.0370667797034462</v>
-      </c>
-      <c r="C194" s="8" t="n">
-        <v>61575</v>
-      </c>
-      <c r="D194" s="14" t="n">
-        <v>0.0374946297787315</v>
-      </c>
-      <c r="E194" s="8" t="n">
-        <v>61575</v>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" s="7" t="inlineStr">
-        <is>
-          <t>2025-12</t>
-        </is>
-      </c>
-      <c r="B195" s="14" t="n">
-        <v>0.0390540762640348</v>
-      </c>
-      <c r="C195" s="8" t="n">
-        <v>61187</v>
-      </c>
-      <c r="D195" s="14" t="n">
-        <v>0.037953859267198</v>
-      </c>
-      <c r="E195" s="8" t="n">
-        <v>61187</v>
+      <c r="E195" s="6" t="inlineStr">
+        <is>
+          <t>G卡V6 样本数</t>
+        </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="7" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="B196" s="14" t="n">
-        <v>0.0515761509290846</v>
+        <v>0</v>
       </c>
       <c r="C196" s="8" t="n">
-        <v>61337</v>
+        <v>60987</v>
       </c>
       <c r="D196" s="14" t="n">
-        <v>0.0513486409380324</v>
+        <v>0</v>
       </c>
       <c r="E196" s="8" t="n">
-        <v>61337</v>
-      </c>
-    </row>
-    <row r="197"/>
-    <row r="198"/>
+        <v>60987</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="7" t="inlineStr">
+        <is>
+          <t>2025-07</t>
+        </is>
+      </c>
+      <c r="B197" s="14" t="n">
+        <v>0.0042066470274786</v>
+      </c>
+      <c r="C197" s="8" t="n">
+        <v>60999</v>
+      </c>
+      <c r="D197" s="14" t="n">
+        <v>0.0039617289107395</v>
+      </c>
+      <c r="E197" s="8" t="n">
+        <v>60999</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="7" t="inlineStr">
+        <is>
+          <t>2025-08</t>
+        </is>
+      </c>
+      <c r="B198" s="14" t="n">
+        <v>0.0082819345625923</v>
+      </c>
+      <c r="C198" s="8" t="n">
+        <v>61035</v>
+      </c>
+      <c r="D198" s="14" t="n">
+        <v>0.008781353907189701</v>
+      </c>
+      <c r="E198" s="8" t="n">
+        <v>61035</v>
+      </c>
+    </row>
     <row r="199">
-      <c r="A199" s="4" t="inlineStr">
-        <is>
-          <t>分箱 PSI 明细（基线月 vs 最新月）</t>
-        </is>
-      </c>
-      <c r="B199" s="5" t="n"/>
-      <c r="C199" s="5" t="n"/>
-      <c r="D199" s="5" t="n"/>
-      <c r="E199" s="5" t="n"/>
+      <c r="A199" s="7" t="inlineStr">
+        <is>
+          <t>2025-09</t>
+        </is>
+      </c>
+      <c r="B199" s="14" t="n">
+        <v>0.0201542045656684</v>
+      </c>
+      <c r="C199" s="8" t="n">
+        <v>61200</v>
+      </c>
+      <c r="D199" s="14" t="n">
+        <v>0.0205341765523362</v>
+      </c>
+      <c r="E199" s="8" t="n">
+        <v>61200</v>
+      </c>
     </row>
     <row r="200">
-      <c r="A200" s="6" t="inlineStr">
-        <is>
-          <t>版本</t>
-        </is>
-      </c>
-      <c r="B200" s="6" t="inlineStr">
-        <is>
-          <t>分箱</t>
-        </is>
-      </c>
-      <c r="C200" s="6" t="inlineStr">
-        <is>
-          <t>基线占比(2025-06)</t>
-        </is>
-      </c>
-      <c r="D200" s="6" t="inlineStr">
-        <is>
-          <t>当期占比(2026-01)</t>
-        </is>
-      </c>
-      <c r="E200" s="6" t="inlineStr">
-        <is>
-          <t>PSI贡献</t>
-        </is>
+      <c r="A200" s="7" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="B200" s="14" t="n">
+        <v>0.0292165455740987</v>
+      </c>
+      <c r="C200" s="8" t="n">
+        <v>61423</v>
+      </c>
+      <c r="D200" s="14" t="n">
+        <v>0.0309303876901276</v>
+      </c>
+      <c r="E200" s="8" t="n">
+        <v>61423</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="7" t="inlineStr">
         <is>
-          <t>本轮</t>
-        </is>
-      </c>
-      <c r="B201" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="C201" s="9" t="n">
-        <v>0.0941</v>
-      </c>
-      <c r="D201" s="9" t="n">
-        <v>0.09859999999999999</v>
-      </c>
-      <c r="E201" s="14" t="n">
-        <v>0.00021</v>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="B201" s="14" t="n">
+        <v>0.0370667797034462</v>
+      </c>
+      <c r="C201" s="8" t="n">
+        <v>61575</v>
+      </c>
+      <c r="D201" s="14" t="n">
+        <v>0.0374946297787315</v>
+      </c>
+      <c r="E201" s="8" t="n">
+        <v>61575</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="7" t="inlineStr">
         <is>
-          <t>本轮</t>
-        </is>
-      </c>
-      <c r="B202" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C202" s="9" t="n">
-        <v>0.08599999999999999</v>
-      </c>
-      <c r="D202" s="9" t="n">
-        <v>0.1055</v>
-      </c>
-      <c r="E202" s="14" t="n">
-        <v>0.00397</v>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="B202" s="14" t="n">
+        <v>0.0390540762640348</v>
+      </c>
+      <c r="C202" s="8" t="n">
+        <v>61187</v>
+      </c>
+      <c r="D202" s="14" t="n">
+        <v>0.037953859267198</v>
+      </c>
+      <c r="E202" s="8" t="n">
+        <v>61187</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="7" t="inlineStr">
         <is>
-          <t>本轮</t>
-        </is>
-      </c>
-      <c r="B203" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="C203" s="9" t="n">
-        <v>0.0828</v>
-      </c>
-      <c r="D203" s="9" t="n">
-        <v>0.1119</v>
-      </c>
-      <c r="E203" s="14" t="n">
-        <v>0.00877</v>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" s="7" t="inlineStr">
-        <is>
-          <t>本轮</t>
-        </is>
-      </c>
-      <c r="B204" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="C204" s="9" t="n">
-        <v>0.0824</v>
-      </c>
-      <c r="D204" s="9" t="n">
-        <v>0.1158</v>
-      </c>
-      <c r="E204" s="14" t="n">
-        <v>0.01136</v>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" s="7" t="inlineStr">
-        <is>
-          <t>本轮</t>
-        </is>
-      </c>
-      <c r="B205" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="C205" s="9" t="n">
-        <v>0.0945</v>
-      </c>
-      <c r="D205" s="9" t="n">
-        <v>0.1051</v>
-      </c>
-      <c r="E205" s="14" t="n">
-        <v>0.00112</v>
-      </c>
-    </row>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="B203" s="14" t="n">
+        <v>0.0515761509290846</v>
+      </c>
+      <c r="C203" s="8" t="n">
+        <v>61337</v>
+      </c>
+      <c r="D203" s="14" t="n">
+        <v>0.0513486409380324</v>
+      </c>
+      <c r="E203" s="8" t="n">
+        <v>61337</v>
+      </c>
+    </row>
+    <row r="204"/>
+    <row r="205"/>
     <row r="206">
-      <c r="A206" s="7" t="inlineStr">
-        <is>
-          <t>本轮</t>
-        </is>
-      </c>
-      <c r="B206" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="C206" s="9" t="n">
-        <v>0.1025</v>
-      </c>
-      <c r="D206" s="9" t="n">
-        <v>0.0983</v>
-      </c>
-      <c r="E206" s="14" t="n">
-        <v>0.00018</v>
-      </c>
+      <c r="A206" s="4" t="inlineStr">
+        <is>
+          <t>分箱 PSI 明细（基线月 vs 最新月）</t>
+        </is>
+      </c>
+      <c r="B206" s="5" t="n"/>
+      <c r="C206" s="5" t="n"/>
+      <c r="D206" s="5" t="n"/>
+      <c r="E206" s="5" t="n"/>
     </row>
     <row r="207">
-      <c r="A207" s="7" t="inlineStr">
-        <is>
-          <t>本轮</t>
-        </is>
-      </c>
-      <c r="B207" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="C207" s="9" t="n">
-        <v>0.1103</v>
-      </c>
-      <c r="D207" s="9" t="n">
-        <v>0.0969</v>
-      </c>
-      <c r="E207" s="14" t="n">
-        <v>0.00173</v>
+      <c r="A207" s="6" t="inlineStr">
+        <is>
+          <t>版本</t>
+        </is>
+      </c>
+      <c r="B207" s="6" t="inlineStr">
+        <is>
+          <t>分箱</t>
+        </is>
+      </c>
+      <c r="C207" s="6" t="inlineStr">
+        <is>
+          <t>基线占比(2025-06)</t>
+        </is>
+      </c>
+      <c r="D207" s="6" t="inlineStr">
+        <is>
+          <t>当期占比(2026-01)</t>
+        </is>
+      </c>
+      <c r="E207" s="6" t="inlineStr">
+        <is>
+          <t>PSI贡献</t>
+        </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="7" t="inlineStr">
         <is>
-          <t>本轮</t>
+          <t>G卡V7</t>
         </is>
       </c>
       <c r="B208" s="7" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C208" s="9" t="n">
-        <v>0.1142</v>
+        <v>0.0941</v>
       </c>
       <c r="D208" s="9" t="n">
-        <v>0.09569999999999999</v>
+        <v>0.09859999999999999</v>
       </c>
       <c r="E208" s="14" t="n">
-        <v>0.00327</v>
+        <v>0.00021</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="7" t="inlineStr">
         <is>
-          <t>本轮</t>
+          <t>G卡V7</t>
         </is>
       </c>
       <c r="B209" s="7" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C209" s="9" t="n">
-        <v>0.1143</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="D209" s="9" t="n">
-        <v>0.0941</v>
+        <v>0.1055</v>
       </c>
       <c r="E209" s="14" t="n">
-        <v>0.00392</v>
+        <v>0.00397</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="7" t="inlineStr">
         <is>
-          <t>本轮</t>
+          <t>G卡V7</t>
         </is>
       </c>
       <c r="B210" s="7" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="C210" s="9" t="n">
-        <v>0.1189</v>
+        <v>0.0828</v>
       </c>
       <c r="D210" s="9" t="n">
-        <v>0.07820000000000001</v>
+        <v>0.1119</v>
       </c>
       <c r="E210" s="14" t="n">
-        <v>0.01705</v>
+        <v>0.00877</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="7" t="inlineStr">
         <is>
-          <t>G卡V6</t>
+          <t>G卡V7</t>
         </is>
       </c>
       <c r="B211" s="7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C211" s="9" t="n">
-        <v>0.0954</v>
+        <v>0.0824</v>
       </c>
       <c r="D211" s="9" t="n">
-        <v>0.1027</v>
+        <v>0.1158</v>
       </c>
       <c r="E211" s="14" t="n">
-        <v>0.00054</v>
+        <v>0.01136</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="7" t="inlineStr">
         <is>
-          <t>G卡V6</t>
+          <t>G卡V7</t>
         </is>
       </c>
       <c r="B212" s="7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C212" s="9" t="n">
-        <v>0.0808</v>
+        <v>0.0945</v>
       </c>
       <c r="D212" s="9" t="n">
-        <v>0.1089</v>
+        <v>0.1051</v>
       </c>
       <c r="E212" s="14" t="n">
-        <v>0.008399999999999999</v>
+        <v>0.00112</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="7" t="inlineStr">
         <is>
-          <t>G卡V6</t>
+          <t>G卡V7</t>
         </is>
       </c>
       <c r="B213" s="7" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C213" s="9" t="n">
-        <v>0.0827</v>
+        <v>0.1025</v>
       </c>
       <c r="D213" s="9" t="n">
-        <v>0.112</v>
+        <v>0.0983</v>
       </c>
       <c r="E213" s="14" t="n">
-        <v>0.00889</v>
+        <v>0.00018</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="7" t="inlineStr">
         <is>
-          <t>G卡V6</t>
+          <t>G卡V7</t>
         </is>
       </c>
       <c r="B214" s="7" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C214" s="9" t="n">
-        <v>0.0851</v>
+        <v>0.1103</v>
       </c>
       <c r="D214" s="9" t="n">
-        <v>0.1118</v>
+        <v>0.0969</v>
       </c>
       <c r="E214" s="14" t="n">
-        <v>0.0073</v>
+        <v>0.00173</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="7" t="inlineStr">
         <is>
-          <t>G卡V6</t>
+          <t>G卡V7</t>
         </is>
       </c>
       <c r="B215" s="7" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C215" s="9" t="n">
-        <v>0.1018</v>
+        <v>0.1142</v>
       </c>
       <c r="D215" s="9" t="n">
-        <v>0.105</v>
+        <v>0.09569999999999999</v>
       </c>
       <c r="E215" s="14" t="n">
-        <v>0.0001</v>
+        <v>0.00327</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="7" t="inlineStr">
         <is>
-          <t>G卡V6</t>
+          <t>G卡V7</t>
         </is>
       </c>
       <c r="B216" s="7" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C216" s="9" t="n">
-        <v>0.0994</v>
+        <v>0.1143</v>
       </c>
       <c r="D216" s="9" t="n">
-        <v>0.099</v>
+        <v>0.0941</v>
       </c>
       <c r="E216" s="14" t="n">
-        <v>0</v>
+        <v>0.00392</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="7" t="inlineStr">
         <is>
-          <t>G卡V6</t>
+          <t>G卡V7</t>
         </is>
       </c>
       <c r="B217" s="7" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C217" s="9" t="n">
-        <v>0.1079</v>
+        <v>0.1189</v>
       </c>
       <c r="D217" s="9" t="n">
-        <v>0.0931</v>
+        <v>0.07820000000000001</v>
       </c>
       <c r="E217" s="14" t="n">
-        <v>0.00218</v>
+        <v>0.01705</v>
       </c>
     </row>
     <row r="218">
@@ -6220,16 +6309,16 @@
         </is>
       </c>
       <c r="B218" s="7" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C218" s="9" t="n">
-        <v>0.1117</v>
+        <v>0.0954</v>
       </c>
       <c r="D218" s="9" t="n">
-        <v>0.09569999999999999</v>
+        <v>0.1027</v>
       </c>
       <c r="E218" s="14" t="n">
-        <v>0.00246</v>
+        <v>0.00054</v>
       </c>
     </row>
     <row r="219">
@@ -6239,16 +6328,16 @@
         </is>
       </c>
       <c r="B219" s="7" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C219" s="9" t="n">
-        <v>0.1176</v>
+        <v>0.0808</v>
       </c>
       <c r="D219" s="9" t="n">
-        <v>0.09329999999999999</v>
+        <v>0.1089</v>
       </c>
       <c r="E219" s="14" t="n">
-        <v>0.00565</v>
+        <v>0.008399999999999999</v>
       </c>
     </row>
     <row r="220">
@@ -6258,174 +6347,308 @@
         </is>
       </c>
       <c r="B220" s="7" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="C220" s="9" t="n">
-        <v>0.1176</v>
+        <v>0.0827</v>
       </c>
       <c r="D220" s="9" t="n">
-        <v>0.0785</v>
+        <v>0.112</v>
       </c>
       <c r="E220" s="14" t="n">
-        <v>0.01584</v>
-      </c>
-    </row>
-    <row r="221"/>
-    <row r="222"/>
+        <v>0.00889</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="7" t="inlineStr">
+        <is>
+          <t>G卡V6</t>
+        </is>
+      </c>
+      <c r="B221" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="C221" s="9" t="n">
+        <v>0.0851</v>
+      </c>
+      <c r="D221" s="9" t="n">
+        <v>0.1118</v>
+      </c>
+      <c r="E221" s="14" t="n">
+        <v>0.0073</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="7" t="inlineStr">
+        <is>
+          <t>G卡V6</t>
+        </is>
+      </c>
+      <c r="B222" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="C222" s="9" t="n">
+        <v>0.1018</v>
+      </c>
+      <c r="D222" s="9" t="n">
+        <v>0.105</v>
+      </c>
+      <c r="E222" s="14" t="n">
+        <v>0.0001</v>
+      </c>
+    </row>
     <row r="223">
-      <c r="A223" s="4" t="inlineStr">
-        <is>
-          <t>补充数据覆盖核对</t>
-        </is>
-      </c>
-      <c r="B223" s="5" t="n"/>
-      <c r="C223" s="5" t="n"/>
+      <c r="A223" s="7" t="inlineStr">
+        <is>
+          <t>G卡V6</t>
+        </is>
+      </c>
+      <c r="B223" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C223" s="9" t="n">
+        <v>0.0994</v>
+      </c>
+      <c r="D223" s="9" t="n">
+        <v>0.099</v>
+      </c>
+      <c r="E223" s="14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="224">
-      <c r="A224" s="6" t="inlineStr">
-        <is>
-          <t>数据项</t>
-        </is>
-      </c>
-      <c r="B224" s="6" t="inlineStr">
-        <is>
-          <t>状态</t>
-        </is>
-      </c>
-      <c r="C224" s="6" t="inlineStr">
-        <is>
-          <t>说明</t>
-        </is>
+      <c r="A224" s="7" t="inlineStr">
+        <is>
+          <t>G卡V6</t>
+        </is>
+      </c>
+      <c r="B224" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="C224" s="9" t="n">
+        <v>0.1079</v>
+      </c>
+      <c r="D224" s="9" t="n">
+        <v>0.0931</v>
+      </c>
+      <c r="E224" s="14" t="n">
+        <v>0.00218</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="7" t="inlineStr">
         <is>
-          <t>特征筛选全过程</t>
-        </is>
-      </c>
-      <c r="B225" s="7" t="inlineStr">
-        <is>
-          <t>已补齐</t>
-        </is>
-      </c>
-      <c r="C225" s="7" t="inlineStr">
-        <is>
-          <t>feature_selection/*.json/txt 已落到当前 run。</t>
-        </is>
+          <t>G卡V6</t>
+        </is>
+      </c>
+      <c r="B225" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="C225" s="9" t="n">
+        <v>0.1117</v>
+      </c>
+      <c r="D225" s="9" t="n">
+        <v>0.09569999999999999</v>
+      </c>
+      <c r="E225" s="14" t="n">
+        <v>0.00246</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="7" t="inlineStr">
         <is>
-          <t>稳定性分箱明细</t>
-        </is>
-      </c>
-      <c r="B226" s="7" t="inlineStr">
-        <is>
-          <t>已补齐</t>
-        </is>
-      </c>
-      <c r="C226" s="7" t="inlineStr">
-        <is>
-          <t>score_psi_bin_detail.csv 覆盖按月、按分箱的 base/current 占比与 PSI component。</t>
-        </is>
+          <t>G卡V6</t>
+        </is>
+      </c>
+      <c r="B226" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="C226" s="9" t="n">
+        <v>0.1176</v>
+      </c>
+      <c r="D226" s="9" t="n">
+        <v>0.09329999999999999</v>
+      </c>
+      <c r="E226" s="14" t="n">
+        <v>0.00565</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="7" t="inlineStr">
         <is>
+          <t>G卡V6</t>
+        </is>
+      </c>
+      <c r="B227" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="C227" s="9" t="n">
+        <v>0.1176</v>
+      </c>
+      <c r="D227" s="9" t="n">
+        <v>0.0785</v>
+      </c>
+      <c r="E227" s="14" t="n">
+        <v>0.01584</v>
+      </c>
+    </row>
+    <row r="228"/>
+    <row r="229"/>
+    <row r="230">
+      <c r="A230" s="4" t="inlineStr">
+        <is>
+          <t>补充数据覆盖核对</t>
+        </is>
+      </c>
+      <c r="B230" s="5" t="n"/>
+      <c r="C230" s="5" t="n"/>
+    </row>
+    <row r="231">
+      <c r="A231" s="6" t="inlineStr">
+        <is>
+          <t>数据项</t>
+        </is>
+      </c>
+      <c r="B231" s="6" t="inlineStr">
+        <is>
+          <t>状态</t>
+        </is>
+      </c>
+      <c r="C231" s="6" t="inlineStr">
+        <is>
+          <t>说明</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="7" t="inlineStr">
+        <is>
+          <t>特征筛选全过程</t>
+        </is>
+      </c>
+      <c r="B232" s="7" t="inlineStr">
+        <is>
+          <t>已补齐</t>
+        </is>
+      </c>
+      <c r="C232" s="7" t="inlineStr">
+        <is>
+          <t>feature_selection/*.json/txt 已落到当前 run。</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="7" t="inlineStr">
+        <is>
+          <t>稳定性分箱明细</t>
+        </is>
+      </c>
+      <c r="B233" s="7" t="inlineStr">
+        <is>
+          <t>已补齐</t>
+        </is>
+      </c>
+      <c r="C233" s="7" t="inlineStr">
+        <is>
+          <t>score_psi_bin_detail.csv 覆盖按月、按分箱的 base/current 占比与 PSI component。</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="7" t="inlineStr">
+        <is>
           <t>意愿风险矩阵（分客群）</t>
         </is>
       </c>
-      <c r="B227" s="7" t="inlineStr">
+      <c r="B234" s="7" t="inlineStr">
         <is>
           <t>已补齐</t>
         </is>
       </c>
-      <c r="C227" s="7" t="inlineStr">
+      <c r="C234" s="7" t="inlineStr">
         <is>
           <t>intent_zc_*_{e2e3,b2}.csv 覆盖意愿 x 资产评级的分客群矩阵。</t>
         </is>
       </c>
     </row>
-    <row r="228">
-      <c r="A228" s="7" t="inlineStr">
+    <row r="235">
+      <c r="A235" s="7" t="inlineStr">
         <is>
           <t>报告刷新范围</t>
         </is>
       </c>
-      <c r="B228" s="7" t="inlineStr">
+      <c r="B235" s="7" t="inlineStr">
         <is>
           <t>已补齐</t>
         </is>
       </c>
-      <c r="C228" s="7" t="inlineStr">
+      <c r="C235" s="7" t="inlineStr">
         <is>
           <t>本次刷新由 rmw report 统一生成；未直接重跑训练/评估。</t>
         </is>
       </c>
     </row>
-    <row r="229"/>
-    <row r="230"/>
-    <row r="231">
-      <c r="A231" s="13" t="inlineStr">
+    <row r="236"/>
+    <row r="237"/>
+    <row r="238">
+      <c r="A238" s="13" t="inlineStr">
         <is>
           <t>证据提示：本页不补造缺失结果；当前 run audit 仍应以 rmw run audit 输出为准。</t>
         </is>
       </c>
-      <c r="B231" s="5" t="n"/>
-      <c r="C231" s="5" t="n"/>
-      <c r="D231" s="5" t="n"/>
-      <c r="E231" s="5" t="n"/>
-      <c r="F231" s="5" t="n"/>
-      <c r="G231" s="5" t="n"/>
-      <c r="H231" s="5" t="n"/>
+      <c r="B238" s="5" t="n"/>
+      <c r="C238" s="5" t="n"/>
+      <c r="D238" s="5" t="n"/>
+      <c r="E238" s="5" t="n"/>
+      <c r="F238" s="5" t="n"/>
+      <c r="G238" s="5" t="n"/>
+      <c r="H238" s="5" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="44">
+  <mergeCells count="45">
     <mergeCell ref="B2:M2"/>
+    <mergeCell ref="A174:I174"/>
     <mergeCell ref="H85:M85"/>
     <mergeCell ref="A97:M97"/>
     <mergeCell ref="A64:H64"/>
     <mergeCell ref="A20:G20"/>
     <mergeCell ref="A60:H60"/>
     <mergeCell ref="A62:M62"/>
-    <mergeCell ref="A223:C223"/>
+    <mergeCell ref="A158:I158"/>
     <mergeCell ref="H119:M119"/>
-    <mergeCell ref="A175:I175"/>
+    <mergeCell ref="A190:M190"/>
     <mergeCell ref="A44:M44"/>
     <mergeCell ref="A85:F85"/>
     <mergeCell ref="A151:I151"/>
     <mergeCell ref="A76:F76"/>
-    <mergeCell ref="A187:E187"/>
     <mergeCell ref="H46:I46"/>
     <mergeCell ref="A99:H99"/>
     <mergeCell ref="A135:F135"/>
     <mergeCell ref="A46:E46"/>
-    <mergeCell ref="A159:I159"/>
     <mergeCell ref="A66:E66"/>
     <mergeCell ref="A133:H133"/>
+    <mergeCell ref="A238:H238"/>
     <mergeCell ref="A74:H74"/>
     <mergeCell ref="A18:H18"/>
     <mergeCell ref="A101:H101"/>
+    <mergeCell ref="A192:H192"/>
+    <mergeCell ref="A230:C230"/>
     <mergeCell ref="H76:M76"/>
     <mergeCell ref="A6:M6"/>
     <mergeCell ref="H8:M8"/>
     <mergeCell ref="H66:L66"/>
-    <mergeCell ref="A185:H185"/>
+    <mergeCell ref="A194:E194"/>
     <mergeCell ref="H135:M135"/>
-    <mergeCell ref="A167:I167"/>
     <mergeCell ref="A8:B8"/>
     <mergeCell ref="B4:M4"/>
     <mergeCell ref="A16:M16"/>
-    <mergeCell ref="A183:M183"/>
+    <mergeCell ref="A206:E206"/>
+    <mergeCell ref="A166:I166"/>
     <mergeCell ref="H103:M103"/>
-    <mergeCell ref="A231:H231"/>
+    <mergeCell ref="A182:I182"/>
     <mergeCell ref="B3:M3"/>
     <mergeCell ref="A103:F103"/>
     <mergeCell ref="A149:M149"/>
-    <mergeCell ref="A199:E199"/>
     <mergeCell ref="A119:F119"/>
     <mergeCell ref="A117:H117"/>
   </mergeCells>
@@ -27511,7 +27734,7 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>最终训练特征</t>
+          <t>选取Top500特征入模</t>
         </is>
       </c>
       <c r="C10" s="7" t="n">
@@ -27870,7 +28093,7 @@
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>（1）在 OOT-OOS 样本上老户次新客群上，本轮全客群模型 KS 0.437；对比G卡V5 KS 0.402 提升3.5个百分点，对比G卡V6 KS 0.436 提升0.1个百分点。</t>
+          <t>（1）在 OOT-OOS 样本上老户次新客群上，G卡V7全客群模型 KS 0.437；对比G卡V5 KS 0.402 提升3.5个百分点，对比G卡V6 KS 0.436 提升0.1个百分点。</t>
         </is>
       </c>
     </row>
@@ -27880,7 +28103,7 @@
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>（2）在 OOT-OOS 样本上流失户客群上，本轮全客群模型 KS 0.650；对比G卡V5 KS 0.632 提升1.9个百分点，较G卡V6 KS 0.651 低0.0个百分点。</t>
+          <t>（2）在 OOT-OOS 样本上流失户客群上，G卡V7全客群模型 KS 0.650；对比G卡V5 KS 0.632 提升1.9个百分点，较G卡V6 KS 0.651 低0.0个百分点。</t>
         </is>
       </c>
     </row>
@@ -27890,7 +28113,7 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>（3）在 OOT-OOS 样本上全客群整体看，本轮模型 KS 0.719，对比G卡V5 KS 0.693 提升2.6个百分点，对比G卡V6 KS 0.716 提升0.3个百分点。</t>
+          <t>（3）在 OOT-OOS 样本上全客群整体看，G卡V7 KS 0.719，对比G卡V5 KS 0.693 提升2.6个百分点，对比G卡V6 KS 0.716 提升0.3个百分点。</t>
         </is>
       </c>
     </row>
@@ -27900,7 +28123,7 @@
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>（4）当前 run 未注册老户次新/流失户专属模型得分，无法复刻历史文档中的“分客群建模 KS”对比；本摘要仅比较本轮全客群模型与已注册的 G卡V5/G卡V6 历史版本。</t>
+          <t>（4）当前 run 未注册老户次新/流失户专属模型得分，无法复刻历史文档中的“分客群建模 KS”对比；本摘要仅比较G卡V7全客群模型与已注册的 G卡V5/G卡V6 历史版本。</t>
         </is>
       </c>
     </row>
@@ -27962,7 +28185,7 @@
       <c r="A11" s="6" t="inlineStr"/>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>本轮模型</t>
+          <t>G卡V7</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
@@ -27988,7 +28211,7 @@
       <c r="I11" s="6" t="inlineStr"/>
       <c r="J11" s="6" t="inlineStr">
         <is>
-          <t>本轮模型</t>
+          <t>G卡V7</t>
         </is>
       </c>
       <c r="K11" s="6" t="inlineStr">
@@ -28322,7 +28545,7 @@
       <c r="A22" s="6" t="inlineStr"/>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>本轮模型</t>
+          <t>G卡V7</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
@@ -28348,7 +28571,7 @@
       <c r="I22" s="6" t="inlineStr"/>
       <c r="J22" s="6" t="inlineStr">
         <is>
-          <t>本轮模型</t>
+          <t>G卡V7</t>
         </is>
       </c>
       <c r="K22" s="6" t="inlineStr">
@@ -28682,7 +28905,7 @@
       <c r="A33" s="6" t="inlineStr"/>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>本轮模型</t>
+          <t>G卡V7</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
@@ -28708,7 +28931,7 @@
       <c r="I33" s="6" t="inlineStr"/>
       <c r="J33" s="6" t="inlineStr">
         <is>
-          <t>本轮模型</t>
+          <t>G卡V7</t>
         </is>
       </c>
       <c r="K33" s="6" t="inlineStr">
@@ -28874,7 +29097,7 @@
       <c r="A40" s="6" t="inlineStr"/>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>本轮模型</t>
+          <t>G卡V7</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
@@ -28900,7 +29123,7 @@
       <c r="I40" s="6" t="inlineStr"/>
       <c r="J40" s="6" t="inlineStr">
         <is>
-          <t>本轮模型</t>
+          <t>G卡V7</t>
         </is>
       </c>
       <c r="K40" s="6" t="inlineStr">
@@ -29081,7 +29304,7 @@
       <c r="A49" s="6" t="inlineStr"/>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>本轮模型</t>
+          <t>G卡V7</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
@@ -29107,7 +29330,7 @@
       <c r="I49" s="6" t="inlineStr"/>
       <c r="J49" s="6" t="inlineStr">
         <is>
-          <t>本轮模型</t>
+          <t>G卡V7</t>
         </is>
       </c>
       <c r="K49" s="6" t="inlineStr">
@@ -29357,7 +29580,7 @@
       <c r="A58" s="6" t="inlineStr"/>
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t>本轮模型</t>
+          <t>G卡V7</t>
         </is>
       </c>
       <c r="C58" s="6" t="inlineStr">
@@ -29383,7 +29606,7 @@
       <c r="I58" s="6" t="inlineStr"/>
       <c r="J58" s="6" t="inlineStr">
         <is>
-          <t>本轮模型</t>
+          <t>G卡V7</t>
         </is>
       </c>
       <c r="K58" s="6" t="inlineStr">
@@ -29633,7 +29856,7 @@
       <c r="A67" s="6" t="inlineStr"/>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>本轮模型</t>
+          <t>G卡V7</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
@@ -29659,7 +29882,7 @@
       <c r="I67" s="6" t="inlineStr"/>
       <c r="J67" s="6" t="inlineStr">
         <is>
-          <t>本轮模型</t>
+          <t>G卡V7</t>
         </is>
       </c>
       <c r="K67" s="6" t="inlineStr">
@@ -29909,7 +30132,7 @@
       <c r="A76" s="6" t="inlineStr"/>
       <c r="B76" s="6" t="inlineStr">
         <is>
-          <t>本轮模型</t>
+          <t>G卡V7</t>
         </is>
       </c>
       <c r="C76" s="6" t="inlineStr">
@@ -29935,7 +30158,7 @@
       <c r="I76" s="6" t="inlineStr"/>
       <c r="J76" s="6" t="inlineStr">
         <is>
-          <t>本轮模型</t>
+          <t>G卡V7</t>
         </is>
       </c>
       <c r="K76" s="6" t="inlineStr">
@@ -30185,7 +30408,7 @@
       <c r="A85" s="6" t="inlineStr"/>
       <c r="B85" s="6" t="inlineStr">
         <is>
-          <t>本轮模型</t>
+          <t>G卡V7</t>
         </is>
       </c>
       <c r="C85" s="6" t="inlineStr">
@@ -30211,7 +30434,7 @@
       <c r="I85" s="6" t="inlineStr"/>
       <c r="J85" s="6" t="inlineStr">
         <is>
-          <t>本轮模型</t>
+          <t>G卡V7</t>
         </is>
       </c>
       <c r="K85" s="6" t="inlineStr">
@@ -31159,13 +31382,13 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="15.3" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
     <col width="16" customWidth="1" min="12" max="12"/>
@@ -31190,7 +31413,7 @@
     <row r="3">
       <c r="A3" s="17" t="inlineStr">
         <is>
-          <t>本轮模型</t>
+          <t>G卡V7</t>
         </is>
       </c>
       <c r="B3" s="5" t="n"/>
@@ -31277,8 +31500,10 @@
           <t>001</t>
         </is>
       </c>
-      <c r="B5" s="9" t="n">
-        <v>0.1000014293210929</v>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C5" s="9" t="n">
         <v>0.001143440530883104</v>
@@ -31297,8 +31522,10 @@
           <t>001</t>
         </is>
       </c>
-      <c r="I5" s="9" t="n">
-        <v>0.1000004085150885</v>
+      <c r="I5" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J5" s="9" t="n">
         <v>0.0009600065362147147</v>
@@ -31319,8 +31546,10 @@
           <t>002</t>
         </is>
       </c>
-      <c r="B6" s="9" t="n">
-        <v>0.09999938743381732</v>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C6" s="9" t="n">
         <v>0.001500781018693402</v>
@@ -31339,8 +31568,10 @@
           <t>002</t>
         </is>
       </c>
-      <c r="I6" s="9" t="n">
-        <v>0.1000004085150885</v>
+      <c r="I6" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J6" s="9" t="n">
         <v>0.00147064831079701</v>
@@ -31361,8 +31592,10 @@
           <t>003</t>
         </is>
       </c>
-      <c r="B7" s="9" t="n">
-        <v>0.09999938743381732</v>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C7" s="9" t="n">
         <v>0.002178011611524404</v>
@@ -31381,8 +31614,10 @@
           <t>003</t>
         </is>
       </c>
-      <c r="I7" s="9" t="n">
-        <v>0.1000004085150885</v>
+      <c r="I7" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J7" s="9" t="n">
         <v>0.002131078339256778</v>
@@ -31403,8 +31638,10 @@
           <t>004</t>
         </is>
       </c>
-      <c r="B8" s="9" t="n">
-        <v>0.09999938743381732</v>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C8" s="9" t="n">
         <v>0.003011786806331899</v>
@@ -31423,8 +31660,10 @@
           <t>004</t>
         </is>
       </c>
-      <c r="I8" s="9" t="n">
-        <v>0.09999836593964598</v>
+      <c r="I8" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J8" s="9" t="n">
         <v>0.003283443377197686</v>
@@ -31445,8 +31684,10 @@
           <t>005</t>
         </is>
       </c>
-      <c r="B9" s="9" t="n">
-        <v>0.1000014293210929</v>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C9" s="9" t="n">
         <v>0.004398216210918357</v>
@@ -31465,8 +31706,10 @@
           <t>005</t>
         </is>
       </c>
-      <c r="I9" s="9" t="n">
-        <v>0.1000004085150885</v>
+      <c r="I9" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J9" s="9" t="n">
         <v>0.005486357638619382</v>
@@ -31487,8 +31730,10 @@
           <t>006</t>
         </is>
       </c>
-      <c r="B10" s="9" t="n">
-        <v>0.09999938743381732</v>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C10" s="9" t="n">
         <v>0.007844244944630862</v>
@@ -31507,8 +31752,10 @@
           <t>006</t>
         </is>
       </c>
-      <c r="I10" s="9" t="n">
-        <v>0.1000004085150885</v>
+      <c r="I10" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J10" s="9" t="n">
         <v>0.01063159793972364</v>
@@ -31529,8 +31776,10 @@
           <t>007</t>
         </is>
       </c>
-      <c r="B11" s="9" t="n">
-        <v>0.09999938743381732</v>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C11" s="9" t="n">
         <v>0.01835657196196255</v>
@@ -31549,8 +31798,10 @@
           <t>007</t>
         </is>
       </c>
-      <c r="I11" s="9" t="n">
-        <v>0.1000004085150885</v>
+      <c r="I11" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J11" s="9" t="n">
         <v>0.02288557213930348</v>
@@ -31571,8 +31822,10 @@
           <t>008</t>
         </is>
       </c>
-      <c r="B12" s="9" t="n">
-        <v>0.09999938743381732</v>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C12" s="9" t="n">
         <v>0.04150650596997402</v>
@@ -31591,8 +31844,10 @@
           <t>008</t>
         </is>
       </c>
-      <c r="I12" s="9" t="n">
-        <v>0.09999836593964598</v>
+      <c r="I12" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J12" s="9" t="n">
         <v>0.04786525116043936</v>
@@ -31613,8 +31868,10 @@
           <t>009</t>
         </is>
       </c>
-      <c r="B13" s="9" t="n">
-        <v>0.09999938743381732</v>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C13" s="9" t="n">
         <v>0.08552344997821984</v>
@@ -31633,8 +31890,10 @@
           <t>009</t>
         </is>
       </c>
-      <c r="I13" s="9" t="n">
-        <v>0.1000004085150885</v>
+      <c r="I13" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J13" s="9" t="n">
         <v>0.09172075711497435</v>
@@ -31655,8 +31914,10 @@
           <t>010</t>
         </is>
       </c>
-      <c r="B14" s="9" t="n">
-        <v>0.1000014293210929</v>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C14" s="9" t="n">
         <v>0.1567332253855594</v>
@@ -31675,8 +31936,10 @@
           <t>010</t>
         </is>
       </c>
-      <c r="I14" s="9" t="n">
-        <v>0.1000004085150885</v>
+      <c r="I14" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J14" s="9" t="n">
         <v>0.1566205997818529</v>
@@ -31783,8 +32046,10 @@
           <t>001</t>
         </is>
       </c>
-      <c r="B19" s="9" t="n">
-        <v>0.1335051272731728</v>
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t>13.4%</t>
+        </is>
       </c>
       <c r="C19" s="9" t="n">
         <v>0.00541433422042764</v>
@@ -31803,8 +32068,10 @@
           <t>001</t>
         </is>
       </c>
-      <c r="I19" s="9" t="n">
-        <v>0.1010019540861227</v>
+      <c r="I19" s="9" t="inlineStr">
+        <is>
+          <t>10.1%</t>
+        </is>
       </c>
       <c r="J19" s="9" t="n">
         <v>0.000849085211765895</v>
@@ -31825,8 +32092,10 @@
           <t>002</t>
         </is>
       </c>
-      <c r="B20" s="9" t="n">
-        <v>0.06672806053898647</v>
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>6.7%</t>
+        </is>
       </c>
       <c r="C20" s="9" t="n">
         <v>0.006699911279713647</v>
@@ -31845,8 +32114,10 @@
           <t>002</t>
         </is>
       </c>
-      <c r="I20" s="9" t="n">
-        <v>0.09932556463287888</v>
+      <c r="I20" s="9" t="inlineStr">
+        <is>
+          <t>9.9%</t>
+        </is>
       </c>
       <c r="J20" s="9" t="n">
         <v>0.001396406038182022</v>
@@ -31867,8 +32138,10 @@
           <t>003</t>
         </is>
       </c>
-      <c r="B21" s="9" t="n">
-        <v>0.09979499075008065</v>
+      <c r="B21" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C21" s="9" t="n">
         <v>0.006370207031728531</v>
@@ -31887,8 +32160,10 @@
           <t>003</t>
         </is>
       </c>
-      <c r="I21" s="9" t="n">
-        <v>0.09967268546972596</v>
+      <c r="I21" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J21" s="9" t="n">
         <v>0.002021467026946088</v>
@@ -31909,8 +32184,10 @@
           <t>004</t>
         </is>
       </c>
-      <c r="B22" s="9" t="n">
-        <v>0.1002462561308792</v>
+      <c r="B22" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C22" s="9" t="n">
         <v>0.007050013263411349</v>
@@ -31929,8 +32206,10 @@
           <t>004</t>
         </is>
       </c>
-      <c r="I22" s="9" t="n">
-        <v>0.09999938743381732</v>
+      <c r="I22" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J22" s="9" t="n">
         <v>0.003149614338147087</v>
@@ -31951,8 +32230,10 @@
           <t>005</t>
         </is>
       </c>
-      <c r="B23" s="9" t="n">
-        <v>0.09984808079488049</v>
+      <c r="B23" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C23" s="9" t="n">
         <v>0.007757413433390357</v>
@@ -31971,8 +32252,10 @@
           <t>005</t>
         </is>
       </c>
-      <c r="I23" s="9" t="n">
-        <v>0.1000014293210929</v>
+      <c r="I23" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J23" s="9" t="n">
         <v>0.005447744127544186</v>
@@ -31993,8 +32276,10 @@
           <t>006</t>
         </is>
       </c>
-      <c r="B24" s="9" t="n">
-        <v>0.0998766677420804</v>
+      <c r="B24" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C24" s="9" t="n">
         <v>0.01292880479172339</v>
@@ -32013,8 +32298,10 @@
           <t>006</t>
         </is>
       </c>
-      <c r="I24" s="9" t="n">
-        <v>0.09999938743381732</v>
+      <c r="I24" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J24" s="9" t="n">
         <v>0.01130864466421187</v>
@@ -32035,8 +32322,10 @@
           <t>007</t>
         </is>
       </c>
-      <c r="B25" s="9" t="n">
-        <v>0.10000122515488</v>
+      <c r="B25" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C25" s="9" t="n">
         <v>0.02473644600278868</v>
@@ -32055,8 +32344,10 @@
           <t>007</t>
         </is>
       </c>
-      <c r="I25" s="9" t="n">
-        <v>0.09999938743381732</v>
+      <c r="I25" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J25" s="9" t="n">
         <v>0.02362464266962254</v>
@@ -32077,8 +32368,10 @@
           <t>008</t>
         </is>
       </c>
-      <c r="B26" s="9" t="n">
-        <v>0.09999918323008</v>
+      <c r="B26" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C26" s="9" t="n">
         <v>0.04778616952578825</v>
@@ -32097,8 +32390,10 @@
           <t>008</t>
         </is>
       </c>
-      <c r="I26" s="9" t="n">
-        <v>0.09999938743381732</v>
+      <c r="I26" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J26" s="9" t="n">
         <v>0.04919932413462177</v>
@@ -32119,8 +32414,10 @@
           <t>009</t>
         </is>
       </c>
-      <c r="B27" s="9" t="n">
-        <v>0.09999918323008</v>
+      <c r="B27" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C27" s="9" t="n">
         <v>0.08969960976495145</v>
@@ -32139,8 +32436,10 @@
           <t>009</t>
         </is>
       </c>
-      <c r="I27" s="9" t="n">
-        <v>0.09999938743381732</v>
+      <c r="I27" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J27" s="9" t="n">
         <v>0.09280619282706548</v>
@@ -32161,8 +32460,10 @@
           <t>010</t>
         </is>
       </c>
-      <c r="B28" s="9" t="n">
-        <v>0.10000122515488</v>
+      <c r="B28" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C28" s="9" t="n">
         <v>0.1567361057226984</v>
@@ -32181,8 +32482,10 @@
           <t>010</t>
         </is>
       </c>
-      <c r="I28" s="9" t="n">
-        <v>0.1000014293210929</v>
+      <c r="I28" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J28" s="9" t="n">
         <v>0.1567332253855594</v>
@@ -32249,8 +32552,10 @@
           <t>001</t>
         </is>
       </c>
-      <c r="B33" s="9" t="n">
-        <v>0.1000014293210929</v>
+      <c r="B33" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C33" s="9" t="n">
         <v>0.0007146503318019398</v>
@@ -32271,8 +32576,10 @@
           <t>002</t>
         </is>
       </c>
-      <c r="B34" s="9" t="n">
-        <v>0.09999938743381732</v>
+      <c r="B34" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C34" s="9" t="n">
         <v>0.001143452204718782</v>
@@ -32293,8 +32600,10 @@
           <t>003</t>
         </is>
       </c>
-      <c r="B35" s="9" t="n">
-        <v>0.09999938743381732</v>
+      <c r="B35" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C35" s="9" t="n">
         <v>0.001912566446369867</v>
@@ -32315,8 +32624,10 @@
           <t>004</t>
         </is>
       </c>
-      <c r="B36" s="9" t="n">
-        <v>0.09999938743381732</v>
+      <c r="B36" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C36" s="9" t="n">
         <v>0.002863749827715585</v>
@@ -32337,8 +32648,10 @@
           <t>005</t>
         </is>
       </c>
-      <c r="B37" s="9" t="n">
-        <v>0.1000014293210929</v>
+      <c r="B37" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C37" s="9" t="n">
         <v>0.004630990885033813</v>
@@ -32359,8 +32672,10 @@
           <t>006</t>
         </is>
       </c>
-      <c r="B38" s="9" t="n">
-        <v>0.09999938743381732</v>
+      <c r="B38" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C38" s="9" t="n">
         <v>0.008698433873525589</v>
@@ -32381,8 +32696,10 @@
           <t>007</t>
         </is>
       </c>
-      <c r="B39" s="9" t="n">
-        <v>0.09999938743381732</v>
+      <c r="B39" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C39" s="9" t="n">
         <v>0.01999883320693075</v>
@@ -32403,8 +32720,10 @@
           <t>008</t>
         </is>
       </c>
-      <c r="B40" s="9" t="n">
-        <v>0.09999938743381732</v>
+      <c r="B40" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C40" s="9" t="n">
         <v>0.04469185337192504</v>
@@ -32425,8 +32744,10 @@
           <t>009</t>
         </is>
       </c>
-      <c r="B41" s="9" t="n">
-        <v>0.09999938743381732</v>
+      <c r="B41" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C41" s="9" t="n">
         <v>0.0883344525918397</v>
@@ -32447,8 +32768,10 @@
           <t>010</t>
         </is>
       </c>
-      <c r="B42" s="9" t="n">
-        <v>0.1000014293210929</v>
+      <c r="B42" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C42" s="9" t="n">
         <v>0.1567332253855594</v>
@@ -32484,7 +32807,7 @@
     <row r="48">
       <c r="A48" s="17" t="inlineStr">
         <is>
-          <t>本轮模型</t>
+          <t>G卡V7</t>
         </is>
       </c>
       <c r="B48" s="5" t="n"/>
@@ -32571,8 +32894,10 @@
           <t>001</t>
         </is>
       </c>
-      <c r="B50" s="9" t="n">
-        <v>0.1000012304814874</v>
+      <c r="B50" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C50" s="9" t="n">
         <v>0.06053894425987449</v>
@@ -32591,8 +32916,10 @@
           <t>001</t>
         </is>
       </c>
-      <c r="I50" s="9" t="n">
-        <v>0.1000049266544321</v>
+      <c r="I50" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J50" s="9" t="n">
         <v>0.08892173163372129</v>
@@ -32613,8 +32940,10 @@
           <t>002</t>
         </is>
       </c>
-      <c r="B51" s="9" t="n">
-        <v>0.1000012304814874</v>
+      <c r="B51" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C51" s="9" t="n">
         <v>0.08767072720561092</v>
@@ -32633,8 +32962,10 @@
           <t>002</t>
         </is>
       </c>
-      <c r="I51" s="9" t="n">
-        <v>0.09999876833639196</v>
+      <c r="I51" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J51" s="9" t="n">
         <v>0.1166363888290175</v>
@@ -32655,8 +32986,10 @@
           <t>003</t>
         </is>
       </c>
-      <c r="B52" s="9" t="n">
-        <v>0.1000012304814874</v>
+      <c r="B52" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C52" s="9" t="n">
         <v>0.1149050490135761</v>
@@ -32675,8 +33008,10 @@
           <t>003</t>
         </is>
       </c>
-      <c r="I52" s="9" t="n">
-        <v>0.09999876833639196</v>
+      <c r="I52" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J52" s="9" t="n">
         <v>0.1446987580827261</v>
@@ -32697,8 +33032,10 @@
           <t>004</t>
         </is>
       </c>
-      <c r="B53" s="9" t="n">
-        <v>0.09999507807405038</v>
+      <c r="B53" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C53" s="9" t="n">
         <v>0.145704837345228</v>
@@ -32717,8 +33054,10 @@
           <t>004</t>
         </is>
       </c>
-      <c r="I53" s="9" t="n">
-        <v>0.09999876833639196</v>
+      <c r="I53" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J53" s="9" t="n">
         <v>0.1751574215201761</v>
@@ -32739,8 +33078,10 @@
           <t>005</t>
         </is>
       </c>
-      <c r="B54" s="9" t="n">
-        <v>0.1000012304814874</v>
+      <c r="B54" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C54" s="9" t="n">
         <v>0.1795149441976645</v>
@@ -32759,8 +33100,10 @@
           <t>005</t>
         </is>
       </c>
-      <c r="I54" s="9" t="n">
-        <v>0.09999876833639196</v>
+      <c r="I54" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J54" s="9" t="n">
         <v>0.2097892623566651</v>
@@ -32781,8 +33124,10 @@
           <t>006</t>
         </is>
       </c>
-      <c r="B55" s="9" t="n">
-        <v>0.1000012304814874</v>
+      <c r="B55" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C55" s="9" t="n">
         <v>0.2197225269936323</v>
@@ -32801,8 +33146,10 @@
           <t>006</t>
         </is>
       </c>
-      <c r="I55" s="9" t="n">
-        <v>0.09999876833639196</v>
+      <c r="I55" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J55" s="9" t="n">
         <v>0.247339087951226</v>
@@ -32823,8 +33170,10 @@
           <t>007</t>
         </is>
       </c>
-      <c r="B56" s="9" t="n">
-        <v>0.09999507807405038</v>
+      <c r="B56" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C56" s="9" t="n">
         <v>0.2647658557164956</v>
@@ -32843,8 +33192,10 @@
           <t>007</t>
         </is>
       </c>
-      <c r="I56" s="9" t="n">
-        <v>0.09999876833639196</v>
+      <c r="I56" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J56" s="9" t="n">
         <v>0.2875944645323621</v>
@@ -32865,8 +33216,10 @@
           <t>008</t>
         </is>
       </c>
-      <c r="B57" s="9" t="n">
-        <v>0.1000012304814874</v>
+      <c r="B57" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C57" s="9" t="n">
         <v>0.3143274628931785</v>
@@ -32885,8 +33238,10 @@
           <t>008</t>
         </is>
       </c>
-      <c r="I57" s="9" t="n">
-        <v>0.09999876833639196</v>
+      <c r="I57" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J57" s="9" t="n">
         <v>0.3294946306916593</v>
@@ -32907,8 +33262,10 @@
           <t>009</t>
         </is>
       </c>
-      <c r="B58" s="9" t="n">
-        <v>0.1000012304814874</v>
+      <c r="B58" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C58" s="9" t="n">
         <v>0.3675111427087036</v>
@@ -32927,8 +33284,10 @@
           <t>009</t>
         </is>
       </c>
-      <c r="I58" s="9" t="n">
-        <v>0.09999876833639196</v>
+      <c r="I58" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J58" s="9" t="n">
         <v>0.3741951376391616</v>
@@ -32949,8 +33308,10 @@
           <t>010</t>
         </is>
       </c>
-      <c r="B59" s="9" t="n">
-        <v>0.1000012304814874</v>
+      <c r="B59" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C59" s="9" t="n">
         <v>0.4240362253749893</v>
@@ -32969,8 +33330,10 @@
           <t>010</t>
         </is>
       </c>
-      <c r="I59" s="9" t="n">
-        <v>0.1000049266544321</v>
+      <c r="I59" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J59" s="9" t="n">
         <v>0.4239447722038157</v>
@@ -33077,8 +33440,10 @@
           <t>001</t>
         </is>
       </c>
-      <c r="B64" s="9" t="n">
-        <v>0.1000012304814874</v>
+      <c r="B64" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C64" s="9" t="n">
         <v>0.1040974529346622</v>
@@ -33097,8 +33462,10 @@
           <t>001</t>
         </is>
       </c>
-      <c r="I64" s="9" t="n">
-        <v>0.1000012304814874</v>
+      <c r="I64" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J64" s="9" t="n">
         <v>0.09326934908330257</v>
@@ -33119,8 +33486,10 @@
           <t>002</t>
         </is>
       </c>
-      <c r="B65" s="9" t="n">
-        <v>0.1000012304814874</v>
+      <c r="B65" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C65" s="9" t="n">
         <v>0.1237233911652516</v>
@@ -33139,8 +33508,10 @@
           <t>002</t>
         </is>
       </c>
-      <c r="I65" s="9" t="n">
-        <v>0.1000012304814874</v>
+      <c r="I65" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J65" s="9" t="n">
         <v>0.1230773963332103</v>
@@ -33161,8 +33532,10 @@
           <t>003</t>
         </is>
       </c>
-      <c r="B66" s="9" t="n">
-        <v>0.1000012304814874</v>
+      <c r="B66" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C66" s="9" t="n">
         <v>0.1465280341249333</v>
@@ -33181,8 +33554,10 @@
           <t>003</t>
         </is>
       </c>
-      <c r="I66" s="9" t="n">
-        <v>0.1000012304814874</v>
+      <c r="I66" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J66" s="9" t="n">
         <v>0.1526598580862147</v>
@@ -33203,8 +33578,10 @@
           <t>004</t>
         </is>
       </c>
-      <c r="B67" s="9" t="n">
-        <v>0.09999507807405038</v>
+      <c r="B67" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C67" s="9" t="n">
         <v>0.1744059063293086</v>
@@ -33223,8 +33600,10 @@
           <t>004</t>
         </is>
       </c>
-      <c r="I67" s="9" t="n">
-        <v>0.09999507807405038</v>
+      <c r="I67" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J67" s="9" t="n">
         <v>0.1835884026763055</v>
@@ -33245,8 +33624,10 @@
           <t>005</t>
         </is>
       </c>
-      <c r="B68" s="9" t="n">
-        <v>0.1000012304814874</v>
+      <c r="B68" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C68" s="9" t="n">
         <v>0.2041614883904072</v>
@@ -33265,8 +33646,10 @@
           <t>005</t>
         </is>
       </c>
-      <c r="I68" s="9" t="n">
-        <v>0.1000012304814874</v>
+      <c r="I68" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J68" s="9" t="n">
         <v>0.2171676777122888</v>
@@ -33287,8 +33670,10 @@
           <t>006</t>
         </is>
       </c>
-      <c r="B69" s="9" t="n">
-        <v>0.1000012304814874</v>
+      <c r="B69" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C69" s="9" t="n">
         <v>0.2397383181403361</v>
@@ -33307,8 +33692,10 @@
           <t>006</t>
         </is>
       </c>
-      <c r="I69" s="9" t="n">
-        <v>0.1000012304814874</v>
+      <c r="I69" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J69" s="9" t="n">
         <v>0.2531813008213447</v>
@@ -33329,8 +33716,10 @@
           <t>007</t>
         </is>
       </c>
-      <c r="B70" s="9" t="n">
-        <v>0.09999507807405038</v>
+      <c r="B70" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C70" s="9" t="n">
         <v>0.2798920686260723</v>
@@ -33349,8 +33738,10 @@
           <t>007</t>
         </is>
       </c>
-      <c r="I70" s="9" t="n">
-        <v>0.09999507807405038</v>
+      <c r="I70" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J70" s="9" t="n">
         <v>0.2920211643931936</v>
@@ -33371,8 +33762,10 @@
           <t>008</t>
         </is>
       </c>
-      <c r="B71" s="9" t="n">
-        <v>0.1000012304814874</v>
+      <c r="B71" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C71" s="9" t="n">
         <v>0.3237483657617473</v>
@@ -33391,8 +33784,10 @@
           <t>008</t>
         </is>
       </c>
-      <c r="I71" s="9" t="n">
-        <v>0.1000012304814874</v>
+      <c r="I71" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J71" s="9" t="n">
         <v>0.3341998000461432</v>
@@ -33413,8 +33808,10 @@
           <t>009</t>
         </is>
       </c>
-      <c r="B72" s="9" t="n">
-        <v>0.1000012304814874</v>
+      <c r="B72" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C72" s="9" t="n">
         <v>0.372125454595171</v>
@@ -33433,8 +33830,10 @@
           <t>009</t>
         </is>
       </c>
-      <c r="I72" s="9" t="n">
-        <v>0.1000012304814874</v>
+      <c r="I72" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J72" s="9" t="n">
         <v>0.3770884033797271</v>
@@ -33455,8 +33854,10 @@
           <t>010</t>
         </is>
       </c>
-      <c r="B73" s="9" t="n">
-        <v>0.1000012304814874</v>
+      <c r="B73" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C73" s="9" t="n">
         <v>0.4240362253749893</v>
@@ -33475,8 +33876,10 @@
           <t>010</t>
         </is>
       </c>
-      <c r="I73" s="9" t="n">
-        <v>0.1000012304814874</v>
+      <c r="I73" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J73" s="9" t="n">
         <v>0.4240362253749893</v>
@@ -33543,8 +33946,10 @@
           <t>001</t>
         </is>
       </c>
-      <c r="B78" s="9" t="n">
-        <v>0.1000012304814874</v>
+      <c r="B78" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C78" s="9" t="n">
         <v>0.06921373200442968</v>
@@ -33565,8 +33970,10 @@
           <t>002</t>
         </is>
       </c>
-      <c r="B79" s="9" t="n">
-        <v>0.1000012304814874</v>
+      <c r="B79" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C79" s="9" t="n">
         <v>0.09972929740371601</v>
@@ -33587,8 +33994,10 @@
           <t>003</t>
         </is>
       </c>
-      <c r="B80" s="9" t="n">
-        <v>0.1000012304814874</v>
+      <c r="B80" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C80" s="9" t="n">
         <v>0.128583733234896</v>
@@ -33609,8 +34018,10 @@
           <t>004</t>
         </is>
       </c>
-      <c r="B81" s="9" t="n">
-        <v>0.09999507807405038</v>
+      <c r="B81" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C81" s="9" t="n">
         <v>0.160562947012228</v>
@@ -33631,8 +34042,10 @@
           <t>005</t>
         </is>
       </c>
-      <c r="B82" s="9" t="n">
-        <v>0.1000012304814874</v>
+      <c r="B82" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C82" s="9" t="n">
         <v>0.1948713531604917</v>
@@ -33653,8 +34066,10 @@
           <t>006</t>
         </is>
       </c>
-      <c r="B83" s="9" t="n">
-        <v>0.1000012304814874</v>
+      <c r="B83" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C83" s="9" t="n">
         <v>0.2336474472688494</v>
@@ -33675,8 +34090,10 @@
           <t>007</t>
         </is>
       </c>
-      <c r="B84" s="9" t="n">
-        <v>0.09999507807405038</v>
+      <c r="B84" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C84" s="9" t="n">
         <v>0.2751459007171987</v>
@@ -33697,8 +34114,10 @@
           <t>008</t>
         </is>
       </c>
-      <c r="B85" s="9" t="n">
-        <v>0.1000012304814874</v>
+      <c r="B85" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C85" s="9" t="n">
         <v>0.320995154964239</v>
@@ -33719,8 +34138,10 @@
           <t>009</t>
         </is>
       </c>
-      <c r="B86" s="9" t="n">
-        <v>0.1000012304814874</v>
+      <c r="B86" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C86" s="9" t="n">
         <v>0.3703549260342895</v>
@@ -33741,8 +34162,10 @@
           <t>010</t>
         </is>
       </c>
-      <c r="B87" s="9" t="n">
-        <v>0.1000012304814874</v>
+      <c r="B87" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C87" s="9" t="n">
         <v>0.4240362253749893</v>
@@ -33778,7 +34201,7 @@
     <row r="93">
       <c r="A93" s="17" t="inlineStr">
         <is>
-          <t>本轮模型</t>
+          <t>G卡V7</t>
         </is>
       </c>
       <c r="B93" s="5" t="n"/>
@@ -33865,8 +34288,10 @@
           <t>001</t>
         </is>
       </c>
-      <c r="B95" s="9" t="n">
-        <v>0.1000015280940083</v>
+      <c r="B95" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C95" s="9" t="n">
         <v>0.0006112282631948902</v>
@@ -33885,8 +34310,10 @@
           <t>001</t>
         </is>
       </c>
-      <c r="I95" s="9" t="n">
-        <v>0.1000012225088326</v>
+      <c r="I95" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J95" s="9" t="n">
         <v>0.0007334963325183374</v>
@@ -33907,8 +34334,10 @@
           <t>002</t>
         </is>
       </c>
-      <c r="B96" s="9" t="n">
-        <v>0.09999847190599166</v>
+      <c r="B96" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C96" s="9" t="n">
         <v>0.001253037086841583</v>
@@ -33927,8 +34356,10 @@
           <t>002</t>
         </is>
       </c>
-      <c r="I96" s="9" t="n">
-        <v>0.1000012225088326</v>
+      <c r="I96" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J96" s="9" t="n">
         <v>0.001115525672371638</v>
@@ -33949,8 +34380,10 @@
           <t>003</t>
         </is>
       </c>
-      <c r="B97" s="9" t="n">
-        <v>0.1000015280940083</v>
+      <c r="B97" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C97" s="9" t="n">
         <v>0.001497524500315804</v>
@@ -33969,8 +34402,10 @@
           <t>003</t>
         </is>
       </c>
-      <c r="I97" s="9" t="n">
-        <v>0.09999816623675106</v>
+      <c r="I97" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J97" s="9" t="n">
         <v>0.001467007610101977</v>
@@ -33991,8 +34426,10 @@
           <t>004</t>
         </is>
       </c>
-      <c r="B98" s="9" t="n">
-        <v>0.09999847190599166</v>
+      <c r="B98" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C98" s="9" t="n">
         <v>0.001933038920554392</v>
@@ -34011,8 +34448,10 @@
           <t>004</t>
         </is>
       </c>
-      <c r="I98" s="9" t="n">
-        <v>0.1000012225088326</v>
+      <c r="I98" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J98" s="9" t="n">
         <v>0.001871958068139274</v>
@@ -34033,8 +34472,10 @@
           <t>005</t>
         </is>
       </c>
-      <c r="B99" s="9" t="n">
-        <v>0.1000015280940083</v>
+      <c r="B99" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C99" s="9" t="n">
         <v>0.002451055298496971</v>
@@ -34053,8 +34494,10 @@
           <t>005</t>
         </is>
       </c>
-      <c r="I99" s="9" t="n">
-        <v>0.09999816623675106</v>
+      <c r="I99" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J99" s="9" t="n">
         <v>0.002506143106883947</v>
@@ -34075,8 +34518,10 @@
           <t>006</t>
         </is>
       </c>
-      <c r="B100" s="9" t="n">
-        <v>0.09999847190599166</v>
+      <c r="B100" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C100" s="9" t="n">
         <v>0.003020532489825441</v>
@@ -34095,8 +34540,10 @@
           <t>006</t>
         </is>
       </c>
-      <c r="I100" s="9" t="n">
-        <v>0.1000012225088326</v>
+      <c r="I100" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J100" s="9" t="n">
         <v>0.003285485793457553</v>
@@ -34117,8 +34564,10 @@
           <t>007</t>
         </is>
       </c>
-      <c r="B101" s="9" t="n">
-        <v>0.09999847190599166</v>
+      <c r="B101" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C101" s="9" t="n">
         <v>0.003903197216243238</v>
@@ -34137,8 +34586,10 @@
           <t>007</t>
         </is>
       </c>
-      <c r="I101" s="9" t="n">
-        <v>0.09999816623675106</v>
+      <c r="I101" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J101" s="9" t="n">
         <v>0.004601876552696726</v>
@@ -34159,8 +34610,10 @@
           <t>008</t>
         </is>
       </c>
-      <c r="B102" s="9" t="n">
-        <v>0.1000015280940083</v>
+      <c r="B102" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C102" s="9" t="n">
         <v>0.005252823153680414</v>
@@ -34179,8 +34632,10 @@
           <t>008</t>
         </is>
       </c>
-      <c r="I102" s="9" t="n">
-        <v>0.1000012225088326</v>
+      <c r="I102" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J102" s="9" t="n">
         <v>0.006655027372715916</v>
@@ -34201,8 +34656,10 @@
           <t>009</t>
         </is>
       </c>
-      <c r="B103" s="9" t="n">
-        <v>0.09999847190599166</v>
+      <c r="B103" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C103" s="9" t="n">
         <v>0.008064954292932722</v>
@@ -34221,8 +34678,10 @@
           <t>009</t>
         </is>
       </c>
-      <c r="I103" s="9" t="n">
-        <v>0.09999816623675106</v>
+      <c r="I103" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J103" s="9" t="n">
         <v>0.01023512951819503</v>
@@ -34243,8 +34702,10 @@
           <t>010</t>
         </is>
       </c>
-      <c r="B104" s="9" t="n">
-        <v>0.1000015280940083</v>
+      <c r="B104" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C104" s="9" t="n">
         <v>0.02395134548677435</v>
@@ -34263,8 +34724,10 @@
           <t>010</t>
         </is>
       </c>
-      <c r="I104" s="9" t="n">
-        <v>0.1000012225088326</v>
+      <c r="I104" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J104" s="9" t="n">
         <v>0.02395200430323109</v>
@@ -34371,8 +34834,10 @@
           <t>001</t>
         </is>
       </c>
-      <c r="B109" s="9" t="n">
-        <v>0.1996845927211824</v>
+      <c r="B109" s="9" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
       </c>
       <c r="C109" s="9" t="n">
         <v>0.005418146198114363</v>
@@ -34391,8 +34856,10 @@
           <t>001</t>
         </is>
       </c>
-      <c r="I109" s="9" t="n">
-        <v>0.1042251799330695</v>
+      <c r="I109" s="9" t="inlineStr">
+        <is>
+          <t>10.4%</t>
+        </is>
       </c>
       <c r="J109" s="9" t="n">
         <v>0.0006157816027915433</v>
@@ -34413,8 +34880,10 @@
           <t>002</t>
         </is>
       </c>
-      <c r="B110" s="9" t="n">
-        <v>0.0003300773848091052</v>
+      <c r="B110" s="9" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
       </c>
       <c r="C110" s="9" t="n">
         <v>0.005424485055925677</v>
@@ -34433,8 +34902,10 @@
           <t>002</t>
         </is>
       </c>
-      <c r="I110" s="9" t="n">
-        <v>0.09579315719503063</v>
+      <c r="I110" s="9" t="inlineStr">
+        <is>
+          <t>9.6%</t>
+        </is>
       </c>
       <c r="J110" s="9" t="n">
         <v>0.001054288202667807</v>
@@ -34455,8 +34926,10 @@
           <t>003</t>
         </is>
       </c>
-      <c r="B111" s="9" t="n">
-        <v>0.1000042787809142</v>
+      <c r="B111" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C111" s="9" t="n">
         <v>0.006703000050934651</v>
@@ -34475,8 +34948,10 @@
           <t>003</t>
         </is>
       </c>
-      <c r="I111" s="9" t="n">
-        <v>0.09998624715392491</v>
+      <c r="I111" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J111" s="9" t="n">
         <v>0.001395637867628332</v>
@@ -34497,8 +34972,10 @@
           <t>004</t>
         </is>
       </c>
-      <c r="B112" s="9" t="n">
-        <v>0.1037420995366692</v>
+      <c r="B112" s="9" t="inlineStr">
+        <is>
+          <t>10.4%</t>
+        </is>
       </c>
       <c r="C112" s="9" t="n">
         <v>0.006161578696379504</v>
@@ -34517,8 +34994,10 @@
           <t>004</t>
         </is>
       </c>
-      <c r="I112" s="9" t="n">
-        <v>0.09999541571797498</v>
+      <c r="I112" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J112" s="9" t="n">
         <v>0.001764948579636619</v>
@@ -34539,8 +35018,10 @@
           <t>005</t>
         </is>
       </c>
-      <c r="B113" s="9" t="n">
-        <v>0.09805132092079365</v>
+      <c r="B113" s="9" t="inlineStr">
+        <is>
+          <t>9.8%</t>
+        </is>
       </c>
       <c r="C113" s="9" t="n">
         <v>0.006790871606848122</v>
@@ -34559,8 +35040,10 @@
           <t>005</t>
         </is>
       </c>
-      <c r="I113" s="9" t="n">
-        <v>0.1000015280940083</v>
+      <c r="I113" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J113" s="9" t="n">
         <v>0.002432718226438391</v>
@@ -34581,8 +35064,10 @@
           <t>006</t>
         </is>
       </c>
-      <c r="B114" s="9" t="n">
-        <v>0.09818885316446412</v>
+      <c r="B114" s="9" t="inlineStr">
+        <is>
+          <t>9.8%</t>
+        </is>
       </c>
       <c r="C114" s="9" t="n">
         <v>0.007095630558583523</v>
@@ -34601,8 +35086,10 @@
           <t>006</t>
         </is>
       </c>
-      <c r="I114" s="9" t="n">
-        <v>0.09999847190599166</v>
+      <c r="I114" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J114" s="9" t="n">
         <v>0.003071468956770221</v>
@@ -34623,8 +35110,10 @@
           <t>007</t>
         </is>
       </c>
-      <c r="B115" s="9" t="n">
-        <v>0.1000073350529958</v>
+      <c r="B115" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C115" s="9" t="n">
         <v>0.007326231225986727</v>
@@ -34643,8 +35132,10 @@
           <t>007</t>
         </is>
       </c>
-      <c r="I115" s="9" t="n">
-        <v>0.09999847190599166</v>
+      <c r="I115" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J115" s="9" t="n">
         <v>0.004191352715428981</v>
@@ -34665,8 +35156,10 @@
           <t>008</t>
         </is>
       </c>
-      <c r="B116" s="9" t="n">
-        <v>0.1002365554591132</v>
+      <c r="B116" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C116" s="9" t="n">
         <v>0.008215034544392121</v>
@@ -34685,8 +35178,10 @@
           <t>008</t>
         </is>
       </c>
-      <c r="I116" s="9" t="n">
-        <v>0.1000015280940083</v>
+      <c r="I116" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J116" s="9" t="n">
         <v>0.006200241438853318</v>
@@ -34707,8 +35202,10 @@
           <t>009</t>
         </is>
       </c>
-      <c r="B117" s="9" t="n">
-        <v>0.09975366447022579</v>
+      <c r="B117" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C117" s="9" t="n">
         <v>0.01326423885138347</v>
@@ -34727,8 +35224,10 @@
           <t>009</t>
         </is>
       </c>
-      <c r="I117" s="9" t="n">
-        <v>0.09999847190599166</v>
+      <c r="I117" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J117" s="9" t="n">
         <v>0.009800192879748985</v>
@@ -34749,8 +35248,10 @@
           <t>010</t>
         </is>
       </c>
-      <c r="B118" s="9" t="n">
-        <v>0.1000012225088326</v>
+      <c r="B118" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C118" s="9" t="n">
         <v>0.02395200430323109</v>
@@ -34769,8 +35270,10 @@
           <t>010</t>
         </is>
       </c>
-      <c r="I118" s="9" t="n">
-        <v>0.1000015280940083</v>
+      <c r="I118" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="J118" s="9" t="n">
         <v>0.02395134548677435</v>
@@ -34837,8 +35340,10 @@
           <t>001</t>
         </is>
       </c>
-      <c r="B123" s="9" t="n">
-        <v>0.1000015280940083</v>
+      <c r="B123" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C123" s="9" t="n">
         <v>0.0006417896763546347</v>
@@ -34859,8 +35364,10 @@
           <t>002</t>
         </is>
       </c>
-      <c r="B124" s="9" t="n">
-        <v>0.09999847190599166</v>
+      <c r="B124" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C124" s="9" t="n">
         <v>0.0008557326446723002</v>
@@ -34881,8 +35388,10 @@
           <t>003</t>
         </is>
       </c>
-      <c r="B125" s="9" t="n">
-        <v>0.1000015280940083</v>
+      <c r="B125" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C125" s="9" t="n">
         <v>0.001151158289358407</v>
@@ -34903,8 +35412,10 @@
           <t>004</t>
         </is>
       </c>
-      <c r="B126" s="9" t="n">
-        <v>0.09999847190599166</v>
+      <c r="B126" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C126" s="9" t="n">
         <v>0.001596858238718846</v>
@@ -34925,8 +35436,10 @@
           <t>005</t>
         </is>
       </c>
-      <c r="B127" s="9" t="n">
-        <v>0.1000015280940083</v>
+      <c r="B127" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C127" s="9" t="n">
         <v>0.002182111574971119</v>
@@ -34947,8 +35460,10 @@
           <t>006</t>
         </is>
       </c>
-      <c r="B128" s="9" t="n">
-        <v>0.09999847190599166</v>
+      <c r="B128" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C128" s="9" t="n">
         <v>0.002888097675769013</v>
@@ -34969,8 +35484,10 @@
           <t>007</t>
         </is>
       </c>
-      <c r="B129" s="9" t="n">
-        <v>0.09999847190599166</v>
+      <c r="B129" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C129" s="9" t="n">
         <v>0.003942491147950385</v>
@@ -34991,8 +35508,10 @@
           <t>008</t>
         </is>
       </c>
-      <c r="B130" s="9" t="n">
-        <v>0.1000015280940083</v>
+      <c r="B130" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C130" s="9" t="n">
         <v>0.005573722895432527</v>
@@ -35013,8 +35532,10 @@
           <t>009</t>
         </is>
       </c>
-      <c r="B131" s="9" t="n">
-        <v>0.09999847190599166</v>
+      <c r="B131" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C131" s="9" t="n">
         <v>0.008845981445511471</v>
@@ -35035,8 +35556,10 @@
           <t>010</t>
         </is>
       </c>
-      <c r="B132" s="9" t="n">
-        <v>0.1000015280940083</v>
+      <c r="B132" s="9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
       </c>
       <c r="C132" s="9" t="n">
         <v>0.02395134548677435</v>
@@ -35084,822 +35607,1237 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I41"/>
+  <dimension ref="A1:I57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="15.3" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
-    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="13" t="inlineStr">
-        <is>
-          <t>当前意愿资产交叉 artifact 缺少老户/流失户、score version、final_flag 和金额风险 x 资产评级维度；下方仅展示当前可用的全量观察口径，待补口径见 missing 文档。</t>
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>3、意愿交叉风险（DEV-OOS）</t>
         </is>
       </c>
       <c r="B1" s="5" t="n"/>
-      <c r="C1" s="5" t="n"/>
-      <c r="D1" s="5" t="n"/>
-      <c r="E1" s="5" t="n"/>
-      <c r="F1" s="5" t="n"/>
-      <c r="G1" s="5" t="n"/>
-      <c r="H1" s="5" t="n"/>
-    </row>
-    <row r="2"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>序号</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>结论</t>
+        </is>
+      </c>
+    </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>当前可用全量观察：占比（意愿评级 x 资产评级）</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="n"/>
-      <c r="C3" s="5" t="n"/>
-      <c r="D3" s="5" t="n"/>
-      <c r="E3" s="5" t="n"/>
-      <c r="F3" s="5" t="n"/>
-      <c r="G3" s="5" t="n"/>
-      <c r="H3" s="5" t="n"/>
-      <c r="I3" s="5" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A3" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>（1）高、中、低意愿评级为对应模型分数在各客群内三等频分箱得到。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4"/>
+    <row r="5"/>
+    <row r="6">
+      <c r="A6" s="13" t="inlineStr">
+        <is>
+          <t>以下矩阵均限定 DEV-OOS；意愿评级按对应客群、对应分数版本等频三等分，资产评级为 zc_level 1-7，并保留行列合计。</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n"/>
+      <c r="C6" s="5" t="n"/>
+      <c r="D6" s="5" t="n"/>
+      <c r="E6" s="5" t="n"/>
+      <c r="F6" s="5" t="n"/>
+      <c r="G6" s="5" t="n"/>
+      <c r="H6" s="5" t="n"/>
+    </row>
+    <row r="7"/>
+    <row r="8">
+      <c r="A8" s="13" t="inlineStr">
+        <is>
+          <t>老户 DEV-OOS 意愿 x 资产评级</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n"/>
+      <c r="C8" s="5" t="n"/>
+      <c r="D8" s="5" t="n"/>
+      <c r="E8" s="5" t="n"/>
+      <c r="F8" s="5" t="n"/>
+      <c r="G8" s="5" t="n"/>
+      <c r="H8" s="5" t="n"/>
+    </row>
+    <row r="9"/>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>老户 - 占比 - G卡V7</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n"/>
+      <c r="C10" s="5" t="n"/>
+      <c r="D10" s="5" t="n"/>
+      <c r="E10" s="5" t="n"/>
+      <c r="F10" s="5" t="n"/>
+      <c r="G10" s="5" t="n"/>
+      <c r="H10" s="5" t="n"/>
+      <c r="I10" s="5" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>意愿</t>
         </is>
       </c>
-      <c r="B4" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C4" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="D4" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="E4" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="F4" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="G4" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="H4" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="I4" s="6" t="inlineStr">
-        <is>
-          <t>sum</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I11" s="6" t="inlineStr">
+        <is>
+          <t>合计</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>低意愿</t>
         </is>
       </c>
-      <c r="B5" s="15" t="n">
-        <v>0.000204</v>
-      </c>
-      <c r="C5" s="15" t="n">
-        <v>0.000764</v>
-      </c>
-      <c r="D5" s="15" t="n">
-        <v>0.003861</v>
-      </c>
-      <c r="E5" s="15" t="n">
-        <v>0.00749</v>
-      </c>
-      <c r="F5" s="15" t="n">
-        <v>0.020909</v>
-      </c>
-      <c r="G5" s="15" t="n">
-        <v>0.163572</v>
-      </c>
-      <c r="H5" s="15" t="n">
-        <v>0.136535</v>
-      </c>
-      <c r="I5" s="15" t="n">
-        <v>0.333335</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>中意愿</t>
-        </is>
-      </c>
-      <c r="B6" s="15" t="n">
-        <v>0.008305999999999999</v>
-      </c>
-      <c r="C6" s="15" t="n">
-        <v>0.026067</v>
-      </c>
-      <c r="D6" s="15" t="n">
-        <v>0.047253</v>
-      </c>
-      <c r="E6" s="15" t="n">
-        <v>0.038475</v>
-      </c>
-      <c r="F6" s="15" t="n">
-        <v>0.07004100000000001</v>
-      </c>
-      <c r="G6" s="15" t="n">
-        <v>0.124647</v>
-      </c>
-      <c r="H6" s="15" t="n">
-        <v>0.018542</v>
-      </c>
-      <c r="I6" s="15" t="n">
-        <v>0.333331</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>高意愿</t>
-        </is>
-      </c>
-      <c r="B7" s="15" t="n">
-        <v>0.014912</v>
-      </c>
-      <c r="C7" s="15" t="n">
-        <v>0.04953</v>
-      </c>
-      <c r="D7" s="15" t="n">
-        <v>0.071578</v>
-      </c>
-      <c r="E7" s="15" t="n">
-        <v>0.08300100000000001</v>
-      </c>
-      <c r="F7" s="15" t="n">
-        <v>0.01968</v>
-      </c>
-      <c r="G7" s="15" t="n">
-        <v>0.074943</v>
-      </c>
-      <c r="H7" s="15" t="n">
-        <v>0.01969</v>
-      </c>
-      <c r="I7" s="15" t="n">
-        <v>0.333334</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>sum</t>
-        </is>
-      </c>
-      <c r="B8" s="15" t="n">
-        <v>0.023422</v>
-      </c>
-      <c r="C8" s="15" t="n">
-        <v>0.076361</v>
-      </c>
-      <c r="D8" s="15" t="n">
-        <v>0.122692</v>
-      </c>
-      <c r="E8" s="15" t="n">
-        <v>0.128966</v>
-      </c>
-      <c r="F8" s="15" t="n">
-        <v>0.11063</v>
-      </c>
-      <c r="G8" s="15" t="n">
-        <v>0.363162</v>
-      </c>
-      <c r="H8" s="15" t="n">
-        <v>0.174767</v>
-      </c>
-      <c r="I8" s="15" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9"/>
-    <row r="10"/>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>当前可用全量观察：30天发起率（意愿评级 x 资产评级）</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="n"/>
-      <c r="C11" s="5" t="n"/>
-      <c r="D11" s="5" t="n"/>
-      <c r="E11" s="5" t="n"/>
-      <c r="F11" s="5" t="n"/>
-      <c r="G11" s="5" t="n"/>
-      <c r="H11" s="5" t="n"/>
-      <c r="I11" s="5" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>意愿</t>
-        </is>
-      </c>
-      <c r="B12" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C12" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="D12" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="E12" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="F12" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="G12" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="H12" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="I12" s="6" t="inlineStr">
-        <is>
-          <t>sum</t>
-        </is>
+      <c r="B12" s="15" t="n">
+        <v>0.0112092862092862</v>
+      </c>
+      <c r="C12" s="15" t="n">
+        <v>0.0551282051282051</v>
+      </c>
+      <c r="D12" s="15" t="n">
+        <v>0.0894317394317394</v>
+      </c>
+      <c r="E12" s="15" t="n">
+        <v>0.101039501039501</v>
+      </c>
+      <c r="F12" s="15" t="n">
+        <v>0.0136001386001386</v>
+      </c>
+      <c r="G12" s="15" t="n">
+        <v>0.0522695772695772</v>
+      </c>
+      <c r="H12" s="15" t="n">
+        <v>0.0106548856548856</v>
+      </c>
+      <c r="I12" s="15" t="n">
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>低意愿</t>
+          <t>中意愿</t>
         </is>
       </c>
       <c r="B13" s="15" t="n">
-        <v>0</v>
+        <v>0.0141198891198891</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>0.00267379679144385</v>
+        <v>0.0514553014553014</v>
       </c>
       <c r="D13" s="15" t="n">
-        <v>0.002644103648863035</v>
+        <v>0.0638600138600138</v>
       </c>
       <c r="E13" s="15" t="n">
-        <v>0.0008178844056706652</v>
+        <v>0.0867983367983368</v>
       </c>
       <c r="F13" s="15" t="n">
-        <v>0.0017578125</v>
+        <v>0.0154712404712404</v>
       </c>
       <c r="G13" s="15" t="n">
-        <v>0.002396764368103061</v>
+        <v>0.0758316008316008</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>0.002721820928111026</v>
+        <v>0.0257969507969507</v>
       </c>
       <c r="I13" s="15" t="n">
-        <v>0.002456385376849946</v>
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>中意愿</t>
+          <t>高意愿</t>
         </is>
       </c>
       <c r="B14" s="15" t="n">
-        <v>0.03515240904621435</v>
+        <v>0.0126645876645876</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>0.03297822340592198</v>
+        <v>0.0452356202356202</v>
       </c>
       <c r="D14" s="15" t="n">
-        <v>0.0326246651110535</v>
+        <v>0.0629244629244629</v>
       </c>
       <c r="E14" s="15" t="n">
-        <v>0.03009074988059226</v>
+        <v>0.08880803880803879</v>
       </c>
       <c r="F14" s="15" t="n">
-        <v>0.02020290362078013</v>
+        <v>0.0149688149688149</v>
       </c>
       <c r="G14" s="15" t="n">
-        <v>0.02085346875255959</v>
+        <v>0.0788981288981289</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>0.02587820724589803</v>
+        <v>0.0298336798336798</v>
       </c>
       <c r="I14" s="15" t="n">
-        <v>0.02503568212585836</v>
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>高意愿</t>
+          <t>合计</t>
         </is>
       </c>
       <c r="B15" s="15" t="n">
-        <v>0.4077776256333014</v>
+        <v>0.0379937629937629</v>
       </c>
       <c r="C15" s="15" t="n">
-        <v>0.435544378942161</v>
+        <v>0.1518191268191268</v>
       </c>
       <c r="D15" s="15" t="n">
-        <v>0.4237341320781629</v>
+        <v>0.2162162162162162</v>
       </c>
       <c r="E15" s="15" t="n">
-        <v>0.4543039189155945</v>
+        <v>0.2766458766458766</v>
       </c>
       <c r="F15" s="15" t="n">
-        <v>0.4099398215397385</v>
+        <v>0.044040194040194</v>
       </c>
       <c r="G15" s="15" t="n">
-        <v>0.4526877911887311</v>
+        <v>0.206999306999307</v>
       </c>
       <c r="H15" s="15" t="n">
-        <v>0.5020221922638183</v>
+        <v>0.0662855162855162</v>
       </c>
       <c r="I15" s="15" t="n">
-        <v>0.4427068019210036</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>sum</t>
-        </is>
-      </c>
-      <c r="B16" s="15" t="n">
-        <v>0.2720774126057013</v>
-      </c>
-      <c r="C16" s="15" t="n">
-        <v>0.2937936198090756</v>
-      </c>
-      <c r="D16" s="15" t="n">
-        <v>0.2598522167487685</v>
-      </c>
-      <c r="E16" s="15" t="n">
-        <v>0.3014091196960101</v>
-      </c>
-      <c r="F16" s="15" t="n">
-        <v>0.08604651162790698</v>
-      </c>
-      <c r="G16" s="15" t="n">
-        <v>0.1016552716804606</v>
-      </c>
-      <c r="H16" s="15" t="n">
-        <v>0.06143169258450071</v>
-      </c>
-      <c r="I16" s="15" t="n">
-        <v>0.1567332253855594</v>
-      </c>
-    </row>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16"/>
     <row r="17"/>
-    <row r="18"/>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>老户 - 30天发起率 - G卡V7</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n"/>
+      <c r="C18" s="5" t="n"/>
+      <c r="D18" s="5" t="n"/>
+      <c r="E18" s="5" t="n"/>
+      <c r="F18" s="5" t="n"/>
+      <c r="G18" s="5" t="n"/>
+      <c r="H18" s="5" t="n"/>
+      <c r="I18" s="5" t="n"/>
+    </row>
     <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>当前可用全量观察：人头风险率（意愿评级 x 资产评级）</t>
-        </is>
-      </c>
-      <c r="B19" s="5" t="n"/>
-      <c r="C19" s="5" t="n"/>
-      <c r="D19" s="5" t="n"/>
-      <c r="E19" s="5" t="n"/>
-      <c r="F19" s="5" t="n"/>
-      <c r="G19" s="5" t="n"/>
-      <c r="H19" s="5" t="n"/>
-      <c r="I19" s="5" t="n"/>
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>意愿</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I19" s="6" t="inlineStr">
+        <is>
+          <t>合计</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="6" t="inlineStr">
-        <is>
-          <t>意愿</t>
-        </is>
-      </c>
-      <c r="B20" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C20" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="D20" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="E20" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="F20" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="G20" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="H20" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="I20" s="6" t="inlineStr">
-        <is>
-          <t>sum</t>
-        </is>
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>低意愿</t>
+        </is>
+      </c>
+      <c r="B20" s="15" t="n">
+        <v>0.1576506955177743</v>
+      </c>
+      <c r="C20" s="15" t="n">
+        <v>0.1407919547454431</v>
+      </c>
+      <c r="D20" s="15" t="n">
+        <v>0.1418055017435102</v>
+      </c>
+      <c r="E20" s="15" t="n">
+        <v>0.150034293552812</v>
+      </c>
+      <c r="F20" s="15" t="n">
+        <v>0.1503184713375796</v>
+      </c>
+      <c r="G20" s="15" t="n">
+        <v>0.1581040768975803</v>
+      </c>
+      <c r="H20" s="15" t="n">
+        <v>0.1560975609756097</v>
+      </c>
+      <c r="I20" s="15" t="n">
+        <v>0.148024948024948</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>低意愿</t>
+          <t>中意愿</t>
         </is>
       </c>
       <c r="B21" s="15" t="n">
-        <v>0</v>
+        <v>0.4159509202453987</v>
       </c>
       <c r="C21" s="15" t="n">
-        <v>0</v>
+        <v>0.4144781144781145</v>
       </c>
       <c r="D21" s="15" t="n">
-        <v>0</v>
+        <v>0.4232230059685296</v>
       </c>
       <c r="E21" s="15" t="n">
-        <v>0</v>
+        <v>0.417564870259481</v>
       </c>
       <c r="F21" s="15" t="n">
-        <v>0</v>
+        <v>0.458006718924972</v>
       </c>
       <c r="G21" s="15" t="n">
-        <v>2.496629550107355e-05</v>
+        <v>0.4537354352296093</v>
       </c>
       <c r="H21" s="15" t="n">
-        <v>0</v>
+        <v>0.4412357286769644</v>
       </c>
       <c r="I21" s="15" t="n">
-        <v>1.225129863765559e-05</v>
+        <v>0.43004158004158</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>中意愿</t>
+          <t>高意愿</t>
         </is>
       </c>
       <c r="B22" s="15" t="n">
-        <v>0.0002458210422812193</v>
+        <v>0.7578659370725034</v>
       </c>
       <c r="C22" s="15" t="n">
-        <v>0.0004699984333385555</v>
+        <v>0.795863653772501</v>
       </c>
       <c r="D22" s="15" t="n">
-        <v>0.0005617492005876761</v>
+        <v>0.7926762114537445</v>
       </c>
       <c r="E22" s="15" t="n">
-        <v>0.000636841267314122</v>
+        <v>0.8055013655872025</v>
       </c>
       <c r="F22" s="15" t="n">
-        <v>0.0003498338289312576</v>
+        <v>0.7824074074074074</v>
       </c>
       <c r="G22" s="15" t="n">
-        <v>0.0001965762961749529</v>
+        <v>0.7749231444883619</v>
       </c>
       <c r="H22" s="15" t="n">
-        <v>0.0001101200308336086</v>
+        <v>0.7799070847851336</v>
       </c>
       <c r="I22" s="15" t="n">
-        <v>0.0003491641500303222</v>
+        <v>0.7893970893970894</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>高意愿</t>
+          <t>合计</t>
         </is>
       </c>
       <c r="B23" s="15" t="n">
-        <v>0.008489661782828974</v>
+        <v>0.4537163702690378</v>
       </c>
       <c r="C23" s="15" t="n">
-        <v>0.01430514902914623</v>
+        <v>0.4287344516718019</v>
       </c>
       <c r="D23" s="15" t="n">
-        <v>0.01363571530452147</v>
+        <v>0.4143429487179487</v>
       </c>
       <c r="E23" s="15" t="n">
-        <v>0.01409628773155551</v>
+        <v>0.4443887775551102</v>
       </c>
       <c r="F23" s="15" t="n">
-        <v>0.01203569205229301</v>
+        <v>0.473249409913454</v>
       </c>
       <c r="G23" s="15" t="n">
-        <v>0.01174290929896739</v>
+        <v>0.5015065282892535</v>
       </c>
       <c r="H23" s="15" t="n">
-        <v>0.00891838639427564</v>
+        <v>0.5478306325143754</v>
       </c>
       <c r="I23" s="15" t="n">
-        <v>0.01282098402430658</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="7" t="inlineStr">
-        <is>
-          <t>sum</t>
-        </is>
-      </c>
-      <c r="B24" s="15" t="n">
-        <v>0.005492110539621654</v>
-      </c>
-      <c r="C24" s="15" t="n">
-        <v>0.009439259833676498</v>
-      </c>
-      <c r="D24" s="15" t="n">
-        <v>0.008171348688590067</v>
-      </c>
-      <c r="E24" s="15" t="n">
-        <v>0.009262191260291324</v>
-      </c>
-      <c r="F24" s="15" t="n">
-        <v>0.0023624953857512</v>
-      </c>
-      <c r="G24" s="15" t="n">
-        <v>0.002502024109391868</v>
-      </c>
-      <c r="H24" s="15" t="n">
-        <v>0.001016462011192766</v>
-      </c>
-      <c r="I24" s="15" t="n">
-        <v>0.004394141417028931</v>
-      </c>
-    </row>
+        <v>0.4558212058212058</v>
+      </c>
+    </row>
+    <row r="24"/>
     <row r="25"/>
-    <row r="26"/>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>老户 - 新增订单3期金额逾期率 - G卡V7</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n"/>
+      <c r="C26" s="5" t="n"/>
+      <c r="D26" s="5" t="n"/>
+      <c r="E26" s="5" t="n"/>
+      <c r="F26" s="5" t="n"/>
+      <c r="G26" s="5" t="n"/>
+      <c r="H26" s="5" t="n"/>
+      <c r="I26" s="5" t="n"/>
+    </row>
     <row r="27">
-      <c r="A27" s="4" t="inlineStr">
-        <is>
-          <t>当前可用全量观察：金额风险（仅意愿维度）</t>
-        </is>
-      </c>
-      <c r="B27" s="5" t="n"/>
-      <c r="C27" s="5" t="n"/>
-      <c r="D27" s="5" t="n"/>
-      <c r="E27" s="5" t="n"/>
-      <c r="F27" s="5" t="n"/>
-      <c r="G27" s="5" t="n"/>
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>意愿</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E27" s="6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F27" s="6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G27" s="6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H27" s="6" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I27" s="6" t="inlineStr">
+        <is>
+          <t>合计</t>
+        </is>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" s="6" t="inlineStr">
-        <is>
-          <t>意愿</t>
-        </is>
-      </c>
-      <c r="B28" s="6" t="inlineStr">
-        <is>
-          <t>样本数</t>
-        </is>
-      </c>
-      <c r="C28" s="6" t="inlineStr">
-        <is>
-          <t>本金金额</t>
-        </is>
-      </c>
-      <c r="D28" s="6" t="inlineStr">
-        <is>
-          <t>逾期金额</t>
-        </is>
-      </c>
-      <c r="E28" s="6" t="inlineStr">
-        <is>
-          <t>金额逾期率</t>
-        </is>
-      </c>
-      <c r="F28" s="6" t="inlineStr">
-        <is>
-          <t>人头风险数</t>
-        </is>
-      </c>
-      <c r="G28" s="6" t="inlineStr">
-        <is>
-          <t>人头风险率</t>
-        </is>
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>低意愿</t>
+        </is>
+      </c>
+      <c r="B28" s="15" t="n">
+        <v>0.0323087574838298</v>
+      </c>
+      <c r="C28" s="15" t="n">
+        <v>0.008611639625493399</v>
+      </c>
+      <c r="D28" s="15" t="n">
+        <v>0.039544904931394</v>
+      </c>
+      <c r="E28" s="15" t="n">
+        <v>0.0361334137107048</v>
+      </c>
+      <c r="F28" s="15" t="n">
+        <v>0.0136527193541979</v>
+      </c>
+      <c r="G28" s="15" t="n">
+        <v>0.035696434223038</v>
+      </c>
+      <c r="H28" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" s="15" t="n">
+        <v>0.0266553219567532</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
         <is>
-          <t>低意愿</t>
-        </is>
-      </c>
-      <c r="B29" s="8" t="n">
-        <v>163248</v>
-      </c>
-      <c r="C29" s="20" t="n">
-        <v>521252.1400000001</v>
-      </c>
-      <c r="D29" s="20" t="n">
-        <v>28750.83</v>
-      </c>
-      <c r="E29" s="21" t="n">
-        <v>0.0551572411769858</v>
-      </c>
-      <c r="F29" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="G29" s="9" t="n">
-        <v>1.2e-05</v>
+          <t>中意愿</t>
+        </is>
+      </c>
+      <c r="B29" s="15" t="n">
+        <v>0.0213400160825072</v>
+      </c>
+      <c r="C29" s="15" t="n">
+        <v>0.0227639202671805</v>
+      </c>
+      <c r="D29" s="15" t="n">
+        <v>0.0414493680214617</v>
+      </c>
+      <c r="E29" s="15" t="n">
+        <v>0.0446821452990801</v>
+      </c>
+      <c r="F29" s="15" t="n">
+        <v>0.0252495877164835</v>
+      </c>
+      <c r="G29" s="15" t="n">
+        <v>0.0503424868185618</v>
+      </c>
+      <c r="H29" s="15" t="n">
+        <v>0.0873597620425407</v>
+      </c>
+      <c r="I29" s="15" t="n">
+        <v>0.033209708967333</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>中意愿</t>
-        </is>
-      </c>
-      <c r="B30" s="8" t="n">
-        <v>163247</v>
-      </c>
-      <c r="C30" s="20" t="n">
-        <v>8700368.42</v>
-      </c>
-      <c r="D30" s="20" t="n">
-        <v>239162.97</v>
-      </c>
-      <c r="E30" s="21" t="n">
-        <v>0.0274888324786595</v>
-      </c>
-      <c r="F30" s="8" t="n">
-        <v>57</v>
-      </c>
-      <c r="G30" s="9" t="n">
-        <v>0.000349</v>
+          <t>高意愿</t>
+        </is>
+      </c>
+      <c r="B30" s="15" t="n">
+        <v>0.0319419912200306</v>
+      </c>
+      <c r="C30" s="15" t="n">
+        <v>0.0369991653035138</v>
+      </c>
+      <c r="D30" s="15" t="n">
+        <v>0.0513274944846388</v>
+      </c>
+      <c r="E30" s="15" t="n">
+        <v>0.0584439853141064</v>
+      </c>
+      <c r="F30" s="15" t="n">
+        <v>0.09829677262143779</v>
+      </c>
+      <c r="G30" s="15" t="n">
+        <v>0.09251907667709471</v>
+      </c>
+      <c r="H30" s="15" t="n">
+        <v>0.0409060914137395</v>
+      </c>
+      <c r="I30" s="15" t="n">
+        <v>0.0489142762289343</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
         <is>
-          <t>高意愿</t>
-        </is>
-      </c>
-      <c r="B31" s="8" t="n">
-        <v>163248</v>
-      </c>
-      <c r="C31" s="20" t="n">
-        <v>174513096.34</v>
-      </c>
-      <c r="D31" s="20" t="n">
-        <v>5938278.56</v>
-      </c>
-      <c r="E31" s="21" t="n">
-        <v>0.0340276958265102</v>
-      </c>
-      <c r="F31" s="8" t="n">
-        <v>2093</v>
-      </c>
-      <c r="G31" s="9" t="n">
-        <v>0.012821</v>
+          <t>合计</t>
+        </is>
+      </c>
+      <c r="B31" s="15" t="n">
+        <v>0.029100256362737</v>
+      </c>
+      <c r="C31" s="15" t="n">
+        <v>0.0306205592399156</v>
+      </c>
+      <c r="D31" s="15" t="n">
+        <v>0.0475325380445715</v>
+      </c>
+      <c r="E31" s="15" t="n">
+        <v>0.0530715870367645</v>
+      </c>
+      <c r="F31" s="15" t="n">
+        <v>0.066624285479436</v>
+      </c>
+      <c r="G31" s="15" t="n">
+        <v>0.0777624539436802</v>
+      </c>
+      <c r="H31" s="15" t="n">
+        <v>0.0519544430035813</v>
+      </c>
+      <c r="I31" s="15" t="n">
+        <v>0.0428829038916342</v>
       </c>
     </row>
     <row r="32"/>
     <row r="33"/>
     <row r="34">
-      <c r="A34" s="4" t="inlineStr">
-        <is>
-          <t>待补矩阵口径</t>
+      <c r="A34" s="13" t="inlineStr">
+        <is>
+          <t>流失户 DEV-OOS 意愿 x 资产评级</t>
         </is>
       </c>
       <c r="B34" s="5" t="n"/>
       <c r="C34" s="5" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="6" t="inlineStr">
-        <is>
-          <t>待补客群</t>
-        </is>
-      </c>
-      <c r="B35" s="6" t="inlineStr">
-        <is>
-          <t>待补指标</t>
-        </is>
-      </c>
-      <c r="C35" s="6" t="inlineStr">
-        <is>
-          <t>目标矩阵</t>
-        </is>
-      </c>
-    </row>
+      <c r="D34" s="5" t="n"/>
+      <c r="E34" s="5" t="n"/>
+      <c r="F34" s="5" t="n"/>
+      <c r="G34" s="5" t="n"/>
+      <c r="H34" s="5" t="n"/>
+    </row>
+    <row r="35"/>
     <row r="36">
-      <c r="A36" s="7" t="inlineStr">
-        <is>
-          <t>老户</t>
-        </is>
-      </c>
-      <c r="B36" s="7" t="inlineStr">
-        <is>
-          <t>占比</t>
-        </is>
-      </c>
-      <c r="C36" s="7" t="inlineStr">
-        <is>
-          <t>资产评级 x 意愿评级，含行/列 sum</t>
-        </is>
-      </c>
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>流失户 - 占比 - G卡V7</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n"/>
+      <c r="C36" s="5" t="n"/>
+      <c r="D36" s="5" t="n"/>
+      <c r="E36" s="5" t="n"/>
+      <c r="F36" s="5" t="n"/>
+      <c r="G36" s="5" t="n"/>
+      <c r="H36" s="5" t="n"/>
+      <c r="I36" s="5" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="7" t="inlineStr">
-        <is>
-          <t>老户</t>
-        </is>
-      </c>
-      <c r="B37" s="7" t="inlineStr">
-        <is>
-          <t>30天发起率</t>
-        </is>
-      </c>
-      <c r="C37" s="7" t="inlineStr">
-        <is>
-          <t>资产评级 x 意愿评级，含行/列加权整体</t>
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>意愿</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E37" s="6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F37" s="6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G37" s="6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H37" s="6" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I37" s="6" t="inlineStr">
+        <is>
+          <t>合计</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="inlineStr">
         <is>
-          <t>老户</t>
-        </is>
-      </c>
-      <c r="B38" s="7" t="inlineStr">
-        <is>
-          <t>新增订单3期金额逾期率</t>
-        </is>
-      </c>
-      <c r="C38" s="7" t="inlineStr">
-        <is>
-          <t>资产评级 x 意愿评级，含行/列加权整体</t>
-        </is>
+          <t>低意愿</t>
+        </is>
+      </c>
+      <c r="B38" s="15" t="n">
+        <v>2.54679740226665e-05</v>
+      </c>
+      <c r="C38" s="15" t="n">
+        <v>0.0002631690649008</v>
+      </c>
+      <c r="D38" s="15" t="n">
+        <v>0.0019695233244195</v>
+      </c>
+      <c r="E38" s="15" t="n">
+        <v>0.0052124453499724</v>
+      </c>
+      <c r="F38" s="15" t="n">
+        <v>0.0124029033490385</v>
+      </c>
+      <c r="G38" s="15" t="n">
+        <v>0.1477312279808141</v>
+      </c>
+      <c r="H38" s="15" t="n">
+        <v>0.1657285962901651</v>
+      </c>
+      <c r="I38" s="15" t="n">
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="7" t="inlineStr">
         <is>
-          <t>流失户</t>
-        </is>
-      </c>
-      <c r="B39" s="7" t="inlineStr">
-        <is>
-          <t>占比</t>
-        </is>
-      </c>
-      <c r="C39" s="7" t="inlineStr">
-        <is>
-          <t>资产评级 x 意愿评级，含行/列 sum</t>
-        </is>
+          <t>中意愿</t>
+        </is>
+      </c>
+      <c r="B39" s="15" t="n">
+        <v>0.0009168470648159</v>
+      </c>
+      <c r="C39" s="15" t="n">
+        <v>0.0044908527526635</v>
+      </c>
+      <c r="D39" s="15" t="n">
+        <v>0.0148478288552145</v>
+      </c>
+      <c r="E39" s="15" t="n">
+        <v>0.0177002419457532</v>
+      </c>
+      <c r="F39" s="15" t="n">
+        <v>0.0548834840188463</v>
+      </c>
+      <c r="G39" s="15" t="n">
+        <v>0.1834458168852668</v>
+      </c>
+      <c r="H39" s="15" t="n">
+        <v>0.0570482618107729</v>
+      </c>
+      <c r="I39" s="15" t="n">
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="inlineStr">
         <is>
-          <t>流失户</t>
-        </is>
-      </c>
-      <c r="B40" s="7" t="inlineStr">
-        <is>
-          <t>30天发起率</t>
-        </is>
-      </c>
-      <c r="C40" s="7" t="inlineStr">
-        <is>
-          <t>资产评级 x 意愿评级，含行/列加权整体</t>
-        </is>
+          <t>高意愿</t>
+        </is>
+      </c>
+      <c r="B40" s="15" t="n">
+        <v>0.015170423192835</v>
+      </c>
+      <c r="C40" s="15" t="n">
+        <v>0.0358673967485886</v>
+      </c>
+      <c r="D40" s="15" t="n">
+        <v>0.0534742561229254</v>
+      </c>
+      <c r="E40" s="15" t="n">
+        <v>0.0344072329046224</v>
+      </c>
+      <c r="F40" s="15" t="n">
+        <v>0.0754106710811155</v>
+      </c>
+      <c r="G40" s="15" t="n">
+        <v>0.1032641453372384</v>
+      </c>
+      <c r="H40" s="15" t="n">
+        <v>0.0157392079460078</v>
+      </c>
+      <c r="I40" s="15" t="n">
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="7" t="inlineStr">
         <is>
-          <t>流失户</t>
-        </is>
-      </c>
-      <c r="B41" s="7" t="inlineStr">
-        <is>
-          <t>新增订单3期金额逾期率</t>
-        </is>
-      </c>
-      <c r="C41" s="7" t="inlineStr">
-        <is>
-          <t>资产评级 x 意愿评级，含行/列加权整体</t>
-        </is>
+          <t>合计</t>
+        </is>
+      </c>
+      <c r="B41" s="15" t="n">
+        <v>0.0161127382316736</v>
+      </c>
+      <c r="C41" s="15" t="n">
+        <v>0.040621418566153</v>
+      </c>
+      <c r="D41" s="15" t="n">
+        <v>0.0702916083025595</v>
+      </c>
+      <c r="E41" s="15" t="n">
+        <v>0.057319920200348</v>
+      </c>
+      <c r="F41" s="15" t="n">
+        <v>0.1426970584490003</v>
+      </c>
+      <c r="G41" s="15" t="n">
+        <v>0.4344411902033193</v>
+      </c>
+      <c r="H41" s="15" t="n">
+        <v>0.2385160660469459</v>
+      </c>
+      <c r="I41" s="15" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42"/>
+    <row r="43"/>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>流失户 - 30天发起率 - G卡V7</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n"/>
+      <c r="C44" s="5" t="n"/>
+      <c r="D44" s="5" t="n"/>
+      <c r="E44" s="5" t="n"/>
+      <c r="F44" s="5" t="n"/>
+      <c r="G44" s="5" t="n"/>
+      <c r="H44" s="5" t="n"/>
+      <c r="I44" s="5" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>意愿</t>
+        </is>
+      </c>
+      <c r="B45" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D45" s="6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E45" s="6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F45" s="6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G45" s="6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H45" s="6" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I45" s="6" t="inlineStr">
+        <is>
+          <t>合计</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="7" t="inlineStr">
+        <is>
+          <t>低意愿</t>
+        </is>
+      </c>
+      <c r="B46" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C46" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D46" s="15" t="n">
+        <v>0.0043103448275862</v>
+      </c>
+      <c r="E46" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" s="15" t="n">
+        <v>0.0027378507871321</v>
+      </c>
+      <c r="G46" s="15" t="n">
+        <v>0.0021836570509136</v>
+      </c>
+      <c r="H46" s="15" t="n">
+        <v>0.0024075402110439</v>
+      </c>
+      <c r="I46" s="15" t="n">
+        <v>0.0022921176620399</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="7" t="inlineStr">
+        <is>
+          <t>中意愿</t>
+        </is>
+      </c>
+      <c r="B47" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C47" s="15" t="n">
+        <v>0.0075614366729678</v>
+      </c>
+      <c r="D47" s="15" t="n">
+        <v>0.006861063464837</v>
+      </c>
+      <c r="E47" s="15" t="n">
+        <v>0.0057553956834532</v>
+      </c>
+      <c r="F47" s="15" t="n">
+        <v>0.0061871616395978</v>
+      </c>
+      <c r="G47" s="15" t="n">
+        <v>0.0068952751168494</v>
+      </c>
+      <c r="H47" s="15" t="n">
+        <v>0.0083333333333333</v>
+      </c>
+      <c r="I47" s="15" t="n">
+        <v>0.0069527569081879</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="7" t="inlineStr">
+        <is>
+          <t>高意愿</t>
+        </is>
+      </c>
+      <c r="B48" s="15" t="n">
+        <v>0.0912143256855064</v>
+      </c>
+      <c r="C48" s="15" t="n">
+        <v>0.0752662721893491</v>
+      </c>
+      <c r="D48" s="15" t="n">
+        <v>0.0598507699634862</v>
+      </c>
+      <c r="E48" s="15" t="n">
+        <v>0.0523069331359486</v>
+      </c>
+      <c r="F48" s="15" t="n">
+        <v>0.0569627378138016</v>
+      </c>
+      <c r="G48" s="15" t="n">
+        <v>0.0752219664584018</v>
+      </c>
+      <c r="H48" s="15" t="n">
+        <v>0.1402373247033441</v>
+      </c>
+      <c r="I48" s="15" t="n">
+        <v>0.0700623965363555</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="7" t="inlineStr">
+        <is>
+          <t>合计</t>
+        </is>
+      </c>
+      <c r="B49" s="15" t="n">
+        <v>0.08587987355110641</v>
+      </c>
+      <c r="C49" s="15" t="n">
+        <v>0.06729362591431549</v>
+      </c>
+      <c r="D49" s="15" t="n">
+        <v>0.0471014492753623</v>
+      </c>
+      <c r="E49" s="15" t="n">
+        <v>0.0331753554502369</v>
+      </c>
+      <c r="F49" s="15" t="n">
+        <v>0.0327205663632577</v>
+      </c>
+      <c r="G49" s="15" t="n">
+        <v>0.021533952125061</v>
+      </c>
+      <c r="H49" s="15" t="n">
+        <v>0.0129199886104783</v>
+      </c>
+      <c r="I49" s="15" t="n">
+        <v>0.0264357570355278</v>
+      </c>
+    </row>
+    <row r="50"/>
+    <row r="51"/>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>流失户 - 新增订单3期金额逾期率 - G卡V7</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n"/>
+      <c r="C52" s="5" t="n"/>
+      <c r="D52" s="5" t="n"/>
+      <c r="E52" s="5" t="n"/>
+      <c r="F52" s="5" t="n"/>
+      <c r="G52" s="5" t="n"/>
+      <c r="H52" s="5" t="n"/>
+      <c r="I52" s="5" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t>意愿</t>
+        </is>
+      </c>
+      <c r="B53" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C53" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D53" s="6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E53" s="6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F53" s="6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G53" s="6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H53" s="6" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I53" s="6" t="inlineStr">
+        <is>
+          <t>合计</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="7" t="inlineStr">
+        <is>
+          <t>低意愿</t>
+        </is>
+      </c>
+      <c r="B54" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C54" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D54" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E54" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F54" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G54" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="7" t="inlineStr">
+        <is>
+          <t>中意愿</t>
+        </is>
+      </c>
+      <c r="B55" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C55" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D55" s="15" t="n">
+        <v>0.0165774948875549</v>
+      </c>
+      <c r="E55" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F55" s="15" t="n">
+        <v>0.1714847347672421</v>
+      </c>
+      <c r="G55" s="15" t="n">
+        <v>0.1730771735522329</v>
+      </c>
+      <c r="H55" s="15" t="n">
+        <v>0.0286460007819287</v>
+      </c>
+      <c r="I55" s="15" t="n">
+        <v>0.1262030289119844</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="7" t="inlineStr">
+        <is>
+          <t>高意愿</t>
+        </is>
+      </c>
+      <c r="B56" s="15" t="n">
+        <v>0.0393828169465833</v>
+      </c>
+      <c r="C56" s="15" t="n">
+        <v>0.0512647772940201</v>
+      </c>
+      <c r="D56" s="15" t="n">
+        <v>0.0397594387590541</v>
+      </c>
+      <c r="E56" s="15" t="n">
+        <v>0.0184595915314542</v>
+      </c>
+      <c r="F56" s="15" t="n">
+        <v>0.0490848860098146</v>
+      </c>
+      <c r="G56" s="15" t="n">
+        <v>0.0490799977647711</v>
+      </c>
+      <c r="H56" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I56" s="15" t="n">
+        <v>0.0422069102478506</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="7" t="inlineStr">
+        <is>
+          <t>合计</t>
+        </is>
+      </c>
+      <c r="B57" s="15" t="n">
+        <v>0.0393828169465833</v>
+      </c>
+      <c r="C57" s="15" t="n">
+        <v>0.0511710568587837</v>
+      </c>
+      <c r="D57" s="15" t="n">
+        <v>0.0364962103504686</v>
+      </c>
+      <c r="E57" s="15" t="n">
+        <v>0.0179759421990095</v>
+      </c>
+      <c r="F57" s="15" t="n">
+        <v>0.0634558099772638</v>
+      </c>
+      <c r="G57" s="15" t="n">
+        <v>0.0763676785486706</v>
+      </c>
+      <c r="H57" s="15" t="n">
+        <v>0.0030933433616706</v>
+      </c>
+      <c r="I57" s="15" t="n">
+        <v>0.047161726640022</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A19:I19"/>
-    <mergeCell ref="A11:I11"/>
-    <mergeCell ref="A27:G27"/>
-    <mergeCell ref="A3:I3"/>
-    <mergeCell ref="A34:C34"/>
-    <mergeCell ref="A1:H1"/>
+  <mergeCells count="10">
+    <mergeCell ref="A52:I52"/>
+    <mergeCell ref="A10:I10"/>
+    <mergeCell ref="A36:I36"/>
+    <mergeCell ref="A44:I44"/>
+    <mergeCell ref="A18:I18"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A8:H8"/>
+    <mergeCell ref="A26:I26"/>
+    <mergeCell ref="A6:H6"/>
+    <mergeCell ref="A34:H34"/>
   </mergeCells>
-  <conditionalFormatting sqref="E29:E31">
+  <conditionalFormatting sqref="B12:I15">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -35911,8 +36849,56 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G29:G31">
+  <conditionalFormatting sqref="B20:I23">
     <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B28:I31">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B38:I41">
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B46:I49">
+    <cfRule type="colorScale" priority="5">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B54:I57">
+    <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>

--- a/projects/2026-05-fujie-gcard-v1/versions/fujie_gcard_v7_20260630/reports_tuned_main_lgbm_tuned_balanced/model_report.xlsx
+++ b/projects/2026-05-fujie-gcard-v1/versions/fujie_gcard_v7_20260630/reports_tuned_main_lgbm_tuned_balanced/model_report.xlsx
@@ -35607,7 +35607,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I57"/>
+  <dimension ref="A1:I52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -35622,1222 +35622,1189 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>3、意愿交叉风险（DEV-OOS）</t>
+      <c r="A1" s="13" t="inlineStr">
+        <is>
+          <t>以下矩阵均限定 DEV-OOS；意愿评级按对应客群、对应分数版本等频三等分，资产评级为 zc_level 1-7，并保留行列合计。</t>
         </is>
       </c>
       <c r="B1" s="5" t="n"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>序号</t>
-        </is>
-      </c>
-      <c r="B2" s="6" t="inlineStr">
-        <is>
-          <t>结论</t>
-        </is>
-      </c>
-    </row>
+      <c r="C1" s="5" t="n"/>
+      <c r="D1" s="5" t="n"/>
+      <c r="E1" s="5" t="n"/>
+      <c r="F1" s="5" t="n"/>
+      <c r="G1" s="5" t="n"/>
+      <c r="H1" s="5" t="n"/>
+    </row>
+    <row r="2"/>
     <row r="3">
-      <c r="A3" s="7" t="n">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>老户 DEV-OOS 意愿 x 资产评级</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="n"/>
+      <c r="C3" s="5" t="n"/>
+      <c r="D3" s="5" t="n"/>
+      <c r="E3" s="5" t="n"/>
+      <c r="F3" s="5" t="n"/>
+      <c r="G3" s="5" t="n"/>
+      <c r="H3" s="5" t="n"/>
+    </row>
+    <row r="4"/>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>老户 - 占比 - G卡V7</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n"/>
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="5" t="n"/>
+      <c r="F5" s="5" t="n"/>
+      <c r="G5" s="5" t="n"/>
+      <c r="H5" s="5" t="n"/>
+      <c r="I5" s="5" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>意愿</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I6" s="6" t="inlineStr">
+        <is>
+          <t>合计</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>低意愿</t>
+        </is>
+      </c>
+      <c r="B7" s="15" t="n">
+        <v>0.0112092862092862</v>
+      </c>
+      <c r="C7" s="15" t="n">
+        <v>0.0551282051282051</v>
+      </c>
+      <c r="D7" s="15" t="n">
+        <v>0.0894317394317394</v>
+      </c>
+      <c r="E7" s="15" t="n">
+        <v>0.101039501039501</v>
+      </c>
+      <c r="F7" s="15" t="n">
+        <v>0.0136001386001386</v>
+      </c>
+      <c r="G7" s="15" t="n">
+        <v>0.0522695772695772</v>
+      </c>
+      <c r="H7" s="15" t="n">
+        <v>0.0106548856548856</v>
+      </c>
+      <c r="I7" s="15" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>中意愿</t>
+        </is>
+      </c>
+      <c r="B8" s="15" t="n">
+        <v>0.0141198891198891</v>
+      </c>
+      <c r="C8" s="15" t="n">
+        <v>0.0514553014553014</v>
+      </c>
+      <c r="D8" s="15" t="n">
+        <v>0.0638600138600138</v>
+      </c>
+      <c r="E8" s="15" t="n">
+        <v>0.0867983367983368</v>
+      </c>
+      <c r="F8" s="15" t="n">
+        <v>0.0154712404712404</v>
+      </c>
+      <c r="G8" s="15" t="n">
+        <v>0.0758316008316008</v>
+      </c>
+      <c r="H8" s="15" t="n">
+        <v>0.0257969507969507</v>
+      </c>
+      <c r="I8" s="15" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>高意愿</t>
+        </is>
+      </c>
+      <c r="B9" s="15" t="n">
+        <v>0.0126645876645876</v>
+      </c>
+      <c r="C9" s="15" t="n">
+        <v>0.0452356202356202</v>
+      </c>
+      <c r="D9" s="15" t="n">
+        <v>0.0629244629244629</v>
+      </c>
+      <c r="E9" s="15" t="n">
+        <v>0.08880803880803879</v>
+      </c>
+      <c r="F9" s="15" t="n">
+        <v>0.0149688149688149</v>
+      </c>
+      <c r="G9" s="15" t="n">
+        <v>0.0788981288981289</v>
+      </c>
+      <c r="H9" s="15" t="n">
+        <v>0.0298336798336798</v>
+      </c>
+      <c r="I9" s="15" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>合计</t>
+        </is>
+      </c>
+      <c r="B10" s="15" t="n">
+        <v>0.0379937629937629</v>
+      </c>
+      <c r="C10" s="15" t="n">
+        <v>0.1518191268191268</v>
+      </c>
+      <c r="D10" s="15" t="n">
+        <v>0.2162162162162162</v>
+      </c>
+      <c r="E10" s="15" t="n">
+        <v>0.2766458766458766</v>
+      </c>
+      <c r="F10" s="15" t="n">
+        <v>0.044040194040194</v>
+      </c>
+      <c r="G10" s="15" t="n">
+        <v>0.206999306999307</v>
+      </c>
+      <c r="H10" s="15" t="n">
+        <v>0.0662855162855162</v>
+      </c>
+      <c r="I10" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="7" t="inlineStr">
-        <is>
-          <t>（1）高、中、低意愿评级为对应模型分数在各客群内三等频分箱得到。</t>
-        </is>
-      </c>
-    </row>
-    <row r="4"/>
-    <row r="5"/>
-    <row r="6">
-      <c r="A6" s="13" t="inlineStr">
-        <is>
-          <t>以下矩阵均限定 DEV-OOS；意愿评级按对应客群、对应分数版本等频三等分，资产评级为 zc_level 1-7，并保留行列合计。</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="n"/>
-      <c r="C6" s="5" t="n"/>
-      <c r="D6" s="5" t="n"/>
-      <c r="E6" s="5" t="n"/>
-      <c r="F6" s="5" t="n"/>
-      <c r="G6" s="5" t="n"/>
-      <c r="H6" s="5" t="n"/>
-    </row>
-    <row r="7"/>
-    <row r="8">
-      <c r="A8" s="13" t="inlineStr">
-        <is>
-          <t>老户 DEV-OOS 意愿 x 资产评级</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="n"/>
-      <c r="C8" s="5" t="n"/>
-      <c r="D8" s="5" t="n"/>
-      <c r="E8" s="5" t="n"/>
-      <c r="F8" s="5" t="n"/>
-      <c r="G8" s="5" t="n"/>
-      <c r="H8" s="5" t="n"/>
-    </row>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>老户 - 占比 - G卡V7</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="n"/>
-      <c r="C10" s="5" t="n"/>
-      <c r="D10" s="5" t="n"/>
-      <c r="E10" s="5" t="n"/>
-      <c r="F10" s="5" t="n"/>
-      <c r="G10" s="5" t="n"/>
-      <c r="H10" s="5" t="n"/>
-      <c r="I10" s="5" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="6" t="inlineStr">
+    </row>
+    <row r="11"/>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>老户 - 30天发起率 - G卡V7</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n"/>
+      <c r="C13" s="5" t="n"/>
+      <c r="D13" s="5" t="n"/>
+      <c r="E13" s="5" t="n"/>
+      <c r="F13" s="5" t="n"/>
+      <c r="G13" s="5" t="n"/>
+      <c r="H13" s="5" t="n"/>
+      <c r="I13" s="5" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>意愿</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B14" s="6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr">
+      <c r="C14" s="6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D11" s="6" t="inlineStr">
+      <c r="D14" s="6" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E11" s="6" t="inlineStr">
+      <c r="E14" s="6" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="F11" s="6" t="inlineStr">
+      <c r="F14" s="6" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="G11" s="6" t="inlineStr">
+      <c r="G14" s="6" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="H11" s="6" t="inlineStr">
+      <c r="H14" s="6" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="I11" s="6" t="inlineStr">
+      <c r="I14" s="6" t="inlineStr">
         <is>
           <t>合计</t>
         </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>低意愿</t>
-        </is>
-      </c>
-      <c r="B12" s="15" t="n">
-        <v>0.0112092862092862</v>
-      </c>
-      <c r="C12" s="15" t="n">
-        <v>0.0551282051282051</v>
-      </c>
-      <c r="D12" s="15" t="n">
-        <v>0.0894317394317394</v>
-      </c>
-      <c r="E12" s="15" t="n">
-        <v>0.101039501039501</v>
-      </c>
-      <c r="F12" s="15" t="n">
-        <v>0.0136001386001386</v>
-      </c>
-      <c r="G12" s="15" t="n">
-        <v>0.0522695772695772</v>
-      </c>
-      <c r="H12" s="15" t="n">
-        <v>0.0106548856548856</v>
-      </c>
-      <c r="I12" s="15" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>中意愿</t>
-        </is>
-      </c>
-      <c r="B13" s="15" t="n">
-        <v>0.0141198891198891</v>
-      </c>
-      <c r="C13" s="15" t="n">
-        <v>0.0514553014553014</v>
-      </c>
-      <c r="D13" s="15" t="n">
-        <v>0.0638600138600138</v>
-      </c>
-      <c r="E13" s="15" t="n">
-        <v>0.0867983367983368</v>
-      </c>
-      <c r="F13" s="15" t="n">
-        <v>0.0154712404712404</v>
-      </c>
-      <c r="G13" s="15" t="n">
-        <v>0.0758316008316008</v>
-      </c>
-      <c r="H13" s="15" t="n">
-        <v>0.0257969507969507</v>
-      </c>
-      <c r="I13" s="15" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>高意愿</t>
-        </is>
-      </c>
-      <c r="B14" s="15" t="n">
-        <v>0.0126645876645876</v>
-      </c>
-      <c r="C14" s="15" t="n">
-        <v>0.0452356202356202</v>
-      </c>
-      <c r="D14" s="15" t="n">
-        <v>0.0629244629244629</v>
-      </c>
-      <c r="E14" s="15" t="n">
-        <v>0.08880803880803879</v>
-      </c>
-      <c r="F14" s="15" t="n">
-        <v>0.0149688149688149</v>
-      </c>
-      <c r="G14" s="15" t="n">
-        <v>0.0788981288981289</v>
-      </c>
-      <c r="H14" s="15" t="n">
-        <v>0.0298336798336798</v>
-      </c>
-      <c r="I14" s="15" t="n">
-        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
+          <t>低意愿</t>
+        </is>
+      </c>
+      <c r="B15" s="15" t="n">
+        <v>0.1576506955177743</v>
+      </c>
+      <c r="C15" s="15" t="n">
+        <v>0.1407919547454431</v>
+      </c>
+      <c r="D15" s="15" t="n">
+        <v>0.1418055017435102</v>
+      </c>
+      <c r="E15" s="15" t="n">
+        <v>0.150034293552812</v>
+      </c>
+      <c r="F15" s="15" t="n">
+        <v>0.1503184713375796</v>
+      </c>
+      <c r="G15" s="15" t="n">
+        <v>0.1581040768975803</v>
+      </c>
+      <c r="H15" s="15" t="n">
+        <v>0.1560975609756097</v>
+      </c>
+      <c r="I15" s="15" t="n">
+        <v>0.148024948024948</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>中意愿</t>
+        </is>
+      </c>
+      <c r="B16" s="15" t="n">
+        <v>0.4159509202453987</v>
+      </c>
+      <c r="C16" s="15" t="n">
+        <v>0.4144781144781145</v>
+      </c>
+      <c r="D16" s="15" t="n">
+        <v>0.4232230059685296</v>
+      </c>
+      <c r="E16" s="15" t="n">
+        <v>0.417564870259481</v>
+      </c>
+      <c r="F16" s="15" t="n">
+        <v>0.458006718924972</v>
+      </c>
+      <c r="G16" s="15" t="n">
+        <v>0.4537354352296093</v>
+      </c>
+      <c r="H16" s="15" t="n">
+        <v>0.4412357286769644</v>
+      </c>
+      <c r="I16" s="15" t="n">
+        <v>0.43004158004158</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>高意愿</t>
+        </is>
+      </c>
+      <c r="B17" s="15" t="n">
+        <v>0.7578659370725034</v>
+      </c>
+      <c r="C17" s="15" t="n">
+        <v>0.795863653772501</v>
+      </c>
+      <c r="D17" s="15" t="n">
+        <v>0.7926762114537445</v>
+      </c>
+      <c r="E17" s="15" t="n">
+        <v>0.8055013655872025</v>
+      </c>
+      <c r="F17" s="15" t="n">
+        <v>0.7824074074074074</v>
+      </c>
+      <c r="G17" s="15" t="n">
+        <v>0.7749231444883619</v>
+      </c>
+      <c r="H17" s="15" t="n">
+        <v>0.7799070847851336</v>
+      </c>
+      <c r="I17" s="15" t="n">
+        <v>0.7893970893970894</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
           <t>合计</t>
         </is>
       </c>
-      <c r="B15" s="15" t="n">
-        <v>0.0379937629937629</v>
-      </c>
-      <c r="C15" s="15" t="n">
-        <v>0.1518191268191268</v>
-      </c>
-      <c r="D15" s="15" t="n">
-        <v>0.2162162162162162</v>
-      </c>
-      <c r="E15" s="15" t="n">
-        <v>0.2766458766458766</v>
-      </c>
-      <c r="F15" s="15" t="n">
-        <v>0.044040194040194</v>
-      </c>
-      <c r="G15" s="15" t="n">
-        <v>0.206999306999307</v>
-      </c>
-      <c r="H15" s="15" t="n">
-        <v>0.0662855162855162</v>
-      </c>
-      <c r="I15" s="15" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>老户 - 30天发起率 - G卡V7</t>
-        </is>
-      </c>
-      <c r="B18" s="5" t="n"/>
-      <c r="C18" s="5" t="n"/>
-      <c r="D18" s="5" t="n"/>
-      <c r="E18" s="5" t="n"/>
-      <c r="F18" s="5" t="n"/>
-      <c r="G18" s="5" t="n"/>
-      <c r="H18" s="5" t="n"/>
-      <c r="I18" s="5" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="6" t="inlineStr">
+      <c r="B18" s="15" t="n">
+        <v>0.4537163702690378</v>
+      </c>
+      <c r="C18" s="15" t="n">
+        <v>0.4287344516718019</v>
+      </c>
+      <c r="D18" s="15" t="n">
+        <v>0.4143429487179487</v>
+      </c>
+      <c r="E18" s="15" t="n">
+        <v>0.4443887775551102</v>
+      </c>
+      <c r="F18" s="15" t="n">
+        <v>0.473249409913454</v>
+      </c>
+      <c r="G18" s="15" t="n">
+        <v>0.5015065282892535</v>
+      </c>
+      <c r="H18" s="15" t="n">
+        <v>0.5478306325143754</v>
+      </c>
+      <c r="I18" s="15" t="n">
+        <v>0.4558212058212058</v>
+      </c>
+    </row>
+    <row r="19"/>
+    <row r="20"/>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>老户 - 新增订单3期金额逾期率 - G卡V7</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n"/>
+      <c r="C21" s="5" t="n"/>
+      <c r="D21" s="5" t="n"/>
+      <c r="E21" s="5" t="n"/>
+      <c r="F21" s="5" t="n"/>
+      <c r="G21" s="5" t="n"/>
+      <c r="H21" s="5" t="n"/>
+      <c r="I21" s="5" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
         <is>
           <t>意愿</t>
         </is>
       </c>
-      <c r="B19" s="6" t="inlineStr">
+      <c r="B22" s="6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr">
+      <c r="C22" s="6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D19" s="6" t="inlineStr">
+      <c r="D22" s="6" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E19" s="6" t="inlineStr">
+      <c r="E22" s="6" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="F19" s="6" t="inlineStr">
+      <c r="F22" s="6" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="G19" s="6" t="inlineStr">
+      <c r="G22" s="6" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="H19" s="6" t="inlineStr">
+      <c r="H22" s="6" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="I19" s="6" t="inlineStr">
+      <c r="I22" s="6" t="inlineStr">
         <is>
           <t>合计</t>
         </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t>低意愿</t>
-        </is>
-      </c>
-      <c r="B20" s="15" t="n">
-        <v>0.1576506955177743</v>
-      </c>
-      <c r="C20" s="15" t="n">
-        <v>0.1407919547454431</v>
-      </c>
-      <c r="D20" s="15" t="n">
-        <v>0.1418055017435102</v>
-      </c>
-      <c r="E20" s="15" t="n">
-        <v>0.150034293552812</v>
-      </c>
-      <c r="F20" s="15" t="n">
-        <v>0.1503184713375796</v>
-      </c>
-      <c r="G20" s="15" t="n">
-        <v>0.1581040768975803</v>
-      </c>
-      <c r="H20" s="15" t="n">
-        <v>0.1560975609756097</v>
-      </c>
-      <c r="I20" s="15" t="n">
-        <v>0.148024948024948</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="7" t="inlineStr">
-        <is>
-          <t>中意愿</t>
-        </is>
-      </c>
-      <c r="B21" s="15" t="n">
-        <v>0.4159509202453987</v>
-      </c>
-      <c r="C21" s="15" t="n">
-        <v>0.4144781144781145</v>
-      </c>
-      <c r="D21" s="15" t="n">
-        <v>0.4232230059685296</v>
-      </c>
-      <c r="E21" s="15" t="n">
-        <v>0.417564870259481</v>
-      </c>
-      <c r="F21" s="15" t="n">
-        <v>0.458006718924972</v>
-      </c>
-      <c r="G21" s="15" t="n">
-        <v>0.4537354352296093</v>
-      </c>
-      <c r="H21" s="15" t="n">
-        <v>0.4412357286769644</v>
-      </c>
-      <c r="I21" s="15" t="n">
-        <v>0.43004158004158</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="7" t="inlineStr">
-        <is>
-          <t>高意愿</t>
-        </is>
-      </c>
-      <c r="B22" s="15" t="n">
-        <v>0.7578659370725034</v>
-      </c>
-      <c r="C22" s="15" t="n">
-        <v>0.795863653772501</v>
-      </c>
-      <c r="D22" s="15" t="n">
-        <v>0.7926762114537445</v>
-      </c>
-      <c r="E22" s="15" t="n">
-        <v>0.8055013655872025</v>
-      </c>
-      <c r="F22" s="15" t="n">
-        <v>0.7824074074074074</v>
-      </c>
-      <c r="G22" s="15" t="n">
-        <v>0.7749231444883619</v>
-      </c>
-      <c r="H22" s="15" t="n">
-        <v>0.7799070847851336</v>
-      </c>
-      <c r="I22" s="15" t="n">
-        <v>0.7893970893970894</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
         <is>
+          <t>低意愿</t>
+        </is>
+      </c>
+      <c r="B23" s="15" t="n">
+        <v>0.0323087574838298</v>
+      </c>
+      <c r="C23" s="15" t="n">
+        <v>0.008611639625493399</v>
+      </c>
+      <c r="D23" s="15" t="n">
+        <v>0.039544904931394</v>
+      </c>
+      <c r="E23" s="15" t="n">
+        <v>0.0361334137107048</v>
+      </c>
+      <c r="F23" s="15" t="n">
+        <v>0.0136527193541979</v>
+      </c>
+      <c r="G23" s="15" t="n">
+        <v>0.035696434223038</v>
+      </c>
+      <c r="H23" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" s="15" t="n">
+        <v>0.0266553219567532</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>中意愿</t>
+        </is>
+      </c>
+      <c r="B24" s="15" t="n">
+        <v>0.0213400160825072</v>
+      </c>
+      <c r="C24" s="15" t="n">
+        <v>0.0227639202671805</v>
+      </c>
+      <c r="D24" s="15" t="n">
+        <v>0.0414493680214617</v>
+      </c>
+      <c r="E24" s="15" t="n">
+        <v>0.0446821452990801</v>
+      </c>
+      <c r="F24" s="15" t="n">
+        <v>0.0252495877164835</v>
+      </c>
+      <c r="G24" s="15" t="n">
+        <v>0.0503424868185618</v>
+      </c>
+      <c r="H24" s="15" t="n">
+        <v>0.0873597620425407</v>
+      </c>
+      <c r="I24" s="15" t="n">
+        <v>0.033209708967333</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>高意愿</t>
+        </is>
+      </c>
+      <c r="B25" s="15" t="n">
+        <v>0.0319419912200306</v>
+      </c>
+      <c r="C25" s="15" t="n">
+        <v>0.0369991653035138</v>
+      </c>
+      <c r="D25" s="15" t="n">
+        <v>0.0513274944846388</v>
+      </c>
+      <c r="E25" s="15" t="n">
+        <v>0.0584439853141064</v>
+      </c>
+      <c r="F25" s="15" t="n">
+        <v>0.09829677262143779</v>
+      </c>
+      <c r="G25" s="15" t="n">
+        <v>0.09251907667709471</v>
+      </c>
+      <c r="H25" s="15" t="n">
+        <v>0.0409060914137395</v>
+      </c>
+      <c r="I25" s="15" t="n">
+        <v>0.0489142762289343</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
           <t>合计</t>
         </is>
       </c>
-      <c r="B23" s="15" t="n">
-        <v>0.4537163702690378</v>
-      </c>
-      <c r="C23" s="15" t="n">
-        <v>0.4287344516718019</v>
-      </c>
-      <c r="D23" s="15" t="n">
-        <v>0.4143429487179487</v>
-      </c>
-      <c r="E23" s="15" t="n">
-        <v>0.4443887775551102</v>
-      </c>
-      <c r="F23" s="15" t="n">
-        <v>0.473249409913454</v>
-      </c>
-      <c r="G23" s="15" t="n">
-        <v>0.5015065282892535</v>
-      </c>
-      <c r="H23" s="15" t="n">
-        <v>0.5478306325143754</v>
-      </c>
-      <c r="I23" s="15" t="n">
-        <v>0.4558212058212058</v>
-      </c>
-    </row>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>老户 - 新增订单3期金额逾期率 - G卡V7</t>
-        </is>
-      </c>
-      <c r="B26" s="5" t="n"/>
-      <c r="C26" s="5" t="n"/>
-      <c r="D26" s="5" t="n"/>
-      <c r="E26" s="5" t="n"/>
-      <c r="F26" s="5" t="n"/>
-      <c r="G26" s="5" t="n"/>
-      <c r="H26" s="5" t="n"/>
-      <c r="I26" s="5" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="6" t="inlineStr">
+      <c r="B26" s="15" t="n">
+        <v>0.029100256362737</v>
+      </c>
+      <c r="C26" s="15" t="n">
+        <v>0.0306205592399156</v>
+      </c>
+      <c r="D26" s="15" t="n">
+        <v>0.0475325380445715</v>
+      </c>
+      <c r="E26" s="15" t="n">
+        <v>0.0530715870367645</v>
+      </c>
+      <c r="F26" s="15" t="n">
+        <v>0.066624285479436</v>
+      </c>
+      <c r="G26" s="15" t="n">
+        <v>0.0777624539436802</v>
+      </c>
+      <c r="H26" s="15" t="n">
+        <v>0.0519544430035813</v>
+      </c>
+      <c r="I26" s="15" t="n">
+        <v>0.0428829038916342</v>
+      </c>
+    </row>
+    <row r="27"/>
+    <row r="28"/>
+    <row r="29">
+      <c r="A29" s="13" t="inlineStr">
+        <is>
+          <t>流失户 DEV-OOS 意愿 x 资产评级</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n"/>
+      <c r="C29" s="5" t="n"/>
+      <c r="D29" s="5" t="n"/>
+      <c r="E29" s="5" t="n"/>
+      <c r="F29" s="5" t="n"/>
+      <c r="G29" s="5" t="n"/>
+      <c r="H29" s="5" t="n"/>
+    </row>
+    <row r="30"/>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>流失户 - 占比 - G卡V7</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n"/>
+      <c r="C31" s="5" t="n"/>
+      <c r="D31" s="5" t="n"/>
+      <c r="E31" s="5" t="n"/>
+      <c r="F31" s="5" t="n"/>
+      <c r="G31" s="5" t="n"/>
+      <c r="H31" s="5" t="n"/>
+      <c r="I31" s="5" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
         <is>
           <t>意愿</t>
         </is>
       </c>
-      <c r="B27" s="6" t="inlineStr">
+      <c r="B32" s="6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="C27" s="6" t="inlineStr">
+      <c r="C32" s="6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D27" s="6" t="inlineStr">
+      <c r="D32" s="6" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E27" s="6" t="inlineStr">
+      <c r="E32" s="6" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="F27" s="6" t="inlineStr">
+      <c r="F32" s="6" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="G27" s="6" t="inlineStr">
+      <c r="G32" s="6" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="H27" s="6" t="inlineStr">
+      <c r="H32" s="6" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="I27" s="6" t="inlineStr">
+      <c r="I32" s="6" t="inlineStr">
         <is>
           <t>合计</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="7" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="7" t="inlineStr">
         <is>
           <t>低意愿</t>
         </is>
       </c>
-      <c r="B28" s="15" t="n">
-        <v>0.0323087574838298</v>
-      </c>
-      <c r="C28" s="15" t="n">
-        <v>0.008611639625493399</v>
-      </c>
-      <c r="D28" s="15" t="n">
-        <v>0.039544904931394</v>
-      </c>
-      <c r="E28" s="15" t="n">
-        <v>0.0361334137107048</v>
-      </c>
-      <c r="F28" s="15" t="n">
-        <v>0.0136527193541979</v>
-      </c>
-      <c r="G28" s="15" t="n">
-        <v>0.035696434223038</v>
-      </c>
-      <c r="H28" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I28" s="15" t="n">
-        <v>0.0266553219567532</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="7" t="inlineStr">
+      <c r="B33" s="15" t="n">
+        <v>2.54679740226665e-05</v>
+      </c>
+      <c r="C33" s="15" t="n">
+        <v>0.0002631690649008</v>
+      </c>
+      <c r="D33" s="15" t="n">
+        <v>0.0019695233244195</v>
+      </c>
+      <c r="E33" s="15" t="n">
+        <v>0.0052124453499724</v>
+      </c>
+      <c r="F33" s="15" t="n">
+        <v>0.0124029033490385</v>
+      </c>
+      <c r="G33" s="15" t="n">
+        <v>0.1477312279808141</v>
+      </c>
+      <c r="H33" s="15" t="n">
+        <v>0.1657285962901651</v>
+      </c>
+      <c r="I33" s="15" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="7" t="inlineStr">
         <is>
           <t>中意愿</t>
         </is>
       </c>
-      <c r="B29" s="15" t="n">
-        <v>0.0213400160825072</v>
-      </c>
-      <c r="C29" s="15" t="n">
-        <v>0.0227639202671805</v>
-      </c>
-      <c r="D29" s="15" t="n">
-        <v>0.0414493680214617</v>
-      </c>
-      <c r="E29" s="15" t="n">
-        <v>0.0446821452990801</v>
-      </c>
-      <c r="F29" s="15" t="n">
-        <v>0.0252495877164835</v>
-      </c>
-      <c r="G29" s="15" t="n">
-        <v>0.0503424868185618</v>
-      </c>
-      <c r="H29" s="15" t="n">
-        <v>0.0873597620425407</v>
-      </c>
-      <c r="I29" s="15" t="n">
-        <v>0.033209708967333</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="7" t="inlineStr">
+      <c r="B34" s="15" t="n">
+        <v>0.0009168470648159</v>
+      </c>
+      <c r="C34" s="15" t="n">
+        <v>0.0044908527526635</v>
+      </c>
+      <c r="D34" s="15" t="n">
+        <v>0.0148478288552145</v>
+      </c>
+      <c r="E34" s="15" t="n">
+        <v>0.0177002419457532</v>
+      </c>
+      <c r="F34" s="15" t="n">
+        <v>0.0548834840188463</v>
+      </c>
+      <c r="G34" s="15" t="n">
+        <v>0.1834458168852668</v>
+      </c>
+      <c r="H34" s="15" t="n">
+        <v>0.0570482618107729</v>
+      </c>
+      <c r="I34" s="15" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="7" t="inlineStr">
         <is>
           <t>高意愿</t>
         </is>
       </c>
-      <c r="B30" s="15" t="n">
-        <v>0.0319419912200306</v>
-      </c>
-      <c r="C30" s="15" t="n">
-        <v>0.0369991653035138</v>
-      </c>
-      <c r="D30" s="15" t="n">
-        <v>0.0513274944846388</v>
-      </c>
-      <c r="E30" s="15" t="n">
-        <v>0.0584439853141064</v>
-      </c>
-      <c r="F30" s="15" t="n">
-        <v>0.09829677262143779</v>
-      </c>
-      <c r="G30" s="15" t="n">
-        <v>0.09251907667709471</v>
-      </c>
-      <c r="H30" s="15" t="n">
-        <v>0.0409060914137395</v>
-      </c>
-      <c r="I30" s="15" t="n">
-        <v>0.0489142762289343</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="7" t="inlineStr">
+      <c r="B35" s="15" t="n">
+        <v>0.015170423192835</v>
+      </c>
+      <c r="C35" s="15" t="n">
+        <v>0.0358673967485886</v>
+      </c>
+      <c r="D35" s="15" t="n">
+        <v>0.0534742561229254</v>
+      </c>
+      <c r="E35" s="15" t="n">
+        <v>0.0344072329046224</v>
+      </c>
+      <c r="F35" s="15" t="n">
+        <v>0.0754106710811155</v>
+      </c>
+      <c r="G35" s="15" t="n">
+        <v>0.1032641453372384</v>
+      </c>
+      <c r="H35" s="15" t="n">
+        <v>0.0157392079460078</v>
+      </c>
+      <c r="I35" s="15" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="7" t="inlineStr">
         <is>
           <t>合计</t>
         </is>
       </c>
-      <c r="B31" s="15" t="n">
-        <v>0.029100256362737</v>
-      </c>
-      <c r="C31" s="15" t="n">
-        <v>0.0306205592399156</v>
-      </c>
-      <c r="D31" s="15" t="n">
-        <v>0.0475325380445715</v>
-      </c>
-      <c r="E31" s="15" t="n">
-        <v>0.0530715870367645</v>
-      </c>
-      <c r="F31" s="15" t="n">
-        <v>0.066624285479436</v>
-      </c>
-      <c r="G31" s="15" t="n">
-        <v>0.0777624539436802</v>
-      </c>
-      <c r="H31" s="15" t="n">
-        <v>0.0519544430035813</v>
-      </c>
-      <c r="I31" s="15" t="n">
-        <v>0.0428829038916342</v>
-      </c>
-    </row>
-    <row r="32"/>
-    <row r="33"/>
-    <row r="34">
-      <c r="A34" s="13" t="inlineStr">
-        <is>
-          <t>流失户 DEV-OOS 意愿 x 资产评级</t>
-        </is>
-      </c>
-      <c r="B34" s="5" t="n"/>
-      <c r="C34" s="5" t="n"/>
-      <c r="D34" s="5" t="n"/>
-      <c r="E34" s="5" t="n"/>
-      <c r="F34" s="5" t="n"/>
-      <c r="G34" s="5" t="n"/>
-      <c r="H34" s="5" t="n"/>
-    </row>
-    <row r="35"/>
-    <row r="36">
-      <c r="A36" s="4" t="inlineStr">
-        <is>
-          <t>流失户 - 占比 - G卡V7</t>
-        </is>
-      </c>
-      <c r="B36" s="5" t="n"/>
-      <c r="C36" s="5" t="n"/>
-      <c r="D36" s="5" t="n"/>
-      <c r="E36" s="5" t="n"/>
-      <c r="F36" s="5" t="n"/>
-      <c r="G36" s="5" t="n"/>
-      <c r="H36" s="5" t="n"/>
-      <c r="I36" s="5" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="6" t="inlineStr">
+      <c r="B36" s="15" t="n">
+        <v>0.0161127382316736</v>
+      </c>
+      <c r="C36" s="15" t="n">
+        <v>0.040621418566153</v>
+      </c>
+      <c r="D36" s="15" t="n">
+        <v>0.0702916083025595</v>
+      </c>
+      <c r="E36" s="15" t="n">
+        <v>0.057319920200348</v>
+      </c>
+      <c r="F36" s="15" t="n">
+        <v>0.1426970584490003</v>
+      </c>
+      <c r="G36" s="15" t="n">
+        <v>0.4344411902033193</v>
+      </c>
+      <c r="H36" s="15" t="n">
+        <v>0.2385160660469459</v>
+      </c>
+      <c r="I36" s="15" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37"/>
+    <row r="38"/>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>流失户 - 30天发起率 - G卡V7</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n"/>
+      <c r="C39" s="5" t="n"/>
+      <c r="D39" s="5" t="n"/>
+      <c r="E39" s="5" t="n"/>
+      <c r="F39" s="5" t="n"/>
+      <c r="G39" s="5" t="n"/>
+      <c r="H39" s="5" t="n"/>
+      <c r="I39" s="5" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="inlineStr">
         <is>
           <t>意愿</t>
         </is>
       </c>
-      <c r="B37" s="6" t="inlineStr">
+      <c r="B40" s="6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="C37" s="6" t="inlineStr">
+      <c r="C40" s="6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D37" s="6" t="inlineStr">
+      <c r="D40" s="6" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E37" s="6" t="inlineStr">
+      <c r="E40" s="6" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="F37" s="6" t="inlineStr">
+      <c r="F40" s="6" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="G37" s="6" t="inlineStr">
+      <c r="G40" s="6" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="H37" s="6" t="inlineStr">
+      <c r="H40" s="6" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="I37" s="6" t="inlineStr">
+      <c r="I40" s="6" t="inlineStr">
         <is>
           <t>合计</t>
         </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="7" t="inlineStr">
-        <is>
-          <t>低意愿</t>
-        </is>
-      </c>
-      <c r="B38" s="15" t="n">
-        <v>2.54679740226665e-05</v>
-      </c>
-      <c r="C38" s="15" t="n">
-        <v>0.0002631690649008</v>
-      </c>
-      <c r="D38" s="15" t="n">
-        <v>0.0019695233244195</v>
-      </c>
-      <c r="E38" s="15" t="n">
-        <v>0.0052124453499724</v>
-      </c>
-      <c r="F38" s="15" t="n">
-        <v>0.0124029033490385</v>
-      </c>
-      <c r="G38" s="15" t="n">
-        <v>0.1477312279808141</v>
-      </c>
-      <c r="H38" s="15" t="n">
-        <v>0.1657285962901651</v>
-      </c>
-      <c r="I38" s="15" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="7" t="inlineStr">
-        <is>
-          <t>中意愿</t>
-        </is>
-      </c>
-      <c r="B39" s="15" t="n">
-        <v>0.0009168470648159</v>
-      </c>
-      <c r="C39" s="15" t="n">
-        <v>0.0044908527526635</v>
-      </c>
-      <c r="D39" s="15" t="n">
-        <v>0.0148478288552145</v>
-      </c>
-      <c r="E39" s="15" t="n">
-        <v>0.0177002419457532</v>
-      </c>
-      <c r="F39" s="15" t="n">
-        <v>0.0548834840188463</v>
-      </c>
-      <c r="G39" s="15" t="n">
-        <v>0.1834458168852668</v>
-      </c>
-      <c r="H39" s="15" t="n">
-        <v>0.0570482618107729</v>
-      </c>
-      <c r="I39" s="15" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="7" t="inlineStr">
-        <is>
-          <t>高意愿</t>
-        </is>
-      </c>
-      <c r="B40" s="15" t="n">
-        <v>0.015170423192835</v>
-      </c>
-      <c r="C40" s="15" t="n">
-        <v>0.0358673967485886</v>
-      </c>
-      <c r="D40" s="15" t="n">
-        <v>0.0534742561229254</v>
-      </c>
-      <c r="E40" s="15" t="n">
-        <v>0.0344072329046224</v>
-      </c>
-      <c r="F40" s="15" t="n">
-        <v>0.0754106710811155</v>
-      </c>
-      <c r="G40" s="15" t="n">
-        <v>0.1032641453372384</v>
-      </c>
-      <c r="H40" s="15" t="n">
-        <v>0.0157392079460078</v>
-      </c>
-      <c r="I40" s="15" t="n">
-        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="7" t="inlineStr">
         <is>
+          <t>低意愿</t>
+        </is>
+      </c>
+      <c r="B41" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C41" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D41" s="15" t="n">
+        <v>0.0043103448275862</v>
+      </c>
+      <c r="E41" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" s="15" t="n">
+        <v>0.0027378507871321</v>
+      </c>
+      <c r="G41" s="15" t="n">
+        <v>0.0021836570509136</v>
+      </c>
+      <c r="H41" s="15" t="n">
+        <v>0.0024075402110439</v>
+      </c>
+      <c r="I41" s="15" t="n">
+        <v>0.0022921176620399</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="7" t="inlineStr">
+        <is>
+          <t>中意愿</t>
+        </is>
+      </c>
+      <c r="B42" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C42" s="15" t="n">
+        <v>0.0075614366729678</v>
+      </c>
+      <c r="D42" s="15" t="n">
+        <v>0.006861063464837</v>
+      </c>
+      <c r="E42" s="15" t="n">
+        <v>0.0057553956834532</v>
+      </c>
+      <c r="F42" s="15" t="n">
+        <v>0.0061871616395978</v>
+      </c>
+      <c r="G42" s="15" t="n">
+        <v>0.0068952751168494</v>
+      </c>
+      <c r="H42" s="15" t="n">
+        <v>0.0083333333333333</v>
+      </c>
+      <c r="I42" s="15" t="n">
+        <v>0.0069527569081879</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="7" t="inlineStr">
+        <is>
+          <t>高意愿</t>
+        </is>
+      </c>
+      <c r="B43" s="15" t="n">
+        <v>0.0912143256855064</v>
+      </c>
+      <c r="C43" s="15" t="n">
+        <v>0.0752662721893491</v>
+      </c>
+      <c r="D43" s="15" t="n">
+        <v>0.0598507699634862</v>
+      </c>
+      <c r="E43" s="15" t="n">
+        <v>0.0523069331359486</v>
+      </c>
+      <c r="F43" s="15" t="n">
+        <v>0.0569627378138016</v>
+      </c>
+      <c r="G43" s="15" t="n">
+        <v>0.0752219664584018</v>
+      </c>
+      <c r="H43" s="15" t="n">
+        <v>0.1402373247033441</v>
+      </c>
+      <c r="I43" s="15" t="n">
+        <v>0.0700623965363555</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="7" t="inlineStr">
+        <is>
           <t>合计</t>
         </is>
       </c>
-      <c r="B41" s="15" t="n">
-        <v>0.0161127382316736</v>
-      </c>
-      <c r="C41" s="15" t="n">
-        <v>0.040621418566153</v>
-      </c>
-      <c r="D41" s="15" t="n">
-        <v>0.0702916083025595</v>
-      </c>
-      <c r="E41" s="15" t="n">
-        <v>0.057319920200348</v>
-      </c>
-      <c r="F41" s="15" t="n">
-        <v>0.1426970584490003</v>
-      </c>
-      <c r="G41" s="15" t="n">
-        <v>0.4344411902033193</v>
-      </c>
-      <c r="H41" s="15" t="n">
-        <v>0.2385160660469459</v>
-      </c>
-      <c r="I41" s="15" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="42"/>
-    <row r="43"/>
-    <row r="44">
-      <c r="A44" s="4" t="inlineStr">
-        <is>
-          <t>流失户 - 30天发起率 - G卡V7</t>
-        </is>
-      </c>
-      <c r="B44" s="5" t="n"/>
-      <c r="C44" s="5" t="n"/>
-      <c r="D44" s="5" t="n"/>
-      <c r="E44" s="5" t="n"/>
-      <c r="F44" s="5" t="n"/>
-      <c r="G44" s="5" t="n"/>
-      <c r="H44" s="5" t="n"/>
-      <c r="I44" s="5" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="6" t="inlineStr">
+      <c r="B44" s="15" t="n">
+        <v>0.08587987355110641</v>
+      </c>
+      <c r="C44" s="15" t="n">
+        <v>0.06729362591431549</v>
+      </c>
+      <c r="D44" s="15" t="n">
+        <v>0.0471014492753623</v>
+      </c>
+      <c r="E44" s="15" t="n">
+        <v>0.0331753554502369</v>
+      </c>
+      <c r="F44" s="15" t="n">
+        <v>0.0327205663632577</v>
+      </c>
+      <c r="G44" s="15" t="n">
+        <v>0.021533952125061</v>
+      </c>
+      <c r="H44" s="15" t="n">
+        <v>0.0129199886104783</v>
+      </c>
+      <c r="I44" s="15" t="n">
+        <v>0.0264357570355278</v>
+      </c>
+    </row>
+    <row r="45"/>
+    <row r="46"/>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>流失户 - 新增订单3期金额逾期率 - G卡V7</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n"/>
+      <c r="C47" s="5" t="n"/>
+      <c r="D47" s="5" t="n"/>
+      <c r="E47" s="5" t="n"/>
+      <c r="F47" s="5" t="n"/>
+      <c r="G47" s="5" t="n"/>
+      <c r="H47" s="5" t="n"/>
+      <c r="I47" s="5" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="6" t="inlineStr">
         <is>
           <t>意愿</t>
         </is>
       </c>
-      <c r="B45" s="6" t="inlineStr">
+      <c r="B48" s="6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="C45" s="6" t="inlineStr">
+      <c r="C48" s="6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D45" s="6" t="inlineStr">
+      <c r="D48" s="6" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E45" s="6" t="inlineStr">
+      <c r="E48" s="6" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="F45" s="6" t="inlineStr">
+      <c r="F48" s="6" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="G45" s="6" t="inlineStr">
+      <c r="G48" s="6" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="H45" s="6" t="inlineStr">
+      <c r="H48" s="6" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="I45" s="6" t="inlineStr">
+      <c r="I48" s="6" t="inlineStr">
         <is>
           <t>合计</t>
         </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="7" t="inlineStr">
-        <is>
-          <t>低意愿</t>
-        </is>
-      </c>
-      <c r="B46" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="C46" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="D46" s="15" t="n">
-        <v>0.0043103448275862</v>
-      </c>
-      <c r="E46" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F46" s="15" t="n">
-        <v>0.0027378507871321</v>
-      </c>
-      <c r="G46" s="15" t="n">
-        <v>0.0021836570509136</v>
-      </c>
-      <c r="H46" s="15" t="n">
-        <v>0.0024075402110439</v>
-      </c>
-      <c r="I46" s="15" t="n">
-        <v>0.0022921176620399</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="7" t="inlineStr">
-        <is>
-          <t>中意愿</t>
-        </is>
-      </c>
-      <c r="B47" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="C47" s="15" t="n">
-        <v>0.0075614366729678</v>
-      </c>
-      <c r="D47" s="15" t="n">
-        <v>0.006861063464837</v>
-      </c>
-      <c r="E47" s="15" t="n">
-        <v>0.0057553956834532</v>
-      </c>
-      <c r="F47" s="15" t="n">
-        <v>0.0061871616395978</v>
-      </c>
-      <c r="G47" s="15" t="n">
-        <v>0.0068952751168494</v>
-      </c>
-      <c r="H47" s="15" t="n">
-        <v>0.0083333333333333</v>
-      </c>
-      <c r="I47" s="15" t="n">
-        <v>0.0069527569081879</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="7" t="inlineStr">
-        <is>
-          <t>高意愿</t>
-        </is>
-      </c>
-      <c r="B48" s="15" t="n">
-        <v>0.0912143256855064</v>
-      </c>
-      <c r="C48" s="15" t="n">
-        <v>0.0752662721893491</v>
-      </c>
-      <c r="D48" s="15" t="n">
-        <v>0.0598507699634862</v>
-      </c>
-      <c r="E48" s="15" t="n">
-        <v>0.0523069331359486</v>
-      </c>
-      <c r="F48" s="15" t="n">
-        <v>0.0569627378138016</v>
-      </c>
-      <c r="G48" s="15" t="n">
-        <v>0.0752219664584018</v>
-      </c>
-      <c r="H48" s="15" t="n">
-        <v>0.1402373247033441</v>
-      </c>
-      <c r="I48" s="15" t="n">
-        <v>0.0700623965363555</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="7" t="inlineStr">
         <is>
+          <t>低意愿</t>
+        </is>
+      </c>
+      <c r="B49" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C49" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D49" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E49" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F49" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G49" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="7" t="inlineStr">
+        <is>
+          <t>中意愿</t>
+        </is>
+      </c>
+      <c r="B50" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C50" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D50" s="15" t="n">
+        <v>0.0165774948875549</v>
+      </c>
+      <c r="E50" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F50" s="15" t="n">
+        <v>0.1714847347672421</v>
+      </c>
+      <c r="G50" s="15" t="n">
+        <v>0.1730771735522329</v>
+      </c>
+      <c r="H50" s="15" t="n">
+        <v>0.0286460007819287</v>
+      </c>
+      <c r="I50" s="15" t="n">
+        <v>0.1262030289119844</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="7" t="inlineStr">
+        <is>
+          <t>高意愿</t>
+        </is>
+      </c>
+      <c r="B51" s="15" t="n">
+        <v>0.0393828169465833</v>
+      </c>
+      <c r="C51" s="15" t="n">
+        <v>0.0512647772940201</v>
+      </c>
+      <c r="D51" s="15" t="n">
+        <v>0.0397594387590541</v>
+      </c>
+      <c r="E51" s="15" t="n">
+        <v>0.0184595915314542</v>
+      </c>
+      <c r="F51" s="15" t="n">
+        <v>0.0490848860098146</v>
+      </c>
+      <c r="G51" s="15" t="n">
+        <v>0.0490799977647711</v>
+      </c>
+      <c r="H51" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" s="15" t="n">
+        <v>0.0422069102478506</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="7" t="inlineStr">
+        <is>
           <t>合计</t>
         </is>
       </c>
-      <c r="B49" s="15" t="n">
-        <v>0.08587987355110641</v>
-      </c>
-      <c r="C49" s="15" t="n">
-        <v>0.06729362591431549</v>
-      </c>
-      <c r="D49" s="15" t="n">
-        <v>0.0471014492753623</v>
-      </c>
-      <c r="E49" s="15" t="n">
-        <v>0.0331753554502369</v>
-      </c>
-      <c r="F49" s="15" t="n">
-        <v>0.0327205663632577</v>
-      </c>
-      <c r="G49" s="15" t="n">
-        <v>0.021533952125061</v>
-      </c>
-      <c r="H49" s="15" t="n">
-        <v>0.0129199886104783</v>
-      </c>
-      <c r="I49" s="15" t="n">
-        <v>0.0264357570355278</v>
-      </c>
-    </row>
-    <row r="50"/>
-    <row r="51"/>
-    <row r="52">
-      <c r="A52" s="4" t="inlineStr">
-        <is>
-          <t>流失户 - 新增订单3期金额逾期率 - G卡V7</t>
-        </is>
-      </c>
-      <c r="B52" s="5" t="n"/>
-      <c r="C52" s="5" t="n"/>
-      <c r="D52" s="5" t="n"/>
-      <c r="E52" s="5" t="n"/>
-      <c r="F52" s="5" t="n"/>
-      <c r="G52" s="5" t="n"/>
-      <c r="H52" s="5" t="n"/>
-      <c r="I52" s="5" t="n"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="6" t="inlineStr">
-        <is>
-          <t>意愿</t>
-        </is>
-      </c>
-      <c r="B53" s="6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C53" s="6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D53" s="6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E53" s="6" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="F53" s="6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G53" s="6" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H53" s="6" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="I53" s="6" t="inlineStr">
-        <is>
-          <t>合计</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="7" t="inlineStr">
-        <is>
-          <t>低意愿</t>
-        </is>
-      </c>
-      <c r="B54" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="C54" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="D54" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E54" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F54" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G54" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H54" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I54" s="15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="7" t="inlineStr">
-        <is>
-          <t>中意愿</t>
-        </is>
-      </c>
-      <c r="B55" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="C55" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="D55" s="15" t="n">
-        <v>0.0165774948875549</v>
-      </c>
-      <c r="E55" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F55" s="15" t="n">
-        <v>0.1714847347672421</v>
-      </c>
-      <c r="G55" s="15" t="n">
-        <v>0.1730771735522329</v>
-      </c>
-      <c r="H55" s="15" t="n">
-        <v>0.0286460007819287</v>
-      </c>
-      <c r="I55" s="15" t="n">
-        <v>0.1262030289119844</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="7" t="inlineStr">
-        <is>
-          <t>高意愿</t>
-        </is>
-      </c>
-      <c r="B56" s="15" t="n">
+      <c r="B52" s="15" t="n">
         <v>0.0393828169465833</v>
       </c>
-      <c r="C56" s="15" t="n">
-        <v>0.0512647772940201</v>
-      </c>
-      <c r="D56" s="15" t="n">
-        <v>0.0397594387590541</v>
-      </c>
-      <c r="E56" s="15" t="n">
-        <v>0.0184595915314542</v>
-      </c>
-      <c r="F56" s="15" t="n">
-        <v>0.0490848860098146</v>
-      </c>
-      <c r="G56" s="15" t="n">
-        <v>0.0490799977647711</v>
-      </c>
-      <c r="H56" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I56" s="15" t="n">
-        <v>0.0422069102478506</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="7" t="inlineStr">
-        <is>
-          <t>合计</t>
-        </is>
-      </c>
-      <c r="B57" s="15" t="n">
-        <v>0.0393828169465833</v>
-      </c>
-      <c r="C57" s="15" t="n">
+      <c r="C52" s="15" t="n">
         <v>0.0511710568587837</v>
       </c>
-      <c r="D57" s="15" t="n">
+      <c r="D52" s="15" t="n">
         <v>0.0364962103504686</v>
       </c>
-      <c r="E57" s="15" t="n">
+      <c r="E52" s="15" t="n">
         <v>0.0179759421990095</v>
       </c>
-      <c r="F57" s="15" t="n">
+      <c r="F52" s="15" t="n">
         <v>0.0634558099772638</v>
       </c>
-      <c r="G57" s="15" t="n">
+      <c r="G52" s="15" t="n">
         <v>0.0763676785486706</v>
       </c>
-      <c r="H57" s="15" t="n">
+      <c r="H52" s="15" t="n">
         <v>0.0030933433616706</v>
       </c>
-      <c r="I57" s="15" t="n">
+      <c r="I52" s="15" t="n">
         <v>0.047161726640022</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A52:I52"/>
-    <mergeCell ref="A10:I10"/>
-    <mergeCell ref="A36:I36"/>
-    <mergeCell ref="A44:I44"/>
-    <mergeCell ref="A18:I18"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A8:H8"/>
-    <mergeCell ref="A26:I26"/>
-    <mergeCell ref="A6:H6"/>
-    <mergeCell ref="A34:H34"/>
+  <mergeCells count="9">
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A29:H29"/>
+    <mergeCell ref="A47:I47"/>
+    <mergeCell ref="A5:I5"/>
+    <mergeCell ref="A13:I13"/>
+    <mergeCell ref="A31:I31"/>
+    <mergeCell ref="A39:I39"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A21:I21"/>
   </mergeCells>
-  <conditionalFormatting sqref="B12:I15">
+  <conditionalFormatting sqref="B7:I10">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -36849,7 +36816,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B20:I23">
+  <conditionalFormatting sqref="B15:I18">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -36861,7 +36828,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B28:I31">
+  <conditionalFormatting sqref="B23:I26">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -36873,7 +36840,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B38:I41">
+  <conditionalFormatting sqref="B33:I36">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
@@ -36885,7 +36852,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B46:I49">
+  <conditionalFormatting sqref="B41:I44">
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="min"/>
@@ -36897,7 +36864,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B54:I57">
+  <conditionalFormatting sqref="B49:I52">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="min"/>

--- a/projects/2026-05-fujie-gcard-v1/versions/fujie_gcard_v7_20260630/reports_tuned_main_lgbm_tuned_balanced/model_report.xlsx
+++ b/projects/2026-05-fujie-gcard-v1/versions/fujie_gcard_v7_20260630/reports_tuned_main_lgbm_tuned_balanced/model_report.xlsx
@@ -1138,7 +1138,7 @@
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>更新日期：2026-07-01；指标来源：当前 run 已注册 train/evaluation artifacts。</t>
+          <t>更新日期：2026-07-02；指标来源：当前 run 已注册 train/evaluation artifacts。</t>
         </is>
       </c>
     </row>
@@ -6713,7 +6713,7 @@
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
     </row>
